--- a/Другое/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/Кино-Книги-Одежда-Спорт.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
@@ -14,6 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Кино!$A$1:$I$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Книги!$A$1:$H$101</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="401">
   <si>
     <t>№</t>
   </si>
@@ -1252,10 +1253,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="168" formatCode="dd\.mmm"/>
-    <numFmt numFmtId="169" formatCode="dd\.mm\.yyyy"/>
-    <numFmt numFmtId="170" formatCode="mmm\.yy"/>
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="dd\.mmm"/>
+    <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
+    <numFmt numFmtId="166" formatCode="mmm\.yy"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -1348,12 +1349,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
+        <fgColor rgb="FFBAE18F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1404,11 +1405,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1423,7 +1437,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1448,10 +1462,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1464,15 +1478,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1494,51 +1508,43 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -4740,8 +4746,8 @@
       <c r="H117" s="11">
         <v>8</v>
       </c>
-      <c r="I117" s="30" t="s">
-        <v>78</v>
+      <c r="I117" s="34">
+        <v>46260</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -6655,1781 +6661,1782 @@
     <col min="9" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="35" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:8" s="33" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="35" t="s">
         <v>292</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="35" t="s">
         <v>294</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="H1" s="39" t="s">
+      <c r="H1" s="35" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="35" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="34">
+    <row r="2" spans="1:8" s="33" customFormat="1" ht="30" customHeight="1">
+      <c r="A2" s="36">
         <v>1</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="34">
+      <c r="F2" s="36">
         <v>2015</v>
       </c>
-      <c r="G2" s="34">
+      <c r="G2" s="36">
         <v>2022</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="H2" s="38" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="35" customFormat="1" ht="30" customHeight="1">
-      <c r="A3" s="33">
+    <row r="3" spans="1:8" s="33" customFormat="1" ht="30" customHeight="1">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="39" t="s">
         <v>308</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="39" t="s">
         <v>355</v>
       </c>
-      <c r="F3" s="33">
+      <c r="F3" s="5">
         <v>2016</v>
       </c>
-      <c r="G3" s="41">
+      <c r="G3" s="40">
         <v>2022</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="40" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="35" customFormat="1" ht="30" customHeight="1">
-      <c r="A4" s="34">
+    <row r="4" spans="1:8" s="33" customFormat="1" ht="30" customHeight="1">
+      <c r="A4" s="36">
         <v>3</v>
       </c>
-      <c r="B4" s="42" t="s">
+      <c r="B4" s="39" t="s">
         <v>356</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="39" t="s">
         <v>371</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="5">
         <v>2016</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="41" t="s">
+      <c r="H4" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" customHeight="1">
-      <c r="A5" s="33">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="41" t="s">
         <v>293</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="E5" s="36" t="s">
+      <c r="E5" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="5">
         <v>2016</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="41" t="s">
+      <c r="H5" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1">
-      <c r="A6" s="34">
+      <c r="A6" s="36">
         <v>5</v>
       </c>
-      <c r="B6" s="38" t="s">
+      <c r="B6" s="41" t="s">
         <v>300</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="E6" s="36" t="s">
+      <c r="E6" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="5">
         <v>2022</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="5">
         <v>2023</v>
       </c>
-      <c r="H6" s="41" t="s">
+      <c r="H6" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" customHeight="1">
-      <c r="A7" s="33">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="B7" s="41" t="s">
         <v>301</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="41" t="s">
         <v>298</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="E7" s="36" t="s">
+      <c r="E7" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="5">
         <v>2022</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="5">
         <v>2023</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1">
-      <c r="A8" s="34">
+      <c r="A8" s="36">
         <v>7</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="39" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="D8" s="42" t="s">
+      <c r="D8" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="5">
         <v>2022</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" customHeight="1">
-      <c r="A9" s="33">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B9" s="39" t="s">
         <v>309</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="42" t="s">
+      <c r="D9" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="5">
         <v>2022</v>
       </c>
-      <c r="G9" s="41" t="s">
+      <c r="G9" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1">
-      <c r="A10" s="34">
+      <c r="A10" s="36">
         <v>9</v>
       </c>
-      <c r="B10" s="42" t="s">
+      <c r="B10" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="42" t="s">
+      <c r="D10" s="39" t="s">
         <v>311</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="5">
         <v>2022</v>
       </c>
-      <c r="G10" s="41" t="s">
+      <c r="G10" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="30" customHeight="1">
-      <c r="A11" s="33">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="39" t="s">
         <v>317</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="D11" s="42" t="s">
+      <c r="D11" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="39" t="s">
         <v>307</v>
       </c>
-      <c r="F11" s="33">
+      <c r="F11" s="5">
         <v>2022</v>
       </c>
-      <c r="G11" s="41" t="s">
+      <c r="G11" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1">
-      <c r="A12" s="34">
+      <c r="A12" s="36">
         <v>11</v>
       </c>
-      <c r="B12" s="42" t="s">
+      <c r="B12" s="39" t="s">
         <v>313</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="39" t="s">
         <v>314</v>
       </c>
-      <c r="D12" s="42" t="s">
+      <c r="D12" s="39" t="s">
         <v>315</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="5">
         <v>2022</v>
       </c>
-      <c r="G12" s="41" t="s">
+      <c r="G12" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" customHeight="1">
-      <c r="A13" s="33">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="39" t="s">
         <v>320</v>
       </c>
-      <c r="D13" s="42" t="s">
+      <c r="D13" s="39" t="s">
         <v>321</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="5">
         <v>2022</v>
       </c>
-      <c r="G13" s="41" t="s">
+      <c r="G13" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1">
-      <c r="A14" s="34">
+      <c r="A14" s="36">
         <v>13</v>
       </c>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="39" t="s">
         <v>322</v>
       </c>
-      <c r="C14" s="42" t="s">
+      <c r="C14" s="39" t="s">
         <v>323</v>
       </c>
-      <c r="D14" s="42" t="s">
+      <c r="D14" s="39" t="s">
         <v>321</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="5">
         <v>2022</v>
       </c>
-      <c r="G14" s="41" t="s">
+      <c r="G14" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="30" customHeight="1">
-      <c r="A15" s="33">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="39" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="42" t="s">
+      <c r="C15" s="39" t="s">
         <v>325</v>
       </c>
-      <c r="D15" s="42" t="s">
+      <c r="D15" s="39" t="s">
         <v>326</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="F15" s="33">
+      <c r="F15" s="5">
         <v>2022</v>
       </c>
-      <c r="G15" s="41" t="s">
+      <c r="G15" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="H15" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1">
-      <c r="A16" s="34">
-        <v>15</v>
-      </c>
-      <c r="B16" s="43" t="s">
+      <c r="A16" s="36">
+        <v>15</v>
+      </c>
+      <c r="B16" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="C16" s="42" t="s">
+      <c r="C16" s="39" t="s">
         <v>327</v>
       </c>
-      <c r="D16" s="42" t="s">
+      <c r="D16" s="39" t="s">
         <v>321</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="39" t="s">
         <v>316</v>
       </c>
-      <c r="F16" s="33">
+      <c r="F16" s="5">
         <v>2022</v>
       </c>
-      <c r="G16" s="41" t="s">
+      <c r="G16" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="41" t="s">
+      <c r="H16" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="30" customHeight="1">
-      <c r="A17" s="33">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="39" t="s">
         <v>329</v>
       </c>
-      <c r="C17" s="42" t="s">
+      <c r="C17" s="39" t="s">
         <v>330</v>
       </c>
-      <c r="D17" s="38" t="s">
+      <c r="D17" s="41" t="s">
         <v>311</v>
       </c>
-      <c r="E17" s="38" t="s">
+      <c r="E17" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="F17" s="33">
+      <c r="F17" s="5">
         <v>2022</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H17" s="33" t="s">
+      <c r="H17" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1">
-      <c r="A18" s="34">
+      <c r="A18" s="36">
         <v>17</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="41" t="s">
         <v>332</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="41" t="s">
         <v>331</v>
       </c>
-      <c r="D18" s="38" t="s">
+      <c r="D18" s="41" t="s">
         <v>333</v>
       </c>
-      <c r="E18" s="38" t="s">
+      <c r="E18" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="F18" s="33">
+      <c r="F18" s="5">
         <v>2022</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H18" s="33" t="s">
+      <c r="H18" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1">
-      <c r="A19" s="33">
+      <c r="A19" s="42">
         <v>18</v>
       </c>
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="43" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="38" t="s">
+      <c r="C19" s="43" t="s">
         <v>335</v>
       </c>
-      <c r="D19" s="38" t="s">
+      <c r="D19" s="43" t="s">
         <v>321</v>
       </c>
-      <c r="E19" s="38" t="s">
+      <c r="E19" s="43" t="s">
         <v>316</v>
       </c>
-      <c r="F19" s="33">
+      <c r="F19" s="42">
         <v>2023</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="33" t="s">
+      <c r="H19" s="42" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1">
-      <c r="A20" s="34">
+      <c r="A20" s="36">
         <v>19</v>
       </c>
-      <c r="B20" s="38" t="s">
+      <c r="B20" s="41" t="s">
         <v>336</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="41" t="s">
         <v>337</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="E20" s="38" t="s">
+      <c r="E20" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="5">
         <v>2023</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H20" s="33" t="s">
+      <c r="H20" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="30" customHeight="1">
-      <c r="A21" s="33">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="41" t="s">
         <v>339</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="41" t="s">
         <v>338</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="41" t="s">
         <v>311</v>
       </c>
-      <c r="E21" s="38" t="s">
+      <c r="E21" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="F21" s="33">
+      <c r="F21" s="5">
         <v>2023</v>
       </c>
-      <c r="G21" s="33" t="s">
+      <c r="G21" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="33" t="s">
+      <c r="H21" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1">
-      <c r="A22" s="34">
+      <c r="A22" s="36">
         <v>21</v>
       </c>
-      <c r="B22" s="38" t="s">
+      <c r="B22" s="41" t="s">
         <v>348</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="41" t="s">
         <v>347</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="41" t="s">
         <v>311</v>
       </c>
-      <c r="E22" s="38" t="s">
+      <c r="E22" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="F22" s="33">
+      <c r="F22" s="5">
         <v>2023</v>
       </c>
-      <c r="G22" s="33" t="s">
+      <c r="G22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H22" s="33" t="s">
+      <c r="H22" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="30" customHeight="1">
-      <c r="A23" s="33">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="38" t="s">
+      <c r="B23" s="41" t="s">
         <v>341</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="41" t="s">
         <v>340</v>
       </c>
-      <c r="D23" s="38" t="s">
+      <c r="D23" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="E23" s="38" t="s">
+      <c r="E23" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="F23" s="33">
+      <c r="F23" s="5">
         <v>2023</v>
       </c>
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H23" s="33" t="s">
+      <c r="H23" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1">
-      <c r="A24" s="34">
+      <c r="A24" s="36">
         <v>23</v>
       </c>
-      <c r="B24" s="38" t="s">
+      <c r="B24" s="41" t="s">
         <v>342</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="41" t="s">
         <v>343</v>
       </c>
-      <c r="D24" s="38" t="s">
+      <c r="D24" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="E24" s="38" t="s">
+      <c r="E24" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="F24" s="33">
+      <c r="F24" s="5">
         <v>2023</v>
       </c>
-      <c r="G24" s="33" t="s">
+      <c r="G24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H24" s="33" t="s">
+      <c r="H24" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="30" customHeight="1">
-      <c r="A25" s="33">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="38" t="s">
+      <c r="B25" s="41" t="s">
         <v>344</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="41" t="s">
         <v>345</v>
       </c>
-      <c r="D25" s="38" t="s">
+      <c r="D25" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="E25" s="38" t="s">
+      <c r="E25" s="41" t="s">
         <v>316</v>
       </c>
-      <c r="F25" s="33">
+      <c r="F25" s="5">
         <v>2023</v>
       </c>
-      <c r="G25" s="33" t="s">
+      <c r="G25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H25" s="33" t="s">
+      <c r="H25" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1">
-      <c r="A26" s="34">
+      <c r="A26" s="36">
         <v>25</v>
       </c>
-      <c r="B26" s="38" t="s">
+      <c r="B26" s="41" t="s">
         <v>350</v>
       </c>
-      <c r="C26" s="38" t="s">
+      <c r="C26" s="41" t="s">
         <v>351</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="41" t="s">
         <v>321</v>
       </c>
-      <c r="E26" s="36" t="s">
+      <c r="E26" s="8" t="s">
         <v>352</v>
       </c>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G26" s="33" t="s">
+      <c r="G26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H26" s="33" t="s">
+      <c r="H26" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1">
-      <c r="A27" s="33">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="38" t="s">
+      <c r="B27" s="41" t="s">
         <v>353</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="41" t="s">
         <v>330</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="41" t="s">
         <v>311</v>
       </c>
-      <c r="E27" s="38" t="s">
+      <c r="E27" s="41" t="s">
         <v>354</v>
       </c>
-      <c r="F27" s="33" t="s">
+      <c r="F27" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="G27" s="33" t="s">
+      <c r="G27" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H27" s="33" t="s">
+      <c r="H27" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1">
-      <c r="A28" s="34">
+      <c r="A28" s="36">
         <v>27</v>
       </c>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="39" t="s">
         <v>392</v>
       </c>
-      <c r="C28" s="42" t="s">
+      <c r="C28" s="39" t="s">
         <v>393</v>
       </c>
-      <c r="D28" s="42" t="s">
+      <c r="D28" s="39" t="s">
         <v>394</v>
       </c>
-      <c r="E28" s="42" t="s">
+      <c r="E28" s="39" t="s">
         <v>395</v>
       </c>
-      <c r="F28" s="41" t="s">
+      <c r="F28" s="40" t="s">
         <v>349</v>
       </c>
-      <c r="G28" s="41" t="s">
+      <c r="G28" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="H28" s="41" t="s">
+      <c r="H28" s="40" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="30" customHeight="1">
-      <c r="A29" s="33">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="38" t="s">
+      <c r="B29" s="41" t="s">
         <v>357</v>
       </c>
-      <c r="C29" s="38" t="s">
+      <c r="C29" s="41" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="D29" s="41" t="s">
         <v>359</v>
       </c>
-      <c r="E29" s="36" t="s">
+      <c r="E29" s="8" t="s">
         <v>360</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="5">
         <v>2024</v>
       </c>
-      <c r="G29" s="33" t="s">
+      <c r="G29" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H29" s="33" t="s">
+      <c r="H29" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="30" customHeight="1">
-      <c r="A30" s="34">
+      <c r="A30" s="36">
         <v>29</v>
       </c>
-      <c r="B30" s="38" t="s">
+      <c r="B30" s="41" t="s">
         <v>362</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="41" t="s">
         <v>361</v>
       </c>
-      <c r="D30" s="38" t="s">
+      <c r="D30" s="41" t="s">
         <v>363</v>
       </c>
-      <c r="E30" s="36" t="s">
+      <c r="E30" s="8" t="s">
         <v>364</v>
       </c>
-      <c r="F30" s="33">
+      <c r="F30" s="5">
         <v>2025</v>
       </c>
-      <c r="G30" s="33" t="s">
+      <c r="G30" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="33" t="s">
+      <c r="H30" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1">
-      <c r="A31" s="44">
+      <c r="A31" s="36">
         <v>30</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="41" t="s">
         <v>365</v>
       </c>
-      <c r="C31" s="45" t="s">
+      <c r="C31" s="41" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="45" t="s">
+      <c r="D31" s="41" t="s">
         <v>366</v>
       </c>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="F31" s="47">
+      <c r="F31" s="5">
         <v>2025</v>
       </c>
-      <c r="G31" s="47" t="s">
+      <c r="G31" s="5">
+        <v>2026</v>
+      </c>
+      <c r="H31" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="47" t="s">
+    </row>
+    <row r="32" spans="1:8" ht="30" customHeight="1">
+      <c r="A32" s="5">
+        <v>31</v>
+      </c>
+      <c r="B32" s="41" t="s">
+        <v>369</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>368</v>
+      </c>
+      <c r="D32" s="41" t="s">
+        <v>346</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="F32" s="5">
+        <v>2026</v>
+      </c>
+      <c r="G32" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1">
-      <c r="A32" s="33">
-        <v>31</v>
-      </c>
-      <c r="B32" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="C32" s="38" t="s">
-        <v>368</v>
-      </c>
-      <c r="D32" s="38" t="s">
+      <c r="H32" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="30" customHeight="1">
+      <c r="A33" s="36">
+        <v>32</v>
+      </c>
+      <c r="B33" s="41" t="s">
+        <v>373</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>372</v>
+      </c>
+      <c r="D33" s="41" t="s">
         <v>346</v>
       </c>
-      <c r="E32" s="36" t="s">
-        <v>370</v>
-      </c>
-      <c r="F32" s="33">
-        <v>2026</v>
-      </c>
-      <c r="G32" s="33" t="s">
-        <v>10</v>
-      </c>
-      <c r="H32" s="33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1">
-      <c r="A33" s="33">
-        <v>32</v>
-      </c>
-      <c r="B33" s="42" t="s">
-        <v>373</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>372</v>
-      </c>
-      <c r="D33" s="42" t="s">
+      <c r="E33" s="8"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8" ht="30" customHeight="1">
+      <c r="A34" s="5">
+        <v>33</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>375</v>
+      </c>
+      <c r="D34" s="41" t="s">
+        <v>376</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8" ht="30" customHeight="1">
+      <c r="A35" s="5">
+        <v>34</v>
+      </c>
+      <c r="B35" s="39" t="s">
+        <v>378</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>377</v>
+      </c>
+      <c r="D35" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="E33" s="38"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-    </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1">
-      <c r="A34" s="33">
-        <v>33</v>
-      </c>
-      <c r="B34" s="43" t="s">
-        <v>374</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>375</v>
-      </c>
-      <c r="D34" s="42" t="s">
-        <v>376</v>
-      </c>
-      <c r="E34" s="38"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="33"/>
-      <c r="H34" s="33"/>
-    </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1">
-      <c r="A35" s="33">
-        <v>34</v>
-      </c>
-      <c r="B35" s="42" t="s">
-        <v>378</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>377</v>
-      </c>
-      <c r="D35" s="42" t="s">
+      <c r="E35" s="44"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+    </row>
+    <row r="36" spans="1:8" ht="30" customHeight="1">
+      <c r="A36" s="5">
+        <v>35</v>
+      </c>
+      <c r="B36" s="39" t="s">
+        <v>379</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>318</v>
+      </c>
+      <c r="D36" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="E35" s="37"/>
-      <c r="F35"/>
-      <c r="G35"/>
-      <c r="H35"/>
-    </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1">
-      <c r="A36" s="33">
-        <v>35</v>
-      </c>
-      <c r="B36" s="42" t="s">
-        <v>379</v>
-      </c>
-      <c r="C36" s="42" t="s">
+      <c r="E36" s="45"/>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+    </row>
+    <row r="37" spans="1:8" ht="30" customHeight="1">
+      <c r="A37" s="5">
+        <v>36</v>
+      </c>
+      <c r="B37" s="39" t="s">
+        <v>380</v>
+      </c>
+      <c r="C37" s="39" t="s">
         <v>318</v>
       </c>
-      <c r="D36" s="42" t="s">
+      <c r="D37" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-    </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1">
-      <c r="A37" s="33">
-        <v>36</v>
-      </c>
-      <c r="B37" s="42" t="s">
-        <v>380</v>
-      </c>
-      <c r="C37" s="42" t="s">
-        <v>318</v>
-      </c>
-      <c r="D37" s="42" t="s">
+      <c r="E37" s="45"/>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+    </row>
+    <row r="38" spans="1:8" ht="30" customHeight="1">
+      <c r="A38" s="5">
+        <v>37</v>
+      </c>
+      <c r="B38" s="39" t="s">
+        <v>381</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>382</v>
+      </c>
+      <c r="D38" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
-    </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1">
-      <c r="A38" s="33">
-        <v>37</v>
-      </c>
-      <c r="B38" s="42" t="s">
-        <v>381</v>
-      </c>
-      <c r="C38" s="42" t="s">
+      <c r="E38" s="45"/>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+    </row>
+    <row r="39" spans="1:8" ht="30" customHeight="1">
+      <c r="A39" s="5">
+        <v>38</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>383</v>
+      </c>
+      <c r="C39" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="D38" s="42" t="s">
+      <c r="D39" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="E38"/>
-      <c r="F38"/>
-      <c r="G38"/>
-      <c r="H38"/>
-    </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1">
-      <c r="A39" s="33">
-        <v>38</v>
-      </c>
-      <c r="B39" s="42" t="s">
-        <v>383</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>382</v>
-      </c>
-      <c r="D39" s="42" t="s">
+      <c r="E39" s="45"/>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+    </row>
+    <row r="40" spans="1:8" ht="30" customHeight="1">
+      <c r="A40" s="5">
+        <v>39</v>
+      </c>
+      <c r="B40" s="39" t="s">
+        <v>384</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>385</v>
+      </c>
+      <c r="D40" s="39" t="s">
         <v>346</v>
       </c>
-      <c r="E39"/>
-      <c r="F39"/>
-      <c r="G39"/>
-      <c r="H39"/>
-    </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1">
-      <c r="A40" s="33">
-        <v>39</v>
-      </c>
-      <c r="B40" s="42" t="s">
-        <v>384</v>
-      </c>
-      <c r="C40" s="42" t="s">
-        <v>385</v>
-      </c>
-      <c r="D40" s="42" t="s">
-        <v>346</v>
-      </c>
-      <c r="E40"/>
-      <c r="F40"/>
-      <c r="G40"/>
-      <c r="H40"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1">
-      <c r="A41" s="33">
+      <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="42" t="s">
+      <c r="B41" s="39" t="s">
         <v>387</v>
       </c>
-      <c r="C41" s="42" t="s">
+      <c r="C41" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D41" s="42" t="s">
+      <c r="D41" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="E41"/>
-      <c r="F41"/>
-      <c r="G41"/>
-      <c r="H41"/>
+      <c r="E41" s="45"/>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1">
-      <c r="A42" s="33">
+      <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="42" t="s">
+      <c r="B42" s="39" t="s">
         <v>388</v>
       </c>
-      <c r="C42" s="42" t="s">
+      <c r="C42" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D42" s="42" t="s">
+      <c r="D42" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="E42"/>
-      <c r="F42"/>
-      <c r="G42"/>
-      <c r="H42"/>
+      <c r="E42" s="45"/>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
     </row>
     <row r="43" spans="1:8" ht="30" customHeight="1">
-      <c r="A43" s="33">
+      <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="42" t="s">
+      <c r="B43" s="39" t="s">
         <v>389</v>
       </c>
-      <c r="C43" s="42" t="s">
+      <c r="C43" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D43" s="42" t="s">
+      <c r="D43" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="E43"/>
-      <c r="F43"/>
-      <c r="G43"/>
-      <c r="H43"/>
+      <c r="E43" s="45"/>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
     </row>
     <row r="44" spans="1:8" ht="30" customHeight="1">
-      <c r="A44" s="33">
+      <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="42" t="s">
+      <c r="B44" s="39" t="s">
         <v>390</v>
       </c>
-      <c r="C44" s="42" t="s">
+      <c r="C44" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D44" s="42" t="s">
+      <c r="D44" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="E44"/>
-      <c r="F44"/>
-      <c r="G44"/>
-      <c r="H44"/>
+      <c r="E44" s="45"/>
+      <c r="F44" s="45"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="45"/>
     </row>
     <row r="45" spans="1:8" ht="30" customHeight="1">
-      <c r="A45" s="33">
+      <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="42" t="s">
+      <c r="B45" s="39" t="s">
         <v>391</v>
       </c>
-      <c r="C45" s="42" t="s">
+      <c r="C45" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D45" s="42" t="s">
+      <c r="D45" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="E45"/>
-      <c r="F45"/>
-      <c r="G45"/>
-      <c r="H45"/>
+      <c r="E45" s="45"/>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1">
-      <c r="A46" s="33">
+      <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="42" t="s">
+      <c r="B46" s="39" t="s">
         <v>396</v>
       </c>
-      <c r="C46" s="42" t="s">
+      <c r="C46" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D46" s="42" t="s">
+      <c r="D46" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="E46"/>
-      <c r="F46"/>
-      <c r="G46"/>
-      <c r="H46"/>
+      <c r="E46" s="45"/>
+      <c r="F46" s="45"/>
+      <c r="G46" s="45"/>
+      <c r="H46" s="45"/>
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1">
-      <c r="A47" s="33">
+      <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="42" t="s">
+      <c r="B47" s="39" t="s">
         <v>397</v>
       </c>
-      <c r="C47" s="42" t="s">
+      <c r="C47" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D47" s="42" t="s">
+      <c r="D47" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="E47"/>
-      <c r="F47"/>
-      <c r="G47"/>
-      <c r="H47"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
     </row>
     <row r="48" spans="1:8" ht="30" customHeight="1">
-      <c r="A48" s="33">
+      <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="42" t="s">
+      <c r="B48" s="39" t="s">
         <v>257</v>
       </c>
-      <c r="C48" s="42" t="s">
+      <c r="C48" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D48" s="42" t="s">
+      <c r="D48" s="39" t="s">
         <v>386</v>
       </c>
-      <c r="E48"/>
-      <c r="F48"/>
-      <c r="G48"/>
-      <c r="H48"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1">
-      <c r="A49" s="33">
+      <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="42" t="s">
+      <c r="B49" s="39" t="s">
         <v>398</v>
       </c>
-      <c r="C49" s="42" t="s">
+      <c r="C49" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D49" s="42" t="s">
+      <c r="D49" s="39" t="s">
         <v>399</v>
       </c>
-      <c r="E49"/>
-      <c r="F49"/>
-      <c r="G49"/>
-      <c r="H49"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="45"/>
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1">
-      <c r="A50" s="33">
+      <c r="A50" s="5">
         <v>49</v>
       </c>
-      <c r="B50" s="42" t="s">
+      <c r="B50" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="42" t="s">
+      <c r="C50" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D50" s="42" t="s">
+      <c r="D50" s="39" t="s">
         <v>399</v>
       </c>
-      <c r="E50"/>
-      <c r="F50"/>
-      <c r="G50"/>
-      <c r="H50"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="45"/>
+      <c r="H50" s="45"/>
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1">
-      <c r="A51" s="33">
+      <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="42" t="s">
+      <c r="B51" s="39" t="s">
         <v>400</v>
       </c>
-      <c r="C51" s="42" t="s">
+      <c r="C51" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="D51" s="42" t="s">
+      <c r="D51" s="39" t="s">
         <v>399</v>
       </c>
-      <c r="E51"/>
-      <c r="F51"/>
-      <c r="G51"/>
-      <c r="H51"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="45"/>
+      <c r="H51" s="45"/>
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1">
-      <c r="A52" s="33">
+      <c r="A52" s="5">
         <v>51</v>
       </c>
-      <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52"/>
-      <c r="G52"/>
-      <c r="H52"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="45"/>
+      <c r="D52" s="45"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="45"/>
+      <c r="G52" s="45"/>
+      <c r="H52" s="45"/>
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1">
-      <c r="A53" s="33">
+      <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53"/>
-      <c r="G53"/>
-      <c r="H53"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="45"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="45"/>
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1">
-      <c r="A54" s="33">
+      <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
+      <c r="B54" s="45"/>
+      <c r="C54" s="45"/>
+      <c r="D54" s="45"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="45"/>
+      <c r="G54" s="45"/>
+      <c r="H54" s="45"/>
     </row>
     <row r="55" spans="1:8" ht="30" customHeight="1">
-      <c r="A55" s="33">
+      <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
+      <c r="B55" s="45"/>
+      <c r="C55" s="45"/>
+      <c r="D55" s="45"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="45"/>
+      <c r="H55" s="45"/>
     </row>
     <row r="56" spans="1:8" ht="30" customHeight="1">
-      <c r="A56" s="33">
+      <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56"/>
-      <c r="C56"/>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
+      <c r="B56" s="45"/>
+      <c r="C56" s="45"/>
+      <c r="D56" s="45"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="45"/>
+      <c r="H56" s="45"/>
     </row>
     <row r="57" spans="1:8" ht="30" customHeight="1">
-      <c r="A57" s="33">
+      <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57"/>
-      <c r="C57"/>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
+      <c r="B57" s="45"/>
+      <c r="C57" s="45"/>
+      <c r="D57" s="45"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="45"/>
+      <c r="G57" s="45"/>
+      <c r="H57" s="45"/>
     </row>
     <row r="58" spans="1:8" ht="30" customHeight="1">
-      <c r="A58" s="33">
+      <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58"/>
-      <c r="C58"/>
-      <c r="D58"/>
-      <c r="E58"/>
-      <c r="F58"/>
-      <c r="G58"/>
-      <c r="H58"/>
+      <c r="B58" s="45"/>
+      <c r="C58" s="45"/>
+      <c r="D58" s="45"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="45"/>
+      <c r="H58" s="45"/>
     </row>
     <row r="59" spans="1:8" ht="30" customHeight="1">
-      <c r="A59" s="33">
+      <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59"/>
-      <c r="C59"/>
-      <c r="D59"/>
-      <c r="E59"/>
-      <c r="F59"/>
-      <c r="G59"/>
-      <c r="H59"/>
+      <c r="B59" s="45"/>
+      <c r="C59" s="45"/>
+      <c r="D59" s="45"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="45"/>
+      <c r="G59" s="45"/>
+      <c r="H59" s="45"/>
     </row>
     <row r="60" spans="1:8" ht="30" customHeight="1">
-      <c r="A60" s="33">
+      <c r="A60" s="5">
         <v>59</v>
       </c>
-      <c r="B60"/>
-      <c r="C60"/>
-      <c r="D60"/>
-      <c r="E60"/>
-      <c r="F60"/>
-      <c r="G60"/>
-      <c r="H60"/>
+      <c r="B60" s="45"/>
+      <c r="C60" s="45"/>
+      <c r="D60" s="45"/>
+      <c r="E60" s="45"/>
+      <c r="F60" s="45"/>
+      <c r="G60" s="45"/>
+      <c r="H60" s="45"/>
     </row>
     <row r="61" spans="1:8" ht="30" customHeight="1">
-      <c r="A61" s="33">
+      <c r="A61" s="5">
         <v>60</v>
       </c>
-      <c r="B61"/>
-      <c r="C61"/>
-      <c r="D61"/>
-      <c r="E61"/>
-      <c r="F61"/>
-      <c r="G61"/>
-      <c r="H61"/>
+      <c r="B61" s="45"/>
+      <c r="C61" s="45"/>
+      <c r="D61" s="45"/>
+      <c r="E61" s="45"/>
+      <c r="F61" s="45"/>
+      <c r="G61" s="45"/>
+      <c r="H61" s="45"/>
     </row>
     <row r="62" spans="1:8" ht="30" customHeight="1">
-      <c r="A62" s="33">
+      <c r="A62" s="5">
         <v>61</v>
       </c>
-      <c r="B62"/>
-      <c r="C62"/>
-      <c r="D62"/>
-      <c r="E62"/>
-      <c r="F62"/>
-      <c r="G62"/>
-      <c r="H62"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="45"/>
+      <c r="H62" s="45"/>
     </row>
     <row r="63" spans="1:8" ht="30" customHeight="1">
-      <c r="A63" s="33">
+      <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63"/>
-      <c r="C63"/>
-      <c r="D63"/>
-      <c r="E63"/>
-      <c r="F63"/>
-      <c r="G63"/>
-      <c r="H63"/>
+      <c r="B63" s="45"/>
+      <c r="C63" s="45"/>
+      <c r="D63" s="45"/>
+      <c r="E63" s="45"/>
+      <c r="F63" s="45"/>
+      <c r="G63" s="45"/>
+      <c r="H63" s="45"/>
     </row>
     <row r="64" spans="1:8" ht="30" customHeight="1">
-      <c r="A64" s="33">
+      <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64"/>
-      <c r="C64"/>
-      <c r="D64"/>
-      <c r="E64"/>
-      <c r="F64"/>
-      <c r="G64"/>
-      <c r="H64"/>
+      <c r="B64" s="45"/>
+      <c r="C64" s="45"/>
+      <c r="D64" s="45"/>
+      <c r="E64" s="45"/>
+      <c r="F64" s="45"/>
+      <c r="G64" s="45"/>
+      <c r="H64" s="45"/>
     </row>
     <row r="65" spans="1:8" ht="30" customHeight="1">
-      <c r="A65" s="33">
+      <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65"/>
-      <c r="C65"/>
-      <c r="D65"/>
-      <c r="E65"/>
-      <c r="F65"/>
-      <c r="G65"/>
-      <c r="H65"/>
+      <c r="B65" s="45"/>
+      <c r="C65" s="45"/>
+      <c r="D65" s="45"/>
+      <c r="E65" s="45"/>
+      <c r="F65" s="45"/>
+      <c r="G65" s="45"/>
+      <c r="H65" s="45"/>
     </row>
     <row r="66" spans="1:8" ht="30" customHeight="1">
-      <c r="A66" s="33">
+      <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66"/>
-      <c r="C66"/>
-      <c r="D66"/>
-      <c r="E66"/>
-      <c r="F66"/>
-      <c r="G66"/>
-      <c r="H66"/>
+      <c r="B66" s="45"/>
+      <c r="C66" s="45"/>
+      <c r="D66" s="45"/>
+      <c r="E66" s="45"/>
+      <c r="F66" s="45"/>
+      <c r="G66" s="45"/>
+      <c r="H66" s="45"/>
     </row>
     <row r="67" spans="1:8" ht="30" customHeight="1">
-      <c r="A67" s="33">
+      <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67"/>
-      <c r="C67"/>
-      <c r="D67"/>
-      <c r="E67"/>
-      <c r="F67"/>
-      <c r="G67"/>
-      <c r="H67"/>
+      <c r="B67" s="45"/>
+      <c r="C67" s="45"/>
+      <c r="D67" s="45"/>
+      <c r="E67" s="45"/>
+      <c r="F67" s="45"/>
+      <c r="G67" s="45"/>
+      <c r="H67" s="45"/>
     </row>
     <row r="68" spans="1:8" ht="30" customHeight="1">
-      <c r="A68" s="33">
+      <c r="A68" s="5">
         <v>67</v>
       </c>
-      <c r="B68"/>
-      <c r="C68"/>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="45"/>
+      <c r="D68" s="45"/>
+      <c r="E68" s="45"/>
+      <c r="F68" s="45"/>
+      <c r="G68" s="45"/>
+      <c r="H68" s="45"/>
     </row>
     <row r="69" spans="1:8" ht="30" customHeight="1">
-      <c r="A69" s="33">
+      <c r="A69" s="5">
         <v>68</v>
       </c>
-      <c r="B69"/>
-      <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
+      <c r="B69" s="45"/>
+      <c r="C69" s="45"/>
+      <c r="D69" s="45"/>
+      <c r="E69" s="45"/>
+      <c r="F69" s="45"/>
+      <c r="G69" s="45"/>
+      <c r="H69" s="45"/>
     </row>
     <row r="70" spans="1:8" ht="30" customHeight="1">
-      <c r="A70" s="33">
+      <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70"/>
-      <c r="C70"/>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
+      <c r="B70" s="45"/>
+      <c r="C70" s="45"/>
+      <c r="D70" s="45"/>
+      <c r="E70" s="45"/>
+      <c r="F70" s="45"/>
+      <c r="G70" s="45"/>
+      <c r="H70" s="45"/>
     </row>
     <row r="71" spans="1:8" ht="30" customHeight="1">
-      <c r="A71" s="33">
+      <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71"/>
-      <c r="C71"/>
-      <c r="D71"/>
-      <c r="E71"/>
-      <c r="F71"/>
-      <c r="G71"/>
-      <c r="H71"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="45"/>
+      <c r="D71" s="45"/>
+      <c r="E71" s="45"/>
+      <c r="F71" s="45"/>
+      <c r="G71" s="45"/>
+      <c r="H71" s="45"/>
     </row>
     <row r="72" spans="1:8" ht="30" customHeight="1">
-      <c r="A72" s="33">
+      <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72"/>
-      <c r="C72"/>
-      <c r="D72"/>
-      <c r="E72"/>
-      <c r="F72"/>
-      <c r="G72"/>
-      <c r="H72"/>
+      <c r="B72" s="45"/>
+      <c r="C72" s="45"/>
+      <c r="D72" s="45"/>
+      <c r="E72" s="45"/>
+      <c r="F72" s="45"/>
+      <c r="G72" s="45"/>
+      <c r="H72" s="45"/>
     </row>
     <row r="73" spans="1:8" ht="30" customHeight="1">
-      <c r="A73" s="33">
+      <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73"/>
-      <c r="C73"/>
-      <c r="D73"/>
-      <c r="E73"/>
-      <c r="F73"/>
-      <c r="G73"/>
-      <c r="H73"/>
+      <c r="B73" s="45"/>
+      <c r="C73" s="45"/>
+      <c r="D73" s="45"/>
+      <c r="E73" s="45"/>
+      <c r="F73" s="45"/>
+      <c r="G73" s="45"/>
+      <c r="H73" s="45"/>
     </row>
     <row r="74" spans="1:8" ht="30" customHeight="1">
-      <c r="A74" s="33">
+      <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74"/>
-      <c r="C74"/>
-      <c r="D74"/>
-      <c r="E74"/>
-      <c r="F74"/>
-      <c r="G74"/>
-      <c r="H74"/>
+      <c r="B74" s="45"/>
+      <c r="C74" s="45"/>
+      <c r="D74" s="45"/>
+      <c r="E74" s="45"/>
+      <c r="F74" s="45"/>
+      <c r="G74" s="45"/>
+      <c r="H74" s="45"/>
     </row>
     <row r="75" spans="1:8" ht="30" customHeight="1">
-      <c r="A75" s="33">
+      <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75"/>
-      <c r="C75"/>
-      <c r="D75"/>
-      <c r="E75"/>
-      <c r="F75"/>
-      <c r="G75"/>
-      <c r="H75"/>
+      <c r="B75" s="45"/>
+      <c r="C75" s="45"/>
+      <c r="D75" s="45"/>
+      <c r="E75" s="45"/>
+      <c r="F75" s="45"/>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
     </row>
     <row r="76" spans="1:8" ht="30" customHeight="1">
-      <c r="A76" s="33">
+      <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76"/>
-      <c r="C76"/>
-      <c r="D76"/>
-      <c r="E76"/>
-      <c r="F76"/>
-      <c r="G76"/>
-      <c r="H76"/>
+      <c r="B76" s="45"/>
+      <c r="C76" s="45"/>
+      <c r="D76" s="45"/>
+      <c r="E76" s="45"/>
+      <c r="F76" s="45"/>
+      <c r="G76" s="45"/>
+      <c r="H76" s="45"/>
     </row>
     <row r="77" spans="1:8" ht="30" customHeight="1">
-      <c r="A77" s="33">
+      <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77"/>
-      <c r="C77"/>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
+      <c r="B77" s="45"/>
+      <c r="C77" s="45"/>
+      <c r="D77" s="45"/>
+      <c r="E77" s="45"/>
+      <c r="F77" s="45"/>
+      <c r="G77" s="45"/>
+      <c r="H77" s="45"/>
     </row>
     <row r="78" spans="1:8" ht="30" customHeight="1">
-      <c r="A78" s="33">
+      <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78"/>
-      <c r="C78"/>
-      <c r="D78"/>
-      <c r="E78"/>
-      <c r="F78"/>
-      <c r="G78"/>
-      <c r="H78"/>
+      <c r="B78" s="45"/>
+      <c r="C78" s="45"/>
+      <c r="D78" s="45"/>
+      <c r="E78" s="45"/>
+      <c r="F78" s="45"/>
+      <c r="G78" s="45"/>
+      <c r="H78" s="45"/>
     </row>
     <row r="79" spans="1:8" ht="30" customHeight="1">
-      <c r="A79" s="33">
+      <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79"/>
-      <c r="C79"/>
-      <c r="D79"/>
-      <c r="E79"/>
-      <c r="F79"/>
-      <c r="G79"/>
-      <c r="H79"/>
+      <c r="B79" s="45"/>
+      <c r="C79" s="45"/>
+      <c r="D79" s="45"/>
+      <c r="E79" s="45"/>
+      <c r="F79" s="45"/>
+      <c r="G79" s="45"/>
+      <c r="H79" s="45"/>
     </row>
     <row r="80" spans="1:8" ht="30" customHeight="1">
-      <c r="A80" s="33">
+      <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80"/>
-      <c r="C80"/>
-      <c r="D80"/>
-      <c r="E80"/>
-      <c r="F80"/>
-      <c r="G80"/>
-      <c r="H80"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="45"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45"/>
     </row>
     <row r="81" spans="1:8" ht="30" customHeight="1">
-      <c r="A81" s="33">
+      <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81"/>
-      <c r="C81"/>
-      <c r="D81"/>
-      <c r="E81"/>
-      <c r="F81"/>
-      <c r="G81"/>
-      <c r="H81"/>
+      <c r="B81" s="45"/>
+      <c r="C81" s="45"/>
+      <c r="D81" s="45"/>
+      <c r="E81" s="45"/>
+      <c r="F81" s="45"/>
+      <c r="G81" s="45"/>
+      <c r="H81" s="45"/>
     </row>
     <row r="82" spans="1:8" ht="30" customHeight="1">
-      <c r="A82" s="33">
+      <c r="A82" s="5">
         <v>81</v>
       </c>
-      <c r="B82"/>
-      <c r="C82"/>
-      <c r="D82"/>
-      <c r="E82"/>
-      <c r="F82"/>
-      <c r="G82"/>
-      <c r="H82"/>
+      <c r="B82" s="45"/>
+      <c r="C82" s="45"/>
+      <c r="D82" s="45"/>
+      <c r="E82" s="45"/>
+      <c r="F82" s="45"/>
+      <c r="G82" s="45"/>
+      <c r="H82" s="45"/>
     </row>
     <row r="83" spans="1:8" ht="30" customHeight="1">
-      <c r="A83" s="33">
+      <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83"/>
-      <c r="C83"/>
-      <c r="D83"/>
-      <c r="E83"/>
-      <c r="F83"/>
-      <c r="G83"/>
-      <c r="H83"/>
+      <c r="B83" s="45"/>
+      <c r="C83" s="45"/>
+      <c r="D83" s="45"/>
+      <c r="E83" s="45"/>
+      <c r="F83" s="45"/>
+      <c r="G83" s="45"/>
+      <c r="H83" s="45"/>
     </row>
     <row r="84" spans="1:8" ht="30" customHeight="1">
-      <c r="A84" s="33">
+      <c r="A84" s="5">
         <v>83</v>
       </c>
-      <c r="B84"/>
-      <c r="C84"/>
-      <c r="D84"/>
-      <c r="E84"/>
-      <c r="F84"/>
-      <c r="G84"/>
-      <c r="H84"/>
+      <c r="B84" s="45"/>
+      <c r="C84" s="45"/>
+      <c r="D84" s="45"/>
+      <c r="E84" s="45"/>
+      <c r="F84" s="45"/>
+      <c r="G84" s="45"/>
+      <c r="H84" s="45"/>
     </row>
     <row r="85" spans="1:8" ht="30" customHeight="1">
-      <c r="A85" s="33">
+      <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85"/>
-      <c r="C85"/>
-      <c r="D85"/>
-      <c r="E85"/>
-      <c r="F85"/>
-      <c r="G85"/>
-      <c r="H85"/>
+      <c r="B85" s="45"/>
+      <c r="C85" s="45"/>
+      <c r="D85" s="45"/>
+      <c r="E85" s="45"/>
+      <c r="F85" s="45"/>
+      <c r="G85" s="45"/>
+      <c r="H85" s="45"/>
     </row>
     <row r="86" spans="1:8" ht="30" customHeight="1">
-      <c r="A86" s="33">
+      <c r="A86" s="5">
         <v>85</v>
       </c>
-      <c r="B86"/>
-      <c r="C86"/>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
+      <c r="B86" s="45"/>
+      <c r="C86" s="45"/>
+      <c r="D86" s="45"/>
+      <c r="E86" s="45"/>
+      <c r="F86" s="45"/>
+      <c r="G86" s="45"/>
+      <c r="H86" s="45"/>
     </row>
     <row r="87" spans="1:8" ht="30" customHeight="1">
-      <c r="A87" s="33">
+      <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87"/>
-      <c r="C87"/>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
+      <c r="B87" s="45"/>
+      <c r="C87" s="45"/>
+      <c r="D87" s="45"/>
+      <c r="E87" s="45"/>
+      <c r="F87" s="45"/>
+      <c r="G87" s="45"/>
+      <c r="H87" s="45"/>
     </row>
     <row r="88" spans="1:8" ht="30" customHeight="1">
-      <c r="A88" s="33">
+      <c r="A88" s="5">
         <v>87</v>
       </c>
-      <c r="B88"/>
-      <c r="C88"/>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
+      <c r="B88" s="45"/>
+      <c r="C88" s="45"/>
+      <c r="D88" s="45"/>
+      <c r="E88" s="45"/>
+      <c r="F88" s="45"/>
+      <c r="G88" s="45"/>
+      <c r="H88" s="45"/>
     </row>
     <row r="89" spans="1:8" ht="30" customHeight="1">
-      <c r="A89" s="33">
+      <c r="A89" s="5">
         <v>88</v>
       </c>
-      <c r="B89"/>
-      <c r="C89"/>
-      <c r="D89"/>
-      <c r="E89"/>
-      <c r="F89"/>
-      <c r="G89"/>
-      <c r="H89"/>
+      <c r="B89" s="45"/>
+      <c r="C89" s="45"/>
+      <c r="D89" s="45"/>
+      <c r="E89" s="45"/>
+      <c r="F89" s="45"/>
+      <c r="G89" s="45"/>
+      <c r="H89" s="45"/>
     </row>
     <row r="90" spans="1:8" ht="30" customHeight="1">
-      <c r="A90" s="33">
+      <c r="A90" s="5">
         <v>89</v>
       </c>
-      <c r="B90"/>
-      <c r="C90"/>
-      <c r="D90"/>
-      <c r="E90"/>
-      <c r="F90"/>
-      <c r="G90"/>
-      <c r="H90"/>
+      <c r="B90" s="45"/>
+      <c r="C90" s="45"/>
+      <c r="D90" s="45"/>
+      <c r="E90" s="45"/>
+      <c r="F90" s="45"/>
+      <c r="G90" s="45"/>
+      <c r="H90" s="45"/>
     </row>
     <row r="91" spans="1:8" ht="30" customHeight="1">
-      <c r="A91" s="33">
+      <c r="A91" s="5">
         <v>90</v>
       </c>
-      <c r="B91"/>
-      <c r="C91"/>
-      <c r="D91"/>
-      <c r="E91"/>
-      <c r="F91"/>
-      <c r="G91"/>
-      <c r="H91"/>
+      <c r="B91" s="45"/>
+      <c r="C91" s="45"/>
+      <c r="D91" s="45"/>
+      <c r="E91" s="45"/>
+      <c r="F91" s="45"/>
+      <c r="G91" s="45"/>
+      <c r="H91" s="45"/>
     </row>
     <row r="92" spans="1:8" ht="30" customHeight="1">
-      <c r="A92" s="33">
+      <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92"/>
-      <c r="C92"/>
-      <c r="D92"/>
-      <c r="E92"/>
-      <c r="F92"/>
-      <c r="G92"/>
-      <c r="H92"/>
+      <c r="B92" s="45"/>
+      <c r="C92" s="45"/>
+      <c r="D92" s="45"/>
+      <c r="E92" s="45"/>
+      <c r="F92" s="45"/>
+      <c r="G92" s="45"/>
+      <c r="H92" s="45"/>
     </row>
     <row r="93" spans="1:8" ht="30" customHeight="1">
-      <c r="A93" s="33">
+      <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93"/>
-      <c r="C93"/>
-      <c r="D93"/>
-      <c r="E93"/>
-      <c r="F93"/>
-      <c r="G93"/>
-      <c r="H93"/>
+      <c r="B93" s="45"/>
+      <c r="C93" s="45"/>
+      <c r="D93" s="45"/>
+      <c r="E93" s="45"/>
+      <c r="F93" s="45"/>
+      <c r="G93" s="45"/>
+      <c r="H93" s="45"/>
     </row>
     <row r="94" spans="1:8" ht="30" customHeight="1">
-      <c r="A94" s="33">
+      <c r="A94" s="5">
         <v>93</v>
       </c>
-      <c r="B94"/>
-      <c r="C94"/>
-      <c r="D94"/>
-      <c r="E94"/>
-      <c r="F94"/>
-      <c r="G94"/>
-      <c r="H94"/>
+      <c r="B94" s="45"/>
+      <c r="C94" s="45"/>
+      <c r="D94" s="45"/>
+      <c r="E94" s="45"/>
+      <c r="F94" s="45"/>
+      <c r="G94" s="45"/>
+      <c r="H94" s="45"/>
     </row>
     <row r="95" spans="1:8" ht="30" customHeight="1">
-      <c r="A95" s="33">
+      <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="B95"/>
-      <c r="C95"/>
-      <c r="D95"/>
-      <c r="E95"/>
-      <c r="F95"/>
-      <c r="G95"/>
-      <c r="H95"/>
+      <c r="B95" s="45"/>
+      <c r="C95" s="45"/>
+      <c r="D95" s="45"/>
+      <c r="E95" s="45"/>
+      <c r="F95" s="45"/>
+      <c r="G95" s="45"/>
+      <c r="H95" s="45"/>
     </row>
     <row r="96" spans="1:8" ht="30" customHeight="1">
-      <c r="A96" s="33">
+      <c r="A96" s="5">
         <v>95</v>
       </c>
-      <c r="B96"/>
-      <c r="C96"/>
-      <c r="D96"/>
-      <c r="E96"/>
-      <c r="F96"/>
-      <c r="G96"/>
-      <c r="H96"/>
+      <c r="B96" s="45"/>
+      <c r="C96" s="45"/>
+      <c r="D96" s="45"/>
+      <c r="E96" s="45"/>
+      <c r="F96" s="45"/>
+      <c r="G96" s="45"/>
+      <c r="H96" s="45"/>
     </row>
     <row r="97" spans="1:8" ht="30" customHeight="1">
-      <c r="A97" s="33">
+      <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97"/>
-      <c r="C97"/>
-      <c r="D97"/>
-      <c r="E97"/>
-      <c r="F97"/>
-      <c r="G97"/>
-      <c r="H97"/>
+      <c r="B97" s="45"/>
+      <c r="C97" s="45"/>
+      <c r="D97" s="45"/>
+      <c r="E97" s="45"/>
+      <c r="F97" s="45"/>
+      <c r="G97" s="45"/>
+      <c r="H97" s="45"/>
     </row>
     <row r="98" spans="1:8" ht="30" customHeight="1">
-      <c r="A98" s="33">
+      <c r="A98" s="5">
         <v>97</v>
       </c>
-      <c r="B98"/>
-      <c r="C98"/>
-      <c r="D98"/>
-      <c r="E98"/>
-      <c r="F98"/>
-      <c r="G98"/>
-      <c r="H98"/>
+      <c r="B98" s="45"/>
+      <c r="C98" s="45"/>
+      <c r="D98" s="45"/>
+      <c r="E98" s="45"/>
+      <c r="F98" s="45"/>
+      <c r="G98" s="45"/>
+      <c r="H98" s="45"/>
     </row>
     <row r="99" spans="1:8" ht="30" customHeight="1">
-      <c r="A99" s="33">
+      <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99"/>
-      <c r="C99"/>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
-      <c r="G99"/>
-      <c r="H99"/>
+      <c r="B99" s="45"/>
+      <c r="C99" s="45"/>
+      <c r="D99" s="45"/>
+      <c r="E99" s="45"/>
+      <c r="F99" s="45"/>
+      <c r="G99" s="45"/>
+      <c r="H99" s="45"/>
     </row>
     <row r="100" spans="1:8" ht="30" customHeight="1">
-      <c r="A100" s="33">
+      <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100"/>
-      <c r="C100"/>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
-      <c r="G100"/>
-      <c r="H100"/>
+      <c r="B100" s="45"/>
+      <c r="C100" s="45"/>
+      <c r="D100" s="45"/>
+      <c r="E100" s="45"/>
+      <c r="F100" s="45"/>
+      <c r="G100" s="45"/>
+      <c r="H100" s="45"/>
     </row>
     <row r="101" spans="1:8" ht="30" customHeight="1">
-      <c r="A101" s="33">
+      <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101"/>
-      <c r="C101"/>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
+      <c r="B101" s="45"/>
+      <c r="C101" s="45"/>
+      <c r="D101" s="45"/>
+      <c r="E101" s="45"/>
+      <c r="F101" s="45"/>
+      <c r="G101" s="45"/>
+      <c r="H101" s="45"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H101"/>
   <hyperlinks>
     <hyperlink ref="C11" r:id="rId1" display="https://yandex.ru/search/?srm=1&amp;text=%D0%AD%D1%80%D0%B8%D1%85%20%D0%9C%D0%B0%D1%80%D0%B8%D1%8F%20%D0%A0%D0%B5%D0%BC%D0%B0%D1%80%D0%BA&amp;lr=14&amp;clid=2270455&amp;win=687&amp;primary_reqid=1786517055526639-14999433768309566645-balancer-l7leveler-kubr-yp-klg-171-BAL&amp;noreask=1&amp;ento=0oCghydXcyMzA3MhgCKglydXcyMzEzNDdqF9Ci0YDQuCDRgtC-0LLQsNGA0LjRidCwcgrQkNCy0YLQvtGAyYrrdg"/>
   </hyperlinks>

--- a/Другое/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/Кино-Книги-Одежда-Спорт.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="408">
   <si>
     <t>№</t>
   </si>
@@ -1246,6 +1246,31 @@
   </si>
   <si>
     <t>Мизери</t>
+  </si>
+  <si>
+    <t>Бег</t>
+  </si>
+  <si>
+    <t>25 мин 10км/ч</t>
+  </si>
+  <si>
+    <t>Сб</t>
+  </si>
+  <si>
+    <t>Отжимания на отжималках 3 по 12</t>
+  </si>
+  <si>
+    <t>25 кг - 2 по 10
+20 кг - 10</t>
+  </si>
+  <si>
+    <t>Армейский жим
+30 кг 2 по 10
+25 кг 10</t>
+  </si>
+  <si>
+    <t>70 кг - 10 раз
+80 кг - 2 по 10</t>
   </si>
 </sst>
 </file>
@@ -1422,7 +1447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1439,9 +1464,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1864,4774 +1886,4774 @@
   <dimension ref="A1:I222"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="9"/>
-    <col min="2" max="2" width="24.85546875" style="9" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="9" customWidth="1"/>
-    <col min="4" max="4" width="43.28515625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="9" customWidth="1"/>
-    <col min="7" max="8" width="14.85546875" style="9" customWidth="1"/>
-    <col min="9" max="9" width="16.28515625" style="9" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="9.140625" style="8"/>
+    <col min="2" max="2" width="24.85546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="22.140625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="43.28515625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="8" customWidth="1"/>
+    <col min="6" max="6" width="16.42578125" style="8" customWidth="1"/>
+    <col min="7" max="8" width="14.85546875" style="8" customWidth="1"/>
+    <col min="9" max="9" width="16.28515625" style="8" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11">
+      <c r="A2" s="10">
         <v>6</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="11">
+      <c r="E2" s="10">
         <v>1938</v>
       </c>
-      <c r="F2" s="13">
+      <c r="F2" s="12">
         <v>7.7</v>
       </c>
-      <c r="G2" s="12"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="14"/>
+      <c r="G2" s="11"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="13"/>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="11">
+      <c r="A3" s="10">
         <v>7</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="10">
         <v>1940</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="12">
         <v>7.8</v>
       </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="14"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="13"/>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="11">
+      <c r="A4" s="10">
         <v>8</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="10">
         <v>1946</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="12">
         <v>7.4</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="14"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="13"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="11">
+      <c r="A5" s="10">
         <v>3</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="10">
         <v>1954</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>8</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H5" s="11">
+      <c r="G5" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="10">
         <v>7</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="14">
         <v>46187</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="11">
+      <c r="A6" s="10">
         <v>5</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="10">
         <v>1954</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="12">
         <v>8.1</v>
       </c>
-      <c r="G6" s="12"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="14"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="13"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="11">
+      <c r="A7" s="10">
         <v>11</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="10">
         <v>1954</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>8</v>
       </c>
-      <c r="G7" s="12"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="14"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="11">
+      <c r="A8" s="10">
         <v>9</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="10">
         <v>1957</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="12">
         <v>8</v>
       </c>
-      <c r="G8" s="12"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="14"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10"/>
+      <c r="I8" s="13"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="11">
+      <c r="A9" s="10">
         <v>12</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="10">
         <v>1957</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <v>8</v>
       </c>
-      <c r="G9" s="12"/>
-      <c r="H9" s="11"/>
-      <c r="I9" s="14"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="11">
-        <v>15</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="10">
+        <v>15</v>
+      </c>
+      <c r="B10" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="10">
         <v>1957</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <v>8.1</v>
       </c>
-      <c r="G10" s="12"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="14"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="11">
+      <c r="A11" s="10">
         <v>4</v>
       </c>
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="12" t="s">
+      <c r="C11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="10">
         <v>1958</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="12">
         <v>7.9</v>
       </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="11"/>
-      <c r="I11" s="14"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="13"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="11">
+      <c r="A12" s="10">
         <v>1</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="10">
         <v>1960</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="12">
         <v>8.1</v>
       </c>
-      <c r="G12" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="11">
+      <c r="G12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="10">
         <v>8</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="14">
         <v>46184</v>
       </c>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="11">
+      <c r="A13" s="10">
         <v>13</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="10">
         <v>1960</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="10">
         <v>7.9</v>
       </c>
-      <c r="G13" s="12"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="14"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="11">
+      <c r="A14" s="10">
         <v>2</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="10">
         <v>1963</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>7.5</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="14"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="13"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="11">
+      <c r="A15" s="10">
         <v>14</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="10">
         <v>1963</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="10">
         <v>8</v>
       </c>
-      <c r="G15" s="12"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="14"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="13"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="11">
+      <c r="A16" s="10">
         <v>16</v>
       </c>
-      <c r="B16" s="12" t="s">
+      <c r="B16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="10">
         <v>1964</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <v>8</v>
       </c>
-      <c r="G16" s="12"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="14"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="11">
+      <c r="A17" s="10">
         <v>10</v>
       </c>
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C17" s="12" t="s">
+      <c r="C17" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="10">
         <v>1966</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>7.9</v>
       </c>
-      <c r="G17" s="12"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="14"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="11">
+      <c r="A18" s="10">
         <v>17</v>
       </c>
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="10">
         <v>1968</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <v>7.9</v>
       </c>
-      <c r="G18" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="11">
+      <c r="G18" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="10">
         <v>9</v>
       </c>
-      <c r="I18" s="16">
+      <c r="I18" s="15">
         <v>45931</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="11">
+      <c r="A19" s="10">
         <v>18</v>
       </c>
-      <c r="B19" s="12" t="s">
+      <c r="B19" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="12" t="s">
+      <c r="C19" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="10">
         <v>1971</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="10">
         <v>7.9</v>
       </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="14"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" spans="1:9" ht="29.25">
-      <c r="A20" s="11">
+      <c r="A20" s="10">
         <v>36</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="10">
         <v>1972</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="10">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G20" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="19">
+      <c r="G20" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="18">
         <v>8</v>
       </c>
-      <c r="I20" s="16">
+      <c r="I20" s="15">
         <v>46082</v>
       </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="11">
+      <c r="A21" s="10">
         <v>20</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C21" s="12" t="s">
+      <c r="C21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="10">
         <v>1973</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="10">
         <v>7.1</v>
       </c>
-      <c r="G21" s="12"/>
-      <c r="H21" s="11"/>
-      <c r="I21" s="14"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="13"/>
     </row>
     <row r="22" spans="1:9" ht="29.25">
-      <c r="A22" s="11">
+      <c r="A22" s="10">
         <v>37</v>
       </c>
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="10">
         <v>1974</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="10">
         <v>8.5</v>
       </c>
-      <c r="G22" s="12"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="11">
+      <c r="A23" s="10">
         <v>39</v>
       </c>
-      <c r="B23" s="17" t="s">
+      <c r="B23" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="20"/>
-      <c r="D23" s="17" t="s">
+      <c r="C23" s="19"/>
+      <c r="D23" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="10">
         <v>1974</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="10">
         <v>7.6</v>
       </c>
-      <c r="G23" s="12"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="11">
+      <c r="A24" s="10">
         <v>21</v>
       </c>
-      <c r="B24" s="12" t="s">
+      <c r="B24" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="12" t="s">
+      <c r="C24" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24" s="10">
         <v>1976</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="10">
         <v>7.7</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="11">
+      <c r="G24" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="10">
         <v>7</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="15">
         <v>45839</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="11">
+      <c r="A25" s="10">
         <v>41</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20" t="s">
+      <c r="C25" s="19"/>
+      <c r="D25" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="10">
         <v>1976</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="10">
         <v>7.2</v>
       </c>
-      <c r="G25" s="12"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="11">
+      <c r="A26" s="10">
         <v>49</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20" t="s">
+      <c r="C26" s="19"/>
+      <c r="D26" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="11">
+      <c r="E26" s="10">
         <v>1977</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="10">
         <v>7.3</v>
       </c>
-      <c r="G26" s="12"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="11">
+      <c r="A27" s="10">
         <v>40</v>
       </c>
-      <c r="B27" s="17" t="s">
+      <c r="B27" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27" s="17" t="s">
+      <c r="C27" s="19"/>
+      <c r="D27" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="11">
+      <c r="E27" s="10">
         <v>1979</v>
       </c>
-      <c r="F27" s="11">
+      <c r="F27" s="10">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="11">
+      <c r="A28" s="10">
         <v>19</v>
       </c>
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="12" t="s">
+      <c r="C28" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="11">
+      <c r="E28" s="10">
         <v>1980</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="10">
         <v>7.8</v>
       </c>
-      <c r="G28" s="12"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="14"/>
+      <c r="G28" s="11"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="13"/>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="11">
+      <c r="A29" s="10">
         <v>22</v>
       </c>
-      <c r="B29" s="12" t="s">
+      <c r="B29" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="12" t="s">
+      <c r="C29" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="10">
         <v>1980</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="10">
         <v>7.8</v>
       </c>
-      <c r="G29" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="11">
+      <c r="G29" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="10">
         <v>6</v>
       </c>
-      <c r="I29" s="16">
+      <c r="I29" s="15">
         <v>45870</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" s="11">
+      <c r="A30" s="10">
         <v>42</v>
       </c>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="20" t="s">
+      <c r="C30" s="19"/>
+      <c r="D30" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E30" s="11">
+      <c r="E30" s="10">
         <v>1980</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="10">
         <v>6.7</v>
       </c>
-      <c r="G30" s="12"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" s="11">
+      <c r="A31" s="10">
         <v>23</v>
       </c>
-      <c r="B31" s="12" t="s">
+      <c r="B31" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="12" t="s">
+      <c r="C31" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="11">
+      <c r="E31" s="10">
         <v>1982</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="10">
         <v>7.6</v>
       </c>
-      <c r="G31" s="12"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="14"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="13"/>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="11">
+      <c r="A32" s="10">
         <v>43</v>
       </c>
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="20"/>
-      <c r="D32" s="20" t="s">
+      <c r="C32" s="19"/>
+      <c r="D32" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E32" s="11">
+      <c r="E32" s="10">
         <v>1983</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="10">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G32" s="12"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
+      <c r="G32" s="11"/>
+      <c r="H32" s="19"/>
+      <c r="I32" s="19"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="11">
+      <c r="A33" s="10">
         <v>75</v>
       </c>
-      <c r="B33" s="17" t="s">
+      <c r="B33" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20" t="s">
+      <c r="C33" s="19"/>
+      <c r="D33" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="10">
         <v>1984</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="10">
         <v>7.3</v>
       </c>
-      <c r="G33" s="12"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="19"/>
+      <c r="I33" s="19"/>
     </row>
     <row r="34" spans="1:9">
-      <c r="A34" s="11">
+      <c r="A34" s="10">
         <v>27</v>
       </c>
-      <c r="B34" s="12" t="s">
+      <c r="B34" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C34" s="12" t="s">
+      <c r="C34" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="D34" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E34" s="11">
+      <c r="E34" s="10">
         <v>1985</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="10">
         <v>7.5</v>
       </c>
-      <c r="G34" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="11">
+      <c r="G34" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="10">
         <v>6</v>
       </c>
-      <c r="I34" s="16">
+      <c r="I34" s="15">
         <v>45839</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="11">
+      <c r="A35" s="10">
         <v>48</v>
       </c>
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="20"/>
-      <c r="D35" s="20" t="s">
+      <c r="C35" s="19"/>
+      <c r="D35" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="11">
+      <c r="E35" s="10">
         <v>1986</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="10">
         <v>7.5</v>
       </c>
-      <c r="G35" s="12"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="11">
+      <c r="A36" s="10">
         <v>44</v>
       </c>
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="C36" s="20"/>
-      <c r="D36" s="20" t="s">
+      <c r="C36" s="19"/>
+      <c r="D36" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E36" s="11">
+      <c r="E36" s="10">
         <v>1987</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="10">
         <v>7.8</v>
       </c>
-      <c r="G36" s="12"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19"/>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="11">
+      <c r="A37" s="10">
         <v>24</v>
       </c>
-      <c r="B37" s="12" t="s">
+      <c r="B37" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C37" s="12" t="s">
+      <c r="C37" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="10">
         <v>1988</v>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="10">
         <v>7.4</v>
       </c>
-      <c r="G37" s="12"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="14"/>
+      <c r="G37" s="11"/>
+      <c r="H37" s="10"/>
+      <c r="I37" s="13"/>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="11">
+      <c r="A38" s="10">
         <v>25</v>
       </c>
-      <c r="B38" s="12" t="s">
+      <c r="B38" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="12" t="s">
+      <c r="C38" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="11">
+      <c r="E38" s="10">
         <v>1990</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="10">
         <v>8.1</v>
       </c>
-      <c r="G38" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H38" s="11">
+      <c r="G38" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="10">
         <v>9</v>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="15">
         <v>45809</v>
       </c>
     </row>
     <row r="39" spans="1:9">
-      <c r="A39" s="11">
+      <c r="A39" s="10">
         <v>38</v>
       </c>
-      <c r="B39" s="17" t="s">
+      <c r="B39" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="17" t="s">
+      <c r="D39" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="11">
+      <c r="E39" s="10">
         <v>1990</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F39" s="10">
         <v>7.9</v>
       </c>
-      <c r="G39" s="12"/>
-      <c r="H39" s="20"/>
-      <c r="I39" s="20"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
     </row>
     <row r="40" spans="1:9">
-      <c r="A40" s="11">
+      <c r="A40" s="10">
         <v>76</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C40" s="20"/>
-      <c r="D40" s="20" t="s">
+      <c r="C40" s="19"/>
+      <c r="D40" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E40" s="11">
+      <c r="E40" s="10">
         <v>1990</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="10">
         <v>7.6</v>
       </c>
-      <c r="G40" s="12"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="19"/>
+      <c r="I40" s="19"/>
     </row>
     <row r="41" spans="1:9">
-      <c r="A41" s="11">
+      <c r="A41" s="10">
         <v>28</v>
       </c>
-      <c r="B41" s="12" t="s">
+      <c r="B41" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C41" s="12" t="s">
+      <c r="C41" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="12" t="s">
+      <c r="D41" s="11" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41" s="10">
         <v>1991</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="10">
         <v>7.2</v>
       </c>
-      <c r="G41" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" s="11">
+      <c r="G41" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="10">
         <v>7</v>
       </c>
-      <c r="I41" s="16">
+      <c r="I41" s="15">
         <v>45839</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="11">
+      <c r="A42" s="10">
         <v>80</v>
       </c>
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20" t="s">
+      <c r="C42" s="19"/>
+      <c r="D42" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E42" s="11">
+      <c r="E42" s="10">
         <v>1991</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="10">
         <v>7.7</v>
       </c>
-      <c r="G42" s="12"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="20"/>
+      <c r="G42" s="11"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
     </row>
     <row r="43" spans="1:9">
-      <c r="A43" s="11">
+      <c r="A43" s="10">
         <v>51</v>
       </c>
-      <c r="B43" s="17" t="s">
+      <c r="B43" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20" t="s">
+      <c r="C43" s="19"/>
+      <c r="D43" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E43" s="11">
+      <c r="E43" s="10">
         <v>1992</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="10">
         <v>8.1</v>
       </c>
-      <c r="G43" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H43" s="19">
+      <c r="G43" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H43" s="18">
         <v>8</v>
       </c>
-      <c r="I43" s="16">
+      <c r="I43" s="15">
         <v>45748</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" s="11">
+      <c r="A44" s="10">
         <v>127</v>
       </c>
-      <c r="B44" s="17" t="s">
+      <c r="B44" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E44" s="11">
+      <c r="E44" s="10">
         <v>1992</v>
       </c>
-      <c r="F44" s="11">
+      <c r="F44" s="10">
         <v>8.5</v>
       </c>
-      <c r="G44" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H44" s="11">
+      <c r="G44" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="10">
         <v>6.5</v>
       </c>
-      <c r="I44" s="21">
+      <c r="I44" s="20">
         <v>45778</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" s="11">
+      <c r="A45" s="10">
         <v>52</v>
       </c>
-      <c r="B45" s="17" t="s">
+      <c r="B45" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20" t="s">
+      <c r="C45" s="19"/>
+      <c r="D45" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="10">
         <v>1994</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="10">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G45" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H45" s="19">
+      <c r="G45" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="18">
         <v>7</v>
       </c>
-      <c r="I45" s="16">
+      <c r="I45" s="15">
         <v>45748</v>
       </c>
     </row>
     <row r="46" spans="1:9">
-      <c r="A46" s="11">
+      <c r="A46" s="10">
         <v>26</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E46" s="11">
+      <c r="E46" s="10">
         <v>1995</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="10">
         <v>8.1</v>
       </c>
-      <c r="G46" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H46" s="11">
+      <c r="G46" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="10">
         <v>8</v>
       </c>
-      <c r="I46" s="16">
+      <c r="I46" s="15">
         <v>45809</v>
       </c>
     </row>
     <row r="47" spans="1:9">
-      <c r="A47" s="11">
+      <c r="A47" s="10">
         <v>70</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="20" t="s">
+      <c r="C47" s="19"/>
+      <c r="D47" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="E47" s="11">
+      <c r="E47" s="10">
         <v>1995</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="10">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G47" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H47" s="19">
+      <c r="G47" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" s="18">
         <v>8</v>
       </c>
-      <c r="I47" s="16">
+      <c r="I47" s="15">
         <v>46023</v>
       </c>
     </row>
     <row r="48" spans="1:9">
-      <c r="A48" s="11">
+      <c r="A48" s="10">
         <v>72</v>
       </c>
-      <c r="B48" s="17" t="s">
+      <c r="B48" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="20" t="s">
+      <c r="C48" s="19"/>
+      <c r="D48" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E48" s="11">
+      <c r="E48" s="10">
         <v>1996</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="10">
         <v>7.6</v>
       </c>
-      <c r="G48" s="12"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
+      <c r="G48" s="11"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="19"/>
     </row>
     <row r="49" spans="1:9">
-      <c r="A49" s="11">
+      <c r="A49" s="10">
         <v>46</v>
       </c>
-      <c r="B49" s="17" t="s">
+      <c r="B49" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20" t="s">
+      <c r="C49" s="19"/>
+      <c r="D49" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49" s="10">
         <v>1997</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="10">
         <v>7.3</v>
       </c>
-      <c r="G49" s="12"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
+      <c r="G49" s="11"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
     </row>
     <row r="50" spans="1:9">
-      <c r="A50" s="11">
+      <c r="A50" s="10">
         <v>53</v>
       </c>
-      <c r="B50" s="17" t="s">
+      <c r="B50" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C50" s="20"/>
-      <c r="D50" s="20" t="s">
+      <c r="C50" s="19"/>
+      <c r="D50" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="11">
+      <c r="E50" s="10">
         <v>1997</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="10">
         <v>7.1</v>
       </c>
-      <c r="G50" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H50" s="19">
+      <c r="G50" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="18">
         <v>5</v>
       </c>
-      <c r="I50" s="16">
+      <c r="I50" s="15">
         <v>45748</v>
       </c>
     </row>
     <row r="51" spans="1:9">
-      <c r="A51" s="11">
+      <c r="A51" s="10">
         <v>65</v>
       </c>
-      <c r="B51" s="17" t="s">
+      <c r="B51" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="20" t="s">
+      <c r="C51" s="19"/>
+      <c r="D51" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="E51" s="11">
+      <c r="E51" s="10">
         <v>1997</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="10">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G51" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" s="19">
+      <c r="G51" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="18">
         <v>8</v>
       </c>
-      <c r="I51" s="14" t="s">
+      <c r="I51" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="52" spans="1:9">
-      <c r="A52" s="11">
+      <c r="A52" s="10">
         <v>95</v>
       </c>
-      <c r="B52" s="17" t="s">
+      <c r="B52" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="20" t="s">
+      <c r="C52" s="19"/>
+      <c r="D52" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="E52" s="11">
+      <c r="E52" s="10">
         <v>1997</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="10">
         <v>7.4</v>
       </c>
-      <c r="G52" s="12"/>
-      <c r="H52" s="20"/>
-      <c r="I52" s="20"/>
+      <c r="G52" s="11"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="19"/>
     </row>
     <row r="53" spans="1:9">
-      <c r="A53" s="11">
+      <c r="A53" s="10">
         <v>74</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C53" s="20"/>
-      <c r="D53" s="20" t="s">
+      <c r="C53" s="19"/>
+      <c r="D53" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="11">
+      <c r="E53" s="10">
         <v>1998</v>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="10">
         <v>7.8</v>
       </c>
-      <c r="G53" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H53" s="19">
+      <c r="G53" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" s="18">
         <v>6</v>
       </c>
-      <c r="I53" s="14" t="s">
+      <c r="I53" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:9">
-      <c r="A54" s="11">
+      <c r="A54" s="10">
         <v>101</v>
       </c>
-      <c r="B54" s="17" t="s">
+      <c r="B54" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20" t="s">
+      <c r="C54" s="19"/>
+      <c r="D54" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="E54" s="11">
+      <c r="E54" s="10">
         <v>1998</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="10">
         <v>7.5</v>
       </c>
-      <c r="G54" s="12"/>
-      <c r="H54" s="20"/>
-      <c r="I54" s="20"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
     </row>
     <row r="55" spans="1:9">
-      <c r="A55" s="11">
+      <c r="A55" s="10">
         <v>112</v>
       </c>
-      <c r="B55" s="17" t="s">
+      <c r="B55" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20" t="s">
+      <c r="C55" s="19"/>
+      <c r="D55" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="E55" s="11">
+      <c r="E55" s="10">
         <v>1998</v>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="10">
         <v>8.6</v>
       </c>
-      <c r="G55" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H55" s="11">
+      <c r="G55" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" s="10">
         <v>6</v>
       </c>
-      <c r="I55" s="21">
+      <c r="I55" s="20">
         <v>45717</v>
       </c>
     </row>
     <row r="56" spans="1:9">
-      <c r="A56" s="11">
+      <c r="A56" s="10">
         <v>50</v>
       </c>
-      <c r="B56" s="17" t="s">
+      <c r="B56" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C56" s="20"/>
-      <c r="D56" s="20" t="s">
+      <c r="C56" s="19"/>
+      <c r="D56" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="E56" s="11">
+      <c r="E56" s="10">
         <v>1999</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F56" s="10">
         <v>7.8</v>
       </c>
-      <c r="G56" s="12"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="19"/>
     </row>
     <row r="57" spans="1:9">
-      <c r="A57" s="11">
+      <c r="A57" s="10">
         <v>66</v>
       </c>
-      <c r="B57" s="17" t="s">
+      <c r="B57" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C57" s="20"/>
-      <c r="D57" s="20" t="s">
+      <c r="C57" s="19"/>
+      <c r="D57" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E57" s="11">
+      <c r="E57" s="10">
         <v>1999</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="10">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G57" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H57" s="19">
+      <c r="G57" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" s="18">
         <v>8</v>
       </c>
-      <c r="I57" s="16">
+      <c r="I57" s="15">
         <v>46023</v>
       </c>
     </row>
     <row r="58" spans="1:9">
-      <c r="A58" s="11">
+      <c r="A58" s="10">
         <v>97</v>
       </c>
-      <c r="B58" s="17" t="s">
+      <c r="B58" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="20"/>
-      <c r="D58" s="20" t="s">
+      <c r="C58" s="19"/>
+      <c r="D58" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="E58" s="11">
+      <c r="E58" s="10">
         <v>1999</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="10">
         <v>7.4</v>
       </c>
-      <c r="G58" s="12"/>
-      <c r="H58" s="20"/>
-      <c r="I58" s="20"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="19"/>
+      <c r="I58" s="19"/>
     </row>
     <row r="59" spans="1:9">
-      <c r="A59" s="11">
+      <c r="A59" s="10">
         <v>130</v>
       </c>
-      <c r="B59" s="17" t="s">
+      <c r="B59" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20" t="s">
+      <c r="C59" s="19"/>
+      <c r="D59" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E59" s="11">
+      <c r="E59" s="10">
         <v>1999</v>
       </c>
-      <c r="F59" s="11">
+      <c r="F59" s="10">
         <v>7.4</v>
       </c>
-      <c r="G59" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H59" s="11">
+      <c r="G59" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" s="10">
         <v>6</v>
       </c>
-      <c r="I59" s="21">
+      <c r="I59" s="20">
         <v>45778</v>
       </c>
     </row>
     <row r="60" spans="1:9">
-      <c r="A60" s="11">
+      <c r="A60" s="10">
         <v>92</v>
       </c>
-      <c r="B60" s="17" t="s">
+      <c r="B60" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C60" s="20"/>
-      <c r="D60" s="22" t="s">
+      <c r="C60" s="19"/>
+      <c r="D60" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="10">
         <v>2000</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="10">
         <v>8</v>
       </c>
-      <c r="G60" s="12"/>
-      <c r="H60" s="20"/>
-      <c r="I60" s="20"/>
+      <c r="G60" s="11"/>
+      <c r="H60" s="19"/>
+      <c r="I60" s="19"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="11">
+      <c r="A61" s="10">
         <v>108</v>
       </c>
-      <c r="B61" s="17" t="s">
+      <c r="B61" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20" t="s">
+      <c r="C61" s="19"/>
+      <c r="D61" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="E61" s="11">
+      <c r="E61" s="10">
         <v>2000</v>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="10">
         <v>7.9</v>
       </c>
-      <c r="G61" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H61" s="19">
+      <c r="G61" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" s="18">
         <v>8</v>
       </c>
-      <c r="I61" s="16">
+      <c r="I61" s="15">
         <v>46082</v>
       </c>
     </row>
     <row r="62" spans="1:9">
-      <c r="A62" s="11">
+      <c r="A62" s="10">
         <v>113</v>
       </c>
-      <c r="B62" s="17" t="s">
+      <c r="B62" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20" t="s">
+      <c r="C62" s="19"/>
+      <c r="D62" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="E62" s="11">
+      <c r="E62" s="10">
         <v>2000</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="10">
         <v>8.6</v>
       </c>
-      <c r="G62" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H62" s="11">
+      <c r="G62" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" s="10">
         <v>7</v>
       </c>
-      <c r="I62" s="21">
+      <c r="I62" s="20">
         <v>45717</v>
       </c>
     </row>
     <row r="63" spans="1:9">
-      <c r="A63" s="11">
+      <c r="A63" s="10">
         <v>47</v>
       </c>
-      <c r="B63" s="17" t="s">
+      <c r="B63" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20" t="s">
+      <c r="C63" s="19"/>
+      <c r="D63" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="E63" s="11">
+      <c r="E63" s="10">
         <v>2001</v>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="10">
         <v>7.7</v>
       </c>
-      <c r="G63" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H63" s="19">
+      <c r="G63" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="18">
         <v>7</v>
       </c>
-      <c r="I63" s="16">
+      <c r="I63" s="15">
         <v>45931</v>
       </c>
     </row>
     <row r="64" spans="1:9">
-      <c r="A64" s="11">
+      <c r="A64" s="10">
         <v>77</v>
       </c>
-      <c r="B64" s="17" t="s">
+      <c r="B64" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20" t="s">
+      <c r="C64" s="19"/>
+      <c r="D64" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="E64" s="11">
+      <c r="E64" s="10">
         <v>2001</v>
       </c>
-      <c r="F64" s="11">
+      <c r="F64" s="10">
         <v>7.6</v>
       </c>
-      <c r="G64" s="12"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="19"/>
+      <c r="I64" s="19"/>
     </row>
     <row r="65" spans="1:9" ht="42.75">
-      <c r="A65" s="11">
+      <c r="A65" s="10">
         <v>31</v>
       </c>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="D65" s="12" t="s">
+      <c r="D65" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="10">
         <v>2002</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="10">
         <v>7.7</v>
       </c>
-      <c r="G65" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H65" s="11">
+      <c r="G65" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" s="10">
         <v>8</v>
       </c>
-      <c r="I65" s="16">
+      <c r="I65" s="15">
         <v>45839</v>
       </c>
     </row>
     <row r="66" spans="1:9">
-      <c r="A66" s="11">
+      <c r="A66" s="10">
         <v>63</v>
       </c>
-      <c r="B66" s="17" t="s">
+      <c r="B66" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20" t="s">
+      <c r="C66" s="19"/>
+      <c r="D66" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="E66" s="11">
+      <c r="E66" s="10">
         <v>2002</v>
       </c>
-      <c r="F66" s="11">
+      <c r="F66" s="10">
         <v>7.3</v>
       </c>
-      <c r="G66" s="12"/>
-      <c r="H66" s="20"/>
-      <c r="I66" s="20"/>
+      <c r="G66" s="11"/>
+      <c r="H66" s="19"/>
+      <c r="I66" s="19"/>
     </row>
     <row r="67" spans="1:9">
-      <c r="A67" s="11">
+      <c r="A67" s="10">
         <v>102</v>
       </c>
-      <c r="B67" s="17" t="s">
+      <c r="B67" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20" t="s">
+      <c r="C67" s="19"/>
+      <c r="D67" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="11">
+      <c r="E67" s="10">
         <v>2002</v>
       </c>
-      <c r="F67" s="11">
+      <c r="F67" s="10">
         <v>7.4</v>
       </c>
-      <c r="G67" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" s="19">
+      <c r="G67" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="18">
         <v>6</v>
       </c>
-      <c r="I67" s="16">
+      <c r="I67" s="15">
         <v>46143</v>
       </c>
     </row>
     <row r="68" spans="1:9">
-      <c r="A68" s="11">
+      <c r="A68" s="10">
         <v>54</v>
       </c>
-      <c r="B68" s="17" t="s">
+      <c r="B68" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20" t="s">
+      <c r="C68" s="19"/>
+      <c r="D68" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="E68" s="11">
+      <c r="E68" s="10">
         <v>2003</v>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="10">
         <v>7.7</v>
       </c>
-      <c r="G68" s="12"/>
-      <c r="H68" s="20"/>
-      <c r="I68" s="20"/>
+      <c r="G68" s="11"/>
+      <c r="H68" s="19"/>
+      <c r="I68" s="19"/>
     </row>
     <row r="69" spans="1:9">
-      <c r="A69" s="11">
+      <c r="A69" s="10">
         <v>89</v>
       </c>
-      <c r="B69" s="17" t="s">
+      <c r="B69" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20" t="s">
+      <c r="C69" s="19"/>
+      <c r="D69" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E69" s="10">
         <v>2003</v>
       </c>
-      <c r="F69" s="11">
+      <c r="F69" s="10">
         <v>8.1</v>
       </c>
-      <c r="G69" s="12"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
+      <c r="G69" s="11"/>
+      <c r="H69" s="19"/>
+      <c r="I69" s="19"/>
     </row>
     <row r="70" spans="1:9">
-      <c r="A70" s="11">
+      <c r="A70" s="10">
         <v>218</v>
       </c>
-      <c r="B70" s="17" t="s">
+      <c r="B70" s="16" t="s">
         <v>103</v>
       </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20" t="s">
+      <c r="C70" s="19"/>
+      <c r="D70" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="E70" s="11">
+      <c r="E70" s="10">
         <v>2003</v>
       </c>
-      <c r="F70" s="11"/>
-      <c r="G70" s="12"/>
-      <c r="H70" s="11"/>
-      <c r="I70" s="24"/>
+      <c r="F70" s="10"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="10"/>
+      <c r="I70" s="23"/>
     </row>
     <row r="71" spans="1:9">
-      <c r="A71" s="11">
+      <c r="A71" s="10">
         <v>29</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D71" s="12" t="s">
+      <c r="D71" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="E71" s="11">
+      <c r="E71" s="10">
         <v>2004</v>
       </c>
-      <c r="F71" s="11">
+      <c r="F71" s="10">
         <v>7.6</v>
       </c>
-      <c r="G71" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" s="11">
+      <c r="G71" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="10">
         <v>8</v>
       </c>
-      <c r="I71" s="16">
+      <c r="I71" s="15">
         <v>45839</v>
       </c>
     </row>
     <row r="72" spans="1:9">
-      <c r="A72" s="11">
+      <c r="A72" s="10">
         <v>55</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B72" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20" t="s">
+      <c r="C72" s="19"/>
+      <c r="D72" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E72" s="11">
+      <c r="E72" s="10">
         <v>2004</v>
       </c>
-      <c r="F72" s="11">
+      <c r="F72" s="10">
         <v>7.6</v>
       </c>
-      <c r="G72" s="12"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="19"/>
+      <c r="I72" s="19"/>
     </row>
     <row r="73" spans="1:9">
-      <c r="A73" s="11">
+      <c r="A73" s="10">
         <v>91</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B73" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20" t="s">
+      <c r="C73" s="19"/>
+      <c r="D73" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="E73" s="11">
+      <c r="E73" s="10">
         <v>2005</v>
       </c>
-      <c r="F73" s="11">
+      <c r="F73" s="10">
         <v>7.6</v>
       </c>
-      <c r="G73" s="12"/>
-      <c r="H73" s="20"/>
-      <c r="I73" s="20"/>
+      <c r="G73" s="11"/>
+      <c r="H73" s="19"/>
+      <c r="I73" s="19"/>
     </row>
     <row r="74" spans="1:9">
-      <c r="A74" s="11">
+      <c r="A74" s="10">
         <v>103</v>
       </c>
-      <c r="B74" s="17" t="s">
+      <c r="B74" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20" t="s">
+      <c r="C74" s="19"/>
+      <c r="D74" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="E74" s="11">
+      <c r="E74" s="10">
         <v>2005</v>
       </c>
-      <c r="F74" s="11">
+      <c r="F74" s="10">
         <v>7.9</v>
       </c>
-      <c r="G74" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H74" s="19">
+      <c r="G74" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="18">
         <v>7</v>
       </c>
-      <c r="I74" s="14" t="s">
+      <c r="I74" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="75" spans="1:9">
-      <c r="A75" s="11">
+      <c r="A75" s="10">
         <v>114</v>
       </c>
-      <c r="B75" s="17" t="s">
+      <c r="B75" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20" t="s">
+      <c r="C75" s="19"/>
+      <c r="D75" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="E75" s="11">
+      <c r="E75" s="10">
         <v>2005</v>
       </c>
-      <c r="F75" s="11">
+      <c r="F75" s="10">
         <v>7.3</v>
       </c>
-      <c r="G75" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" s="11">
+      <c r="G75" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="10">
         <v>6</v>
       </c>
-      <c r="I75" s="21">
+      <c r="I75" s="20">
         <v>45748</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="57">
-      <c r="A76" s="11">
+      <c r="A76" s="10">
         <v>30</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="D76" s="12" t="s">
+      <c r="D76" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E76" s="11">
+      <c r="E76" s="10">
         <v>2006</v>
       </c>
-      <c r="F76" s="11">
+      <c r="F76" s="10">
         <v>8.5</v>
       </c>
-      <c r="G76" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" s="11">
+      <c r="G76" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="10">
         <v>8</v>
       </c>
-      <c r="I76" s="16">
+      <c r="I76" s="15">
         <v>45839</v>
       </c>
     </row>
     <row r="77" spans="1:9">
-      <c r="A77" s="11">
+      <c r="A77" s="10">
         <v>104</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C77" s="20"/>
-      <c r="D77" s="20" t="s">
+      <c r="C77" s="19"/>
+      <c r="D77" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="E77" s="11">
+      <c r="E77" s="10">
         <v>2006</v>
       </c>
-      <c r="F77" s="11">
+      <c r="F77" s="10">
         <v>8.5</v>
       </c>
-      <c r="G77" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="19">
+      <c r="G77" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="18">
         <v>8</v>
       </c>
-      <c r="I77" s="14" t="s">
+      <c r="I77" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="78" spans="1:9">
-      <c r="A78" s="11">
+      <c r="A78" s="10">
         <v>56</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="B78" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C78" s="20"/>
-      <c r="D78" s="20" t="s">
+      <c r="C78" s="19"/>
+      <c r="D78" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="E78" s="11">
+      <c r="E78" s="10">
         <v>2007</v>
       </c>
-      <c r="F78" s="11">
+      <c r="F78" s="10">
         <v>7.1</v>
       </c>
-      <c r="G78" s="12"/>
-      <c r="H78" s="20"/>
-      <c r="I78" s="20"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="19"/>
+      <c r="I78" s="19"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="11">
+      <c r="A79" s="10">
         <v>71</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="B79" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C79" s="20"/>
-      <c r="D79" s="20" t="s">
+      <c r="C79" s="19"/>
+      <c r="D79" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="E79" s="11">
+      <c r="E79" s="10">
         <v>2007</v>
       </c>
-      <c r="F79" s="11">
+      <c r="F79" s="10">
         <v>7.3</v>
       </c>
-      <c r="G79" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" s="19">
+      <c r="G79" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="18">
         <v>8</v>
       </c>
-      <c r="I79" s="14" t="s">
+      <c r="I79" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:9">
-      <c r="A80" s="11">
+      <c r="A80" s="10">
         <v>73</v>
       </c>
-      <c r="B80" s="17" t="s">
+      <c r="B80" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C80" s="20"/>
-      <c r="D80" s="20" t="s">
+      <c r="C80" s="19"/>
+      <c r="D80" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E80" s="11">
+      <c r="E80" s="10">
         <v>2007</v>
       </c>
-      <c r="F80" s="11">
+      <c r="F80" s="10">
         <v>7.8</v>
       </c>
-      <c r="G80" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="19">
+      <c r="G80" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="18">
         <v>7</v>
       </c>
-      <c r="I80" s="16">
+      <c r="I80" s="15">
         <v>45962</v>
       </c>
     </row>
     <row r="81" spans="1:9">
-      <c r="A81" s="11">
+      <c r="A81" s="10">
         <v>94</v>
       </c>
-      <c r="B81" s="17" t="s">
+      <c r="B81" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C81" s="20"/>
-      <c r="D81" s="20" t="s">
+      <c r="C81" s="19"/>
+      <c r="D81" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="E81" s="11">
+      <c r="E81" s="10">
         <v>2007</v>
       </c>
-      <c r="F81" s="11">
+      <c r="F81" s="10">
         <v>7.9</v>
       </c>
-      <c r="G81" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H81" s="19">
+      <c r="G81" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" s="18">
         <v>9</v>
       </c>
-      <c r="I81" s="16">
+      <c r="I81" s="15">
         <v>45839</v>
       </c>
     </row>
     <row r="82" spans="1:9" ht="29.25">
-      <c r="A82" s="11">
+      <c r="A82" s="10">
         <v>62</v>
       </c>
-      <c r="B82" s="17" t="s">
+      <c r="B82" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C82" s="20"/>
-      <c r="D82" s="18" t="s">
+      <c r="C82" s="19"/>
+      <c r="D82" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="E82" s="11">
+      <c r="E82" s="10">
         <v>2008</v>
       </c>
-      <c r="F82" s="11">
+      <c r="F82" s="10">
         <v>8.1</v>
       </c>
-      <c r="G82" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H82" s="19">
+      <c r="G82" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" s="18">
         <v>8</v>
       </c>
-      <c r="I82" s="14">
+      <c r="I82" s="13">
         <v>2024</v>
       </c>
     </row>
     <row r="83" spans="1:9">
-      <c r="A83" s="11">
+      <c r="A83" s="10">
         <v>78</v>
       </c>
-      <c r="B83" s="17" t="s">
+      <c r="B83" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C83" s="20"/>
-      <c r="D83" s="20" t="s">
+      <c r="C83" s="19"/>
+      <c r="D83" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E83" s="11">
+      <c r="E83" s="10">
         <v>2008</v>
       </c>
-      <c r="F83" s="11">
+      <c r="F83" s="10">
         <v>6.9</v>
       </c>
-      <c r="G83" s="12"/>
-      <c r="H83" s="20"/>
-      <c r="I83" s="20"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="19"/>
+      <c r="I83" s="19"/>
     </row>
     <row r="84" spans="1:9">
-      <c r="A84" s="11">
+      <c r="A84" s="10">
         <v>111</v>
       </c>
-      <c r="B84" s="17" t="s">
+      <c r="B84" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20" t="s">
+      <c r="C84" s="19"/>
+      <c r="D84" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="E84" s="11">
+      <c r="E84" s="10">
         <v>2008</v>
       </c>
-      <c r="F84" s="11">
+      <c r="F84" s="10">
         <v>8.5</v>
       </c>
-      <c r="G84" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H84" s="25">
+      <c r="G84" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" s="24">
         <v>7.7</v>
       </c>
-      <c r="I84" s="15">
+      <c r="I84" s="14">
         <v>46200</v>
       </c>
     </row>
     <row r="85" spans="1:9">
-      <c r="A85" s="11">
+      <c r="A85" s="10">
         <v>115</v>
       </c>
-      <c r="B85" s="17" t="s">
+      <c r="B85" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C85" s="20"/>
-      <c r="D85" s="20" t="s">
+      <c r="C85" s="19"/>
+      <c r="D85" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="E85" s="11">
+      <c r="E85" s="10">
         <v>2008</v>
       </c>
-      <c r="F85" s="11">
+      <c r="F85" s="10">
         <v>7.8</v>
       </c>
-      <c r="G85" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H85" s="11">
+      <c r="G85" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" s="10">
         <v>6</v>
       </c>
-      <c r="I85" s="21">
+      <c r="I85" s="20">
         <v>45748</v>
       </c>
     </row>
     <row r="86" spans="1:9">
-      <c r="A86" s="11">
+      <c r="A86" s="10">
         <v>131</v>
       </c>
-      <c r="B86" s="17" t="s">
+      <c r="B86" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C86" s="20" t="s">
+      <c r="C86" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D86" s="20" t="s">
+      <c r="D86" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="E86" s="11">
+      <c r="E86" s="10">
         <v>2008</v>
       </c>
-      <c r="F86" s="11">
+      <c r="F86" s="10">
         <v>6.8</v>
       </c>
-      <c r="G86" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H86" s="11">
+      <c r="G86" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="10">
         <v>6</v>
       </c>
-      <c r="I86" s="21">
+      <c r="I86" s="20">
         <v>45778</v>
       </c>
     </row>
     <row r="87" spans="1:9">
-      <c r="A87" s="11">
+      <c r="A87" s="10">
         <v>33</v>
       </c>
-      <c r="B87" s="12" t="s">
+      <c r="B87" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C87" s="12" t="s">
+      <c r="C87" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="D87" s="12" t="s">
+      <c r="D87" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="E87" s="11">
+      <c r="E87" s="10">
         <v>2009</v>
       </c>
-      <c r="F87" s="11">
+      <c r="F87" s="10">
         <v>8.6</v>
       </c>
-      <c r="G87" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H87" s="11">
+      <c r="G87" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" s="10">
         <v>9</v>
       </c>
-      <c r="I87" s="14" t="s">
+      <c r="I87" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:9">
-      <c r="A88" s="11">
+      <c r="A88" s="10">
         <v>57</v>
       </c>
-      <c r="B88" s="17" t="s">
+      <c r="B88" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C88" s="20"/>
-      <c r="D88" s="20" t="s">
+      <c r="C88" s="19"/>
+      <c r="D88" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="E88" s="11">
+      <c r="E88" s="10">
         <v>2009</v>
       </c>
-      <c r="F88" s="11">
+      <c r="F88" s="10">
         <v>8</v>
       </c>
-      <c r="G88" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H88" s="19">
+      <c r="G88" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" s="18">
         <v>7</v>
       </c>
-      <c r="I88" s="16">
+      <c r="I88" s="15">
         <v>45748</v>
       </c>
     </row>
     <row r="89" spans="1:9">
-      <c r="A89" s="11">
+      <c r="A89" s="10">
         <v>116</v>
       </c>
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C89" s="20"/>
-      <c r="D89" s="20" t="s">
+      <c r="C89" s="19"/>
+      <c r="D89" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="E89" s="11">
+      <c r="E89" s="10">
         <v>2009</v>
       </c>
-      <c r="F89" s="11">
+      <c r="F89" s="10">
         <v>8.1</v>
       </c>
-      <c r="G89" s="12"/>
-      <c r="H89" s="11"/>
-      <c r="I89" s="20"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="10"/>
+      <c r="I89" s="19"/>
     </row>
     <row r="90" spans="1:9">
-      <c r="A90" s="11">
+      <c r="A90" s="10">
         <v>58</v>
       </c>
-      <c r="B90" s="17" t="s">
+      <c r="B90" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C90" s="20"/>
-      <c r="D90" s="20" t="s">
+      <c r="C90" s="19"/>
+      <c r="D90" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E90" s="11">
+      <c r="E90" s="10">
         <v>2010</v>
       </c>
-      <c r="F90" s="11">
+      <c r="F90" s="10">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G90" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H90" s="19">
+      <c r="G90" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" s="18">
         <v>7</v>
       </c>
-      <c r="I90" s="16">
+      <c r="I90" s="15">
         <v>45748</v>
       </c>
     </row>
     <row r="91" spans="1:9">
-      <c r="A91" s="11">
+      <c r="A91" s="10">
         <v>69</v>
       </c>
-      <c r="B91" s="17" t="s">
+      <c r="B91" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C91" s="20"/>
-      <c r="D91" s="20" t="s">
+      <c r="C91" s="19"/>
+      <c r="D91" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="E91" s="11">
+      <c r="E91" s="10">
         <v>2010</v>
       </c>
-      <c r="F91" s="11">
+      <c r="F91" s="10">
         <v>7.7</v>
       </c>
-      <c r="G91" s="12"/>
-      <c r="H91" s="20"/>
-      <c r="I91" s="20"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="19"/>
+      <c r="I91" s="19"/>
     </row>
     <row r="92" spans="1:9">
-      <c r="A92" s="11">
+      <c r="A92" s="10">
         <v>79</v>
       </c>
-      <c r="B92" s="17" t="s">
+      <c r="B92" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C92" s="20"/>
-      <c r="D92" s="20" t="s">
+      <c r="C92" s="19"/>
+      <c r="D92" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="E92" s="11">
+      <c r="E92" s="10">
         <v>2010</v>
       </c>
-      <c r="F92" s="11">
+      <c r="F92" s="10">
         <v>7.6</v>
       </c>
-      <c r="G92" s="12"/>
-      <c r="H92" s="20"/>
-      <c r="I92" s="20"/>
+      <c r="G92" s="11"/>
+      <c r="H92" s="19"/>
+      <c r="I92" s="19"/>
     </row>
     <row r="93" spans="1:9">
-      <c r="A93" s="11">
+      <c r="A93" s="10">
         <v>82</v>
       </c>
-      <c r="B93" s="17" t="s">
+      <c r="B93" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C93" s="20"/>
-      <c r="D93" s="20" t="s">
+      <c r="C93" s="19"/>
+      <c r="D93" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="E93" s="11">
+      <c r="E93" s="10">
         <v>2010</v>
       </c>
-      <c r="F93" s="11">
+      <c r="F93" s="10">
         <v>8.1</v>
       </c>
-      <c r="G93" s="12"/>
-      <c r="H93" s="20"/>
-      <c r="I93" s="20"/>
+      <c r="G93" s="11"/>
+      <c r="H93" s="19"/>
+      <c r="I93" s="19"/>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="11">
+      <c r="A94" s="10">
         <v>109</v>
       </c>
-      <c r="B94" s="17" t="s">
+      <c r="B94" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C94" s="20"/>
-      <c r="D94" s="20" t="s">
+      <c r="C94" s="19"/>
+      <c r="D94" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="E94" s="11">
+      <c r="E94" s="10">
         <v>2010</v>
       </c>
-      <c r="F94" s="11">
+      <c r="F94" s="10">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G94" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H94" s="19">
+      <c r="G94" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H94" s="18">
         <v>8</v>
       </c>
-      <c r="I94" s="14" t="s">
+      <c r="I94" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:9">
-      <c r="A95" s="11">
+      <c r="A95" s="10">
         <v>219</v>
       </c>
-      <c r="B95" s="17" t="s">
+      <c r="B95" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="C95" s="20" t="s">
+      <c r="C95" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="D95" s="20" t="s">
+      <c r="D95" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="E95" s="11">
+      <c r="E95" s="10">
         <v>2010</v>
       </c>
-      <c r="F95" s="11">
+      <c r="F95" s="10">
         <v>7.6</v>
       </c>
-      <c r="G95" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H95" s="11">
+      <c r="G95" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H95" s="10">
         <v>7.1</v>
       </c>
-      <c r="I95" s="24">
+      <c r="I95" s="23">
         <v>46200</v>
       </c>
     </row>
     <row r="96" spans="1:9">
-      <c r="A96" s="11">
+      <c r="A96" s="10">
         <v>67</v>
       </c>
-      <c r="B96" s="17" t="s">
+      <c r="B96" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C96" s="20"/>
-      <c r="D96" s="20" t="s">
+      <c r="C96" s="19"/>
+      <c r="D96" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="E96" s="11">
+      <c r="E96" s="10">
         <v>2011</v>
       </c>
-      <c r="F96" s="11">
+      <c r="F96" s="10">
         <v>7.8</v>
       </c>
-      <c r="G96" s="12"/>
-      <c r="H96" s="20"/>
-      <c r="I96" s="20"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="19"/>
+      <c r="I96" s="19"/>
     </row>
     <row r="97" spans="1:9">
-      <c r="A97" s="11">
+      <c r="A97" s="10">
         <v>117</v>
       </c>
-      <c r="B97" s="17" t="s">
+      <c r="B97" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C97" s="20"/>
-      <c r="D97" s="20" t="s">
+      <c r="C97" s="19"/>
+      <c r="D97" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="E97" s="11">
+      <c r="E97" s="10">
         <v>2011</v>
       </c>
-      <c r="F97" s="11">
+      <c r="F97" s="10">
         <v>7.9</v>
       </c>
-      <c r="G97" s="12"/>
-      <c r="H97" s="11"/>
-      <c r="I97" s="20"/>
+      <c r="G97" s="11"/>
+      <c r="H97" s="10"/>
+      <c r="I97" s="19"/>
     </row>
     <row r="98" spans="1:9">
-      <c r="A98" s="11">
+      <c r="A98" s="10">
         <v>99</v>
       </c>
-      <c r="B98" s="17" t="s">
+      <c r="B98" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C98" s="20"/>
-      <c r="D98" s="20" t="s">
+      <c r="C98" s="19"/>
+      <c r="D98" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="E98" s="11">
+      <c r="E98" s="10">
         <v>2012</v>
       </c>
-      <c r="F98" s="11">
+      <c r="F98" s="10">
         <v>6.8</v>
       </c>
-      <c r="G98" s="12"/>
-      <c r="H98" s="20"/>
-      <c r="I98" s="20"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="19"/>
+      <c r="I98" s="19"/>
     </row>
     <row r="99" spans="1:9">
-      <c r="A99" s="11">
+      <c r="A99" s="10">
         <v>107</v>
       </c>
-      <c r="B99" s="17" t="s">
+      <c r="B99" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C99" s="20"/>
-      <c r="D99" s="22" t="s">
+      <c r="C99" s="19"/>
+      <c r="D99" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="E99" s="11">
+      <c r="E99" s="10">
         <v>2012</v>
       </c>
-      <c r="F99" s="11">
+      <c r="F99" s="10">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G99" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H99" s="19">
+      <c r="G99" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H99" s="18">
         <v>8</v>
       </c>
-      <c r="I99" s="14" t="s">
+      <c r="I99" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="100" spans="1:9">
-      <c r="A100" s="11">
+      <c r="A100" s="10">
         <v>126</v>
       </c>
-      <c r="B100" s="17" t="s">
+      <c r="B100" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C100" s="20" t="s">
+      <c r="C100" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="D100" s="20" t="s">
+      <c r="D100" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E100" s="11">
+      <c r="E100" s="10">
         <v>2012</v>
       </c>
-      <c r="F100" s="11">
+      <c r="F100" s="10">
         <v>7.5</v>
       </c>
-      <c r="G100" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H100" s="11">
+      <c r="G100" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H100" s="10">
         <v>7</v>
       </c>
-      <c r="I100" s="21">
+      <c r="I100" s="20">
         <v>45748</v>
       </c>
     </row>
     <row r="101" spans="1:9" ht="42.75">
-      <c r="A101" s="11">
+      <c r="A101" s="10">
         <v>32</v>
       </c>
-      <c r="B101" s="12" t="s">
+      <c r="B101" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C101" s="23" t="s">
+      <c r="C101" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="D101" s="12" t="s">
+      <c r="D101" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="E101" s="11">
+      <c r="E101" s="10">
         <v>2013</v>
       </c>
-      <c r="F101" s="11">
+      <c r="F101" s="10">
         <v>8.1</v>
       </c>
-      <c r="G101" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H101" s="11">
+      <c r="G101" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H101" s="10">
         <v>9</v>
       </c>
-      <c r="I101" s="14" t="s">
+      <c r="I101" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="102" spans="1:9">
-      <c r="A102" s="11">
+      <c r="A102" s="10">
         <v>81</v>
       </c>
-      <c r="B102" s="17" t="s">
+      <c r="B102" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C102" s="20"/>
-      <c r="D102" s="20" t="s">
+      <c r="C102" s="19"/>
+      <c r="D102" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="E102" s="11">
+      <c r="E102" s="10">
         <v>2013</v>
       </c>
-      <c r="F102" s="11">
+      <c r="F102" s="10">
         <v>7.8</v>
       </c>
-      <c r="G102" s="12"/>
-      <c r="H102" s="20"/>
-      <c r="I102" s="20"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="19"/>
+      <c r="I102" s="19"/>
     </row>
     <row r="103" spans="1:9">
-      <c r="A103" s="11">
+      <c r="A103" s="10">
         <v>125</v>
       </c>
-      <c r="B103" s="17" t="s">
+      <c r="B103" s="16" t="s">
         <v>147</v>
       </c>
-      <c r="C103" s="20" t="s">
+      <c r="C103" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D103" s="20" t="s">
+      <c r="D103" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="E103" s="11">
+      <c r="E103" s="10">
         <v>2013</v>
       </c>
-      <c r="F103" s="11">
+      <c r="F103" s="10">
         <v>8</v>
       </c>
-      <c r="G103" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H103" s="11">
+      <c r="G103" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H103" s="10">
         <v>9</v>
       </c>
-      <c r="I103" s="21">
+      <c r="I103" s="20">
         <v>45658</v>
       </c>
     </row>
     <row r="104" spans="1:9">
-      <c r="A104" s="11">
+      <c r="A104" s="10">
         <v>68</v>
       </c>
-      <c r="B104" s="17" t="s">
+      <c r="B104" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C104" s="20"/>
-      <c r="D104" s="20" t="s">
+      <c r="C104" s="19"/>
+      <c r="D104" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="E104" s="11">
+      <c r="E104" s="10">
         <v>2014</v>
       </c>
-      <c r="F104" s="11">
+      <c r="F104" s="10">
         <v>8</v>
       </c>
-      <c r="G104" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H104" s="19">
+      <c r="G104" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H104" s="18">
         <v>8</v>
       </c>
-      <c r="I104" s="14" t="s">
+      <c r="I104" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="105" spans="1:9">
-      <c r="A105" s="11">
+      <c r="A105" s="10">
         <v>106</v>
       </c>
-      <c r="B105" s="17" t="s">
+      <c r="B105" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C105" s="20" t="s">
+      <c r="C105" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D105" s="20" t="s">
+      <c r="D105" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="E105" s="11">
+      <c r="E105" s="10">
         <v>2014</v>
       </c>
-      <c r="F105" s="11">
+      <c r="F105" s="10">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G105" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H105" s="19">
+      <c r="G105" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="18">
         <v>10</v>
       </c>
-      <c r="I105" s="16">
+      <c r="I105" s="15">
         <v>46082</v>
       </c>
     </row>
     <row r="106" spans="1:9" ht="28.5">
-      <c r="A106" s="11">
+      <c r="A106" s="10">
         <v>128</v>
       </c>
-      <c r="B106" s="22" t="s">
+      <c r="B106" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="C106" s="20"/>
-      <c r="D106" s="17" t="s">
+      <c r="C106" s="19"/>
+      <c r="D106" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="E106" s="11">
+      <c r="E106" s="10">
         <v>2014</v>
       </c>
-      <c r="F106" s="11">
+      <c r="F106" s="10">
         <v>7.7</v>
       </c>
-      <c r="G106" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H106" s="11">
+      <c r="G106" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H106" s="10">
         <v>7</v>
       </c>
-      <c r="I106" s="21">
+      <c r="I106" s="20">
         <v>45778</v>
       </c>
     </row>
     <row r="107" spans="1:9">
-      <c r="A107" s="11">
+      <c r="A107" s="10">
         <v>59</v>
       </c>
-      <c r="B107" s="17" t="s">
+      <c r="B107" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C107" s="20"/>
-      <c r="D107" s="20" t="s">
+      <c r="C107" s="19"/>
+      <c r="D107" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="E107" s="11">
+      <c r="E107" s="10">
         <v>2015</v>
       </c>
-      <c r="F107" s="11">
+      <c r="F107" s="10">
         <v>8</v>
       </c>
-      <c r="G107" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H107" s="19">
+      <c r="G107" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H107" s="18">
         <v>8</v>
       </c>
-      <c r="I107" s="16">
+      <c r="I107" s="15">
         <v>45748</v>
       </c>
     </row>
     <row r="108" spans="1:9">
-      <c r="A108" s="11">
+      <c r="A108" s="10">
         <v>87</v>
       </c>
-      <c r="B108" s="17" t="s">
+      <c r="B108" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C108" s="20"/>
-      <c r="D108" s="20" t="s">
+      <c r="C108" s="19"/>
+      <c r="D108" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E108" s="11">
+      <c r="E108" s="10">
         <v>2015</v>
       </c>
-      <c r="F108" s="11">
+      <c r="F108" s="10">
         <v>7.2</v>
       </c>
-      <c r="G108" s="12"/>
-      <c r="H108" s="20"/>
-      <c r="I108" s="20"/>
+      <c r="G108" s="11"/>
+      <c r="H108" s="19"/>
+      <c r="I108" s="19"/>
     </row>
     <row r="109" spans="1:9">
-      <c r="A109" s="11">
+      <c r="A109" s="10">
         <v>118</v>
       </c>
-      <c r="B109" s="17" t="s">
+      <c r="B109" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C109" s="20"/>
-      <c r="D109" s="20" t="s">
+      <c r="C109" s="19"/>
+      <c r="D109" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="E109" s="11">
+      <c r="E109" s="10">
         <v>2015</v>
       </c>
-      <c r="F109" s="11">
+      <c r="F109" s="10">
         <v>7.6</v>
       </c>
-      <c r="G109" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H109" s="11">
+      <c r="G109" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H109" s="10">
         <v>7</v>
       </c>
-      <c r="I109" s="20">
+      <c r="I109" s="19">
         <v>2023</v>
       </c>
     </row>
     <row r="110" spans="1:9">
-      <c r="A110" s="11">
+      <c r="A110" s="10">
         <v>86</v>
       </c>
-      <c r="B110" s="17" t="s">
+      <c r="B110" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C110" s="20"/>
-      <c r="D110" s="18" t="s">
+      <c r="C110" s="19"/>
+      <c r="D110" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="E110" s="11">
+      <c r="E110" s="10">
         <v>2016</v>
       </c>
-      <c r="F110" s="11">
+      <c r="F110" s="10">
         <v>7.6</v>
       </c>
-      <c r="G110" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H110" s="19">
+      <c r="G110" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H110" s="18">
         <v>7</v>
       </c>
-      <c r="I110" s="14" t="s">
+      <c r="I110" s="13" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="111" spans="1:9">
-      <c r="A111" s="11">
+      <c r="A111" s="10">
         <v>88</v>
       </c>
-      <c r="B111" s="17" t="s">
+      <c r="B111" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C111" s="20"/>
-      <c r="D111" s="20" t="s">
+      <c r="C111" s="19"/>
+      <c r="D111" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="E111" s="11">
+      <c r="E111" s="10">
         <v>2016</v>
       </c>
-      <c r="F111" s="11">
+      <c r="F111" s="10">
         <v>7.7</v>
       </c>
-      <c r="G111" s="12"/>
-      <c r="H111" s="20"/>
-      <c r="I111" s="20"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="19"/>
+      <c r="I111" s="19"/>
     </row>
     <row r="112" spans="1:9">
-      <c r="A112" s="11">
+      <c r="A112" s="10">
         <v>85</v>
       </c>
-      <c r="B112" s="26" t="s">
+      <c r="B112" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C112" s="27"/>
-      <c r="D112" s="27" t="s">
+      <c r="C112" s="26"/>
+      <c r="D112" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="E112" s="28">
+      <c r="E112" s="27">
         <v>2017</v>
       </c>
-      <c r="F112" s="28">
+      <c r="F112" s="27">
         <v>7.8</v>
       </c>
-      <c r="G112" s="29"/>
-      <c r="H112" s="27"/>
-      <c r="I112" s="27"/>
+      <c r="G112" s="28"/>
+      <c r="H112" s="26"/>
+      <c r="I112" s="26"/>
     </row>
     <row r="113" spans="1:9">
-      <c r="A113" s="11">
+      <c r="A113" s="10">
         <v>96</v>
       </c>
-      <c r="B113" s="17" t="s">
+      <c r="B113" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C113" s="20"/>
-      <c r="D113" s="20" t="s">
+      <c r="C113" s="19"/>
+      <c r="D113" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="E113" s="11">
+      <c r="E113" s="10">
         <v>2017</v>
       </c>
-      <c r="F113" s="11">
+      <c r="F113" s="10">
         <v>7.1</v>
       </c>
-      <c r="G113" s="12"/>
-      <c r="H113" s="20"/>
-      <c r="I113" s="20"/>
+      <c r="G113" s="11"/>
+      <c r="H113" s="19"/>
+      <c r="I113" s="19"/>
     </row>
     <row r="114" spans="1:9">
-      <c r="A114" s="11">
+      <c r="A114" s="10">
         <v>105</v>
       </c>
-      <c r="B114" s="17" t="s">
+      <c r="B114" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C114" s="20"/>
-      <c r="D114" s="20" t="s">
+      <c r="C114" s="19"/>
+      <c r="D114" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="E114" s="11">
+      <c r="E114" s="10">
         <v>2017</v>
       </c>
-      <c r="F114" s="11">
+      <c r="F114" s="10">
         <v>7.3</v>
       </c>
-      <c r="G114" s="12"/>
-      <c r="H114" s="20"/>
-      <c r="I114" s="20"/>
+      <c r="G114" s="11"/>
+      <c r="H114" s="19"/>
+      <c r="I114" s="19"/>
     </row>
     <row r="115" spans="1:9" ht="28.5">
-      <c r="A115" s="11">
+      <c r="A115" s="10">
         <v>34</v>
       </c>
-      <c r="B115" s="12" t="s">
+      <c r="B115" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C115" s="23" t="s">
+      <c r="C115" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="D115" s="12" t="s">
+      <c r="D115" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="E115" s="11">
+      <c r="E115" s="10">
         <v>2019</v>
       </c>
-      <c r="F115" s="11">
+      <c r="F115" s="10">
         <v>7.4</v>
       </c>
-      <c r="G115" s="12"/>
-      <c r="H115" s="11"/>
-      <c r="I115" s="14"/>
+      <c r="G115" s="11"/>
+      <c r="H115" s="10"/>
+      <c r="I115" s="13"/>
     </row>
     <row r="116" spans="1:9">
-      <c r="A116" s="11">
+      <c r="A116" s="10">
         <v>60</v>
       </c>
-      <c r="B116" s="17" t="s">
+      <c r="B116" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C116" s="20"/>
-      <c r="D116" s="20" t="s">
+      <c r="C116" s="19"/>
+      <c r="D116" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="E116" s="11">
+      <c r="E116" s="10">
         <v>2019</v>
       </c>
-      <c r="F116" s="11">
+      <c r="F116" s="10">
         <v>7.7</v>
       </c>
-      <c r="G116" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H116" s="19">
+      <c r="G116" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H116" s="18">
         <v>7</v>
       </c>
-      <c r="I116" s="16">
+      <c r="I116" s="15">
         <v>45748</v>
       </c>
     </row>
     <row r="117" spans="1:9">
-      <c r="A117" s="11">
+      <c r="A117" s="10">
         <v>119</v>
       </c>
-      <c r="B117" s="17" t="s">
+      <c r="B117" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C117" s="20" t="s">
+      <c r="C117" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D117" s="20" t="s">
+      <c r="D117" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="E117" s="11">
+      <c r="E117" s="10">
         <v>2019</v>
       </c>
-      <c r="F117" s="11">
+      <c r="F117" s="10">
         <v>8.6999999999999993</v>
       </c>
-      <c r="G117" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H117" s="11">
+      <c r="G117" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H117" s="10">
         <v>8</v>
       </c>
-      <c r="I117" s="34">
+      <c r="I117" s="33">
         <v>46260</v>
       </c>
     </row>
     <row r="118" spans="1:9">
-      <c r="A118" s="11">
+      <c r="A118" s="10">
         <v>129</v>
       </c>
-      <c r="B118" s="17" t="s">
+      <c r="B118" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="C118" s="20"/>
-      <c r="D118" s="20" t="s">
+      <c r="C118" s="19"/>
+      <c r="D118" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="E118" s="11">
+      <c r="E118" s="10">
         <v>2019</v>
       </c>
-      <c r="F118" s="11">
+      <c r="F118" s="10">
         <v>8.1</v>
       </c>
-      <c r="G118" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H118" s="11">
+      <c r="G118" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H118" s="10">
         <v>7.5</v>
       </c>
-      <c r="I118" s="21">
+      <c r="I118" s="20">
         <v>45778</v>
       </c>
     </row>
     <row r="119" spans="1:9">
-      <c r="A119" s="11">
+      <c r="A119" s="10">
         <v>61</v>
       </c>
-      <c r="B119" s="17" t="s">
+      <c r="B119" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C119" s="20"/>
-      <c r="D119" s="20" t="s">
+      <c r="C119" s="19"/>
+      <c r="D119" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="E119" s="11">
+      <c r="E119" s="10">
         <v>2020</v>
       </c>
-      <c r="F119" s="11">
+      <c r="F119" s="10">
         <v>7</v>
       </c>
-      <c r="G119" s="12"/>
-      <c r="H119" s="20"/>
-      <c r="I119" s="20"/>
+      <c r="G119" s="11"/>
+      <c r="H119" s="19"/>
+      <c r="I119" s="19"/>
     </row>
     <row r="120" spans="1:9">
-      <c r="A120" s="11">
+      <c r="A120" s="10">
         <v>100</v>
       </c>
-      <c r="B120" s="17" t="s">
+      <c r="B120" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C120" s="20"/>
-      <c r="D120" s="20" t="s">
+      <c r="C120" s="19"/>
+      <c r="D120" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E120" s="11">
+      <c r="E120" s="10">
         <v>2020</v>
       </c>
-      <c r="F120" s="11">
+      <c r="F120" s="10">
         <v>7.5</v>
       </c>
-      <c r="G120" s="12"/>
-      <c r="H120" s="20"/>
-      <c r="I120" s="20"/>
+      <c r="G120" s="11"/>
+      <c r="H120" s="19"/>
+      <c r="I120" s="19"/>
     </row>
     <row r="121" spans="1:9">
-      <c r="A121" s="11">
+      <c r="A121" s="10">
         <v>83</v>
       </c>
-      <c r="B121" s="17" t="s">
+      <c r="B121" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C121" s="20"/>
-      <c r="D121" s="20" t="s">
+      <c r="C121" s="19"/>
+      <c r="D121" s="19" t="s">
         <v>169</v>
       </c>
-      <c r="E121" s="11">
+      <c r="E121" s="10">
         <v>2021</v>
       </c>
-      <c r="F121" s="11">
+      <c r="F121" s="10">
         <v>7.7</v>
       </c>
-      <c r="G121" s="12"/>
-      <c r="H121" s="20"/>
-      <c r="I121" s="20"/>
+      <c r="G121" s="11"/>
+      <c r="H121" s="19"/>
+      <c r="I121" s="19"/>
     </row>
     <row r="122" spans="1:9">
-      <c r="A122" s="11">
+      <c r="A122" s="10">
         <v>98</v>
       </c>
-      <c r="B122" s="17" t="s">
+      <c r="B122" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C122" s="20"/>
-      <c r="D122" s="20" t="s">
+      <c r="C122" s="19"/>
+      <c r="D122" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="E122" s="11">
+      <c r="E122" s="10">
         <v>2021</v>
       </c>
-      <c r="F122" s="11">
+      <c r="F122" s="10">
         <v>7</v>
       </c>
-      <c r="G122" s="12"/>
-      <c r="H122" s="20"/>
-      <c r="I122" s="20"/>
+      <c r="G122" s="11"/>
+      <c r="H122" s="19"/>
+      <c r="I122" s="19"/>
     </row>
     <row r="123" spans="1:9">
-      <c r="A123" s="11">
+      <c r="A123" s="10">
         <v>120</v>
       </c>
-      <c r="B123" s="17" t="s">
+      <c r="B123" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C123" s="20"/>
-      <c r="D123" s="20" t="s">
+      <c r="C123" s="19"/>
+      <c r="D123" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="E123" s="11">
+      <c r="E123" s="10">
         <v>2021</v>
       </c>
-      <c r="F123" s="11">
+      <c r="F123" s="10">
         <v>7.7</v>
       </c>
-      <c r="G123" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H123" s="11">
+      <c r="G123" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H123" s="10">
         <v>7</v>
       </c>
-      <c r="I123" s="30" t="s">
+      <c r="I123" s="29" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="124" spans="1:9">
-      <c r="A124" s="11">
+      <c r="A124" s="10">
         <v>90</v>
       </c>
-      <c r="B124" s="17" t="s">
+      <c r="B124" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="C124" s="20"/>
-      <c r="D124" s="20" t="s">
+      <c r="C124" s="19"/>
+      <c r="D124" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="E124" s="11">
+      <c r="E124" s="10">
         <v>2022</v>
       </c>
-      <c r="F124" s="11">
+      <c r="F124" s="10">
         <v>7.1</v>
       </c>
-      <c r="G124" s="12"/>
-      <c r="H124" s="20"/>
-      <c r="I124" s="20"/>
+      <c r="G124" s="11"/>
+      <c r="H124" s="19"/>
+      <c r="I124" s="19"/>
     </row>
     <row r="125" spans="1:9">
-      <c r="A125" s="11">
+      <c r="A125" s="10">
         <v>121</v>
       </c>
-      <c r="B125" s="17" t="s">
+      <c r="B125" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C125" s="20"/>
-      <c r="D125" s="20" t="s">
+      <c r="C125" s="19"/>
+      <c r="D125" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="E125" s="11">
+      <c r="E125" s="10">
         <v>2022</v>
       </c>
-      <c r="F125" s="11">
+      <c r="F125" s="10">
         <v>7.9</v>
       </c>
-      <c r="G125" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H125" s="11">
+      <c r="G125" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H125" s="10">
         <v>7</v>
       </c>
-      <c r="I125" s="21">
+      <c r="I125" s="20">
         <v>44713</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="29.25">
-      <c r="A126" s="11">
+      <c r="A126" s="10">
         <v>122</v>
       </c>
-      <c r="B126" s="17" t="s">
+      <c r="B126" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C126" s="20"/>
-      <c r="D126" s="18" t="s">
+      <c r="C126" s="19"/>
+      <c r="D126" s="17" t="s">
         <v>174</v>
       </c>
-      <c r="E126" s="11">
+      <c r="E126" s="10">
         <v>2022</v>
       </c>
-      <c r="F126" s="11">
+      <c r="F126" s="10">
         <v>7.2</v>
       </c>
-      <c r="G126" s="12"/>
-      <c r="H126" s="11"/>
-      <c r="I126" s="20"/>
+      <c r="G126" s="11"/>
+      <c r="H126" s="10"/>
+      <c r="I126" s="19"/>
     </row>
     <row r="127" spans="1:9" ht="42.75">
-      <c r="A127" s="11">
+      <c r="A127" s="10">
         <v>35</v>
       </c>
-      <c r="B127" s="12" t="s">
+      <c r="B127" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C127" s="23" t="s">
+      <c r="C127" s="22" t="s">
         <v>175</v>
       </c>
-      <c r="D127" s="12" t="s">
+      <c r="D127" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E127" s="11">
+      <c r="E127" s="10">
         <v>2023</v>
       </c>
-      <c r="F127" s="11">
+      <c r="F127" s="10">
         <v>7.1</v>
       </c>
-      <c r="G127" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H127" s="19">
+      <c r="G127" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H127" s="18">
         <v>8</v>
       </c>
-      <c r="I127" s="16">
+      <c r="I127" s="15">
         <v>45717</v>
       </c>
     </row>
     <row r="128" spans="1:9">
-      <c r="A128" s="11">
+      <c r="A128" s="10">
         <v>64</v>
       </c>
-      <c r="B128" s="17" t="s">
+      <c r="B128" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C128" s="20"/>
-      <c r="D128" s="20" t="s">
+      <c r="C128" s="19"/>
+      <c r="D128" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="E128" s="11">
+      <c r="E128" s="10">
         <v>2023</v>
       </c>
-      <c r="F128" s="11">
+      <c r="F128" s="10">
         <v>6.6</v>
       </c>
-      <c r="G128" s="12"/>
-      <c r="H128" s="20"/>
-      <c r="I128" s="20"/>
+      <c r="G128" s="11"/>
+      <c r="H128" s="19"/>
+      <c r="I128" s="19"/>
     </row>
     <row r="129" spans="1:9">
-      <c r="A129" s="11">
+      <c r="A129" s="10">
         <v>110</v>
       </c>
-      <c r="B129" s="17" t="s">
+      <c r="B129" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C129" s="20"/>
-      <c r="D129" s="20" t="s">
+      <c r="C129" s="19"/>
+      <c r="D129" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="E129" s="11">
+      <c r="E129" s="10">
         <v>2023</v>
       </c>
-      <c r="F129" s="11">
+      <c r="F129" s="10">
         <v>8.1</v>
       </c>
-      <c r="G129" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H129" s="19">
+      <c r="G129" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" s="18">
         <v>7</v>
       </c>
-      <c r="I129" s="16">
+      <c r="I129" s="15">
         <v>45231</v>
       </c>
     </row>
     <row r="130" spans="1:9">
-      <c r="A130" s="11">
+      <c r="A130" s="10">
         <v>84</v>
       </c>
-      <c r="B130" s="17" t="s">
+      <c r="B130" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="C130" s="20"/>
-      <c r="D130" s="20" t="s">
+      <c r="C130" s="19"/>
+      <c r="D130" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="E130" s="11">
+      <c r="E130" s="10">
         <v>2024</v>
       </c>
-      <c r="F130" s="11">
+      <c r="F130" s="10">
         <v>8.1999999999999993</v>
       </c>
-      <c r="G130" s="12"/>
-      <c r="H130" s="20"/>
-      <c r="I130" s="20"/>
+      <c r="G130" s="11"/>
+      <c r="H130" s="19"/>
+      <c r="I130" s="19"/>
     </row>
     <row r="131" spans="1:9">
-      <c r="A131" s="11">
+      <c r="A131" s="10">
         <v>123</v>
       </c>
-      <c r="B131" s="17" t="s">
+      <c r="B131" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C131" s="20"/>
-      <c r="D131" s="20" t="s">
+      <c r="C131" s="19"/>
+      <c r="D131" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="E131" s="11">
+      <c r="E131" s="10">
         <v>2024</v>
       </c>
-      <c r="F131" s="11">
+      <c r="F131" s="10">
         <v>7.3</v>
       </c>
-      <c r="G131" s="12"/>
-      <c r="H131" s="11"/>
-      <c r="I131" s="20"/>
+      <c r="G131" s="11"/>
+      <c r="H131" s="10"/>
+      <c r="I131" s="19"/>
     </row>
     <row r="132" spans="1:9">
-      <c r="A132" s="11">
+      <c r="A132" s="10">
         <v>93</v>
       </c>
-      <c r="B132" s="17" t="s">
+      <c r="B132" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C132" s="20"/>
-      <c r="D132" s="20" t="s">
+      <c r="C132" s="19"/>
+      <c r="D132" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="E132" s="11">
+      <c r="E132" s="10">
         <v>2025</v>
       </c>
-      <c r="F132" s="11">
+      <c r="F132" s="10">
         <v>7</v>
       </c>
-      <c r="G132" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H132" s="19">
+      <c r="G132" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" s="18">
         <v>7</v>
       </c>
-      <c r="I132" s="31" t="s">
+      <c r="I132" s="30" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="133" spans="1:9">
-      <c r="A133" s="11">
+      <c r="A133" s="10">
         <v>124</v>
       </c>
-      <c r="B133" s="17" t="s">
+      <c r="B133" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C133" s="20"/>
-      <c r="D133" s="20" t="s">
+      <c r="C133" s="19"/>
+      <c r="D133" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="E133" s="11">
+      <c r="E133" s="10">
         <v>2026</v>
       </c>
-      <c r="F133" s="11">
+      <c r="F133" s="10">
         <v>6.6</v>
       </c>
-      <c r="G133" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H133" s="11">
+      <c r="G133" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" s="10">
         <v>6</v>
       </c>
-      <c r="I133" s="24">
+      <c r="I133" s="23">
         <v>46171</v>
       </c>
     </row>
     <row r="134" spans="1:9">
-      <c r="A134" s="11">
+      <c r="A134" s="10">
         <v>45</v>
       </c>
-      <c r="B134" s="17" t="s">
+      <c r="B134" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="C134" s="20"/>
-      <c r="D134" s="20" t="s">
+      <c r="C134" s="19"/>
+      <c r="D134" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="E134" s="11" t="s">
+      <c r="E134" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="F134" s="11">
+      <c r="F134" s="10">
         <v>8.4</v>
       </c>
-      <c r="G134" s="12"/>
-      <c r="H134" s="20"/>
-      <c r="I134" s="20"/>
+      <c r="G134" s="11"/>
+      <c r="H134" s="19"/>
+      <c r="I134" s="19"/>
     </row>
     <row r="135" spans="1:9">
-      <c r="A135" s="11">
+      <c r="A135" s="10">
         <v>132</v>
       </c>
-      <c r="B135" s="17"/>
-      <c r="C135" s="20"/>
-      <c r="D135" s="20" t="s">
+      <c r="B135" s="16"/>
+      <c r="C135" s="19"/>
+      <c r="D135" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="E135" s="11"/>
-      <c r="F135" s="11"/>
-      <c r="G135" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H135" s="11"/>
-      <c r="I135" s="21">
+      <c r="E135" s="10"/>
+      <c r="F135" s="10"/>
+      <c r="G135" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" s="10"/>
+      <c r="I135" s="20">
         <v>45809</v>
       </c>
     </row>
     <row r="136" spans="1:9">
-      <c r="A136" s="11">
+      <c r="A136" s="10">
         <v>133</v>
       </c>
-      <c r="B136" s="17"/>
-      <c r="C136" s="20"/>
-      <c r="D136" s="20" t="s">
+      <c r="B136" s="16"/>
+      <c r="C136" s="19"/>
+      <c r="D136" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
-      <c r="G136" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H136" s="11"/>
-      <c r="I136" s="21">
+      <c r="E136" s="10"/>
+      <c r="F136" s="10"/>
+      <c r="G136" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" s="10"/>
+      <c r="I136" s="20">
         <v>45809</v>
       </c>
     </row>
     <row r="137" spans="1:9">
-      <c r="A137" s="11">
+      <c r="A137" s="10">
         <v>134</v>
       </c>
-      <c r="B137" s="17"/>
-      <c r="C137" s="20"/>
-      <c r="D137" s="20" t="s">
+      <c r="B137" s="16"/>
+      <c r="C137" s="19"/>
+      <c r="D137" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="E137" s="11"/>
-      <c r="F137" s="11"/>
-      <c r="G137" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H137" s="11"/>
-      <c r="I137" s="21">
+      <c r="E137" s="10"/>
+      <c r="F137" s="10"/>
+      <c r="G137" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H137" s="10"/>
+      <c r="I137" s="20">
         <v>45809</v>
       </c>
     </row>
     <row r="138" spans="1:9">
-      <c r="A138" s="11">
+      <c r="A138" s="10">
         <v>135</v>
       </c>
-      <c r="B138" s="17"/>
-      <c r="C138" s="20"/>
-      <c r="D138" s="20" t="s">
+      <c r="B138" s="16"/>
+      <c r="C138" s="19"/>
+      <c r="D138" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="E138" s="11"/>
-      <c r="F138" s="11"/>
-      <c r="G138" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H138" s="11"/>
-      <c r="I138" s="21">
+      <c r="E138" s="10"/>
+      <c r="F138" s="10"/>
+      <c r="G138" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H138" s="10"/>
+      <c r="I138" s="20">
         <v>45839</v>
       </c>
     </row>
     <row r="139" spans="1:9">
-      <c r="A139" s="11">
+      <c r="A139" s="10">
         <v>136</v>
       </c>
-      <c r="B139" s="17"/>
-      <c r="C139" s="20"/>
-      <c r="D139" s="20" t="s">
+      <c r="B139" s="16"/>
+      <c r="C139" s="19"/>
+      <c r="D139" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
-      <c r="G139" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H139" s="11"/>
-      <c r="I139" s="21">
+      <c r="E139" s="10"/>
+      <c r="F139" s="10"/>
+      <c r="G139" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H139" s="10"/>
+      <c r="I139" s="20">
         <v>46054</v>
       </c>
     </row>
     <row r="140" spans="1:9">
-      <c r="A140" s="11">
+      <c r="A140" s="10">
         <v>137</v>
       </c>
-      <c r="B140" s="17"/>
-      <c r="C140" s="20"/>
-      <c r="D140" s="20" t="s">
+      <c r="B140" s="16"/>
+      <c r="C140" s="19"/>
+      <c r="D140" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="E140" s="11"/>
-      <c r="F140" s="11"/>
-      <c r="G140" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H140" s="11"/>
-      <c r="I140" s="21">
+      <c r="E140" s="10"/>
+      <c r="F140" s="10"/>
+      <c r="G140" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H140" s="10"/>
+      <c r="I140" s="20">
         <v>45839</v>
       </c>
     </row>
     <row r="141" spans="1:9">
-      <c r="A141" s="11">
+      <c r="A141" s="10">
         <v>138</v>
       </c>
-      <c r="B141" s="17"/>
-      <c r="C141" s="20"/>
-      <c r="D141" s="20" t="s">
+      <c r="B141" s="16"/>
+      <c r="C141" s="19"/>
+      <c r="D141" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="E141" s="11"/>
-      <c r="F141" s="11"/>
-      <c r="G141" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H141" s="11"/>
-      <c r="I141" s="21">
+      <c r="E141" s="10"/>
+      <c r="F141" s="10"/>
+      <c r="G141" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H141" s="10"/>
+      <c r="I141" s="20">
         <v>45839</v>
       </c>
     </row>
     <row r="142" spans="1:9">
-      <c r="A142" s="11">
+      <c r="A142" s="10">
         <v>139</v>
       </c>
-      <c r="B142" s="17"/>
-      <c r="C142" s="20"/>
-      <c r="D142" s="20" t="s">
+      <c r="B142" s="16"/>
+      <c r="C142" s="19"/>
+      <c r="D142" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="E142" s="11"/>
-      <c r="F142" s="11"/>
-      <c r="G142" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H142" s="11"/>
-      <c r="I142" s="21">
+      <c r="E142" s="10"/>
+      <c r="F142" s="10"/>
+      <c r="G142" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H142" s="10"/>
+      <c r="I142" s="20">
         <v>45839</v>
       </c>
     </row>
     <row r="143" spans="1:9">
-      <c r="A143" s="11">
+      <c r="A143" s="10">
         <v>140</v>
       </c>
-      <c r="B143" s="17"/>
-      <c r="C143" s="20"/>
-      <c r="D143" s="20" t="s">
+      <c r="B143" s="16"/>
+      <c r="C143" s="19"/>
+      <c r="D143" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
-      <c r="G143" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H143" s="11"/>
-      <c r="I143" s="21">
+      <c r="E143" s="10"/>
+      <c r="F143" s="10"/>
+      <c r="G143" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H143" s="10"/>
+      <c r="I143" s="20">
         <v>45839</v>
       </c>
     </row>
     <row r="144" spans="1:9">
-      <c r="A144" s="11">
+      <c r="A144" s="10">
         <v>141</v>
       </c>
-      <c r="B144" s="17"/>
-      <c r="C144" s="20"/>
-      <c r="D144" s="20" t="s">
+      <c r="B144" s="16"/>
+      <c r="C144" s="19"/>
+      <c r="D144" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="E144" s="11"/>
-      <c r="F144" s="11"/>
-      <c r="G144" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H144" s="11"/>
-      <c r="I144" s="24">
+      <c r="E144" s="10"/>
+      <c r="F144" s="10"/>
+      <c r="G144" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H144" s="10"/>
+      <c r="I144" s="23">
         <v>45859</v>
       </c>
     </row>
     <row r="145" spans="1:9">
-      <c r="A145" s="11">
+      <c r="A145" s="10">
         <v>142</v>
       </c>
-      <c r="B145" s="17"/>
-      <c r="C145" s="20" t="s">
+      <c r="B145" s="16"/>
+      <c r="C145" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D145" s="20" t="s">
+      <c r="D145" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="E145" s="11"/>
-      <c r="F145" s="11"/>
-      <c r="G145" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H145" s="11"/>
-      <c r="I145" s="24"/>
+      <c r="E145" s="10"/>
+      <c r="F145" s="10"/>
+      <c r="G145" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H145" s="10"/>
+      <c r="I145" s="23"/>
     </row>
     <row r="146" spans="1:9">
-      <c r="A146" s="11">
+      <c r="A146" s="10">
         <v>143</v>
       </c>
-      <c r="B146" s="17"/>
-      <c r="C146" s="20"/>
-      <c r="D146" s="20" t="s">
+      <c r="B146" s="16"/>
+      <c r="C146" s="19"/>
+      <c r="D146" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="E146" s="11"/>
-      <c r="F146" s="11"/>
-      <c r="G146" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H146" s="11"/>
-      <c r="I146" s="24"/>
+      <c r="E146" s="10"/>
+      <c r="F146" s="10"/>
+      <c r="G146" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H146" s="10"/>
+      <c r="I146" s="23"/>
     </row>
     <row r="147" spans="1:9">
-      <c r="A147" s="11">
+      <c r="A147" s="10">
         <v>144</v>
       </c>
-      <c r="B147" s="17"/>
-      <c r="C147" s="20"/>
-      <c r="D147" s="20" t="s">
+      <c r="B147" s="16"/>
+      <c r="C147" s="19"/>
+      <c r="D147" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="E147" s="11"/>
-      <c r="F147" s="11"/>
-      <c r="G147" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H147" s="11"/>
-      <c r="I147" s="24"/>
+      <c r="E147" s="10"/>
+      <c r="F147" s="10"/>
+      <c r="G147" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H147" s="10"/>
+      <c r="I147" s="23"/>
     </row>
     <row r="148" spans="1:9">
-      <c r="A148" s="11">
+      <c r="A148" s="10">
         <v>145</v>
       </c>
-      <c r="B148" s="17"/>
-      <c r="C148" s="20"/>
-      <c r="D148" s="20" t="s">
+      <c r="B148" s="16"/>
+      <c r="C148" s="19"/>
+      <c r="D148" s="19" t="s">
         <v>198</v>
       </c>
-      <c r="E148" s="11"/>
-      <c r="F148" s="11"/>
-      <c r="G148" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H148" s="11"/>
-      <c r="I148" s="24"/>
+      <c r="E148" s="10"/>
+      <c r="F148" s="10"/>
+      <c r="G148" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H148" s="10"/>
+      <c r="I148" s="23"/>
     </row>
     <row r="149" spans="1:9">
-      <c r="A149" s="11">
+      <c r="A149" s="10">
         <v>146</v>
       </c>
-      <c r="B149" s="17"/>
-      <c r="C149" s="20" t="s">
+      <c r="B149" s="16"/>
+      <c r="C149" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D149" s="20" t="s">
+      <c r="D149" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="E149" s="11"/>
-      <c r="F149" s="11"/>
-      <c r="G149" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H149" s="11"/>
-      <c r="I149" s="24"/>
+      <c r="E149" s="10"/>
+      <c r="F149" s="10"/>
+      <c r="G149" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H149" s="10"/>
+      <c r="I149" s="23"/>
     </row>
     <row r="150" spans="1:9">
-      <c r="A150" s="11">
+      <c r="A150" s="10">
         <v>147</v>
       </c>
-      <c r="B150" s="17"/>
-      <c r="C150" s="20"/>
-      <c r="D150" s="20" t="s">
+      <c r="B150" s="16"/>
+      <c r="C150" s="19"/>
+      <c r="D150" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="E150" s="11"/>
-      <c r="F150" s="11"/>
-      <c r="G150" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H150" s="11"/>
-      <c r="I150" s="24"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
+      <c r="G150" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H150" s="10"/>
+      <c r="I150" s="23"/>
     </row>
     <row r="151" spans="1:9">
-      <c r="A151" s="11">
+      <c r="A151" s="10">
         <v>148</v>
       </c>
-      <c r="B151" s="17"/>
-      <c r="C151" s="20"/>
-      <c r="D151" s="20" t="s">
+      <c r="B151" s="16"/>
+      <c r="C151" s="19"/>
+      <c r="D151" s="19" t="s">
         <v>201</v>
       </c>
-      <c r="E151" s="11"/>
-      <c r="F151" s="11"/>
-      <c r="G151" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H151" s="11"/>
-      <c r="I151" s="24"/>
+      <c r="E151" s="10"/>
+      <c r="F151" s="10"/>
+      <c r="G151" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H151" s="10"/>
+      <c r="I151" s="23"/>
     </row>
     <row r="152" spans="1:9">
-      <c r="A152" s="11">
+      <c r="A152" s="10">
         <v>149</v>
       </c>
-      <c r="B152" s="17"/>
-      <c r="C152" s="20"/>
-      <c r="D152" s="20" t="s">
+      <c r="B152" s="16"/>
+      <c r="C152" s="19"/>
+      <c r="D152" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="E152" s="11"/>
-      <c r="F152" s="11"/>
-      <c r="G152" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H152" s="11"/>
-      <c r="I152" s="24"/>
+      <c r="E152" s="10"/>
+      <c r="F152" s="10"/>
+      <c r="G152" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H152" s="10"/>
+      <c r="I152" s="23"/>
     </row>
     <row r="153" spans="1:9">
-      <c r="A153" s="11">
+      <c r="A153" s="10">
         <v>150</v>
       </c>
-      <c r="B153" s="17"/>
-      <c r="C153" s="20"/>
-      <c r="D153" s="20" t="s">
+      <c r="B153" s="16"/>
+      <c r="C153" s="19"/>
+      <c r="D153" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="E153" s="11"/>
-      <c r="F153" s="11"/>
-      <c r="G153" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H153" s="11"/>
-      <c r="I153" s="24"/>
+      <c r="E153" s="10"/>
+      <c r="F153" s="10"/>
+      <c r="G153" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H153" s="10"/>
+      <c r="I153" s="23"/>
     </row>
     <row r="154" spans="1:9">
-      <c r="A154" s="11">
+      <c r="A154" s="10">
         <v>151</v>
       </c>
-      <c r="B154" s="17"/>
-      <c r="C154" s="20"/>
-      <c r="D154" s="20" t="s">
+      <c r="B154" s="16"/>
+      <c r="C154" s="19"/>
+      <c r="D154" s="19" t="s">
         <v>204</v>
       </c>
-      <c r="E154" s="11"/>
-      <c r="F154" s="11"/>
-      <c r="G154" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H154" s="11"/>
-      <c r="I154" s="24"/>
+      <c r="E154" s="10"/>
+      <c r="F154" s="10"/>
+      <c r="G154" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H154" s="10"/>
+      <c r="I154" s="23"/>
     </row>
     <row r="155" spans="1:9">
-      <c r="A155" s="11">
+      <c r="A155" s="10">
         <v>152</v>
       </c>
-      <c r="B155" s="17"/>
-      <c r="C155" s="20"/>
-      <c r="D155" s="20" t="s">
+      <c r="B155" s="16"/>
+      <c r="C155" s="19"/>
+      <c r="D155" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="E155" s="11"/>
-      <c r="F155" s="11"/>
-      <c r="G155" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H155" s="11"/>
-      <c r="I155" s="24"/>
+      <c r="E155" s="10"/>
+      <c r="F155" s="10"/>
+      <c r="G155" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H155" s="10"/>
+      <c r="I155" s="23"/>
     </row>
     <row r="156" spans="1:9">
-      <c r="A156" s="11">
+      <c r="A156" s="10">
         <v>153</v>
       </c>
-      <c r="B156" s="17"/>
-      <c r="C156" s="20"/>
-      <c r="D156" s="20" t="s">
+      <c r="B156" s="16"/>
+      <c r="C156" s="19"/>
+      <c r="D156" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="E156" s="11"/>
-      <c r="F156" s="11"/>
-      <c r="G156" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H156" s="11"/>
-      <c r="I156" s="24"/>
+      <c r="E156" s="10"/>
+      <c r="F156" s="10"/>
+      <c r="G156" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H156" s="10"/>
+      <c r="I156" s="23"/>
     </row>
     <row r="157" spans="1:9">
-      <c r="A157" s="11">
+      <c r="A157" s="10">
         <v>154</v>
       </c>
-      <c r="B157" s="17"/>
-      <c r="C157" s="20"/>
-      <c r="D157" s="20" t="s">
+      <c r="B157" s="16"/>
+      <c r="C157" s="19"/>
+      <c r="D157" s="19" t="s">
         <v>207</v>
       </c>
-      <c r="E157" s="11"/>
-      <c r="F157" s="11"/>
-      <c r="G157" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H157" s="11"/>
-      <c r="I157" s="24"/>
+      <c r="E157" s="10"/>
+      <c r="F157" s="10"/>
+      <c r="G157" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H157" s="10"/>
+      <c r="I157" s="23"/>
     </row>
     <row r="158" spans="1:9">
-      <c r="A158" s="11">
+      <c r="A158" s="10">
         <v>155</v>
       </c>
-      <c r="B158" s="17"/>
-      <c r="C158" s="20"/>
-      <c r="D158" s="20" t="s">
+      <c r="B158" s="16"/>
+      <c r="C158" s="19"/>
+      <c r="D158" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="E158" s="11"/>
-      <c r="F158" s="11"/>
-      <c r="G158" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H158" s="11"/>
-      <c r="I158" s="24"/>
+      <c r="E158" s="10"/>
+      <c r="F158" s="10"/>
+      <c r="G158" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H158" s="10"/>
+      <c r="I158" s="23"/>
     </row>
     <row r="159" spans="1:9">
-      <c r="A159" s="11">
+      <c r="A159" s="10">
         <v>156</v>
       </c>
-      <c r="B159" s="17"/>
-      <c r="C159" s="20"/>
-      <c r="D159" s="20" t="s">
+      <c r="B159" s="16"/>
+      <c r="C159" s="19"/>
+      <c r="D159" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="E159" s="11"/>
-      <c r="F159" s="11"/>
-      <c r="G159" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H159" s="11"/>
-      <c r="I159" s="24"/>
+      <c r="E159" s="10"/>
+      <c r="F159" s="10"/>
+      <c r="G159" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H159" s="10"/>
+      <c r="I159" s="23"/>
     </row>
     <row r="160" spans="1:9">
-      <c r="A160" s="11">
+      <c r="A160" s="10">
         <v>157</v>
       </c>
-      <c r="B160" s="17"/>
-      <c r="C160" s="20"/>
-      <c r="D160" s="20" t="s">
+      <c r="B160" s="16"/>
+      <c r="C160" s="19"/>
+      <c r="D160" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="E160" s="11"/>
-      <c r="F160" s="11"/>
-      <c r="G160" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H160" s="11"/>
-      <c r="I160" s="24"/>
+      <c r="E160" s="10"/>
+      <c r="F160" s="10"/>
+      <c r="G160" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H160" s="10"/>
+      <c r="I160" s="23"/>
     </row>
     <row r="161" spans="1:9">
-      <c r="A161" s="11">
+      <c r="A161" s="10">
         <v>158</v>
       </c>
-      <c r="B161" s="17"/>
-      <c r="C161" s="20"/>
-      <c r="D161" s="20" t="s">
+      <c r="B161" s="16"/>
+      <c r="C161" s="19"/>
+      <c r="D161" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="E161" s="11"/>
-      <c r="F161" s="11"/>
-      <c r="G161" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H161" s="11"/>
-      <c r="I161" s="24"/>
+      <c r="E161" s="10"/>
+      <c r="F161" s="10"/>
+      <c r="G161" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H161" s="10"/>
+      <c r="I161" s="23"/>
     </row>
     <row r="162" spans="1:9">
-      <c r="A162" s="11">
+      <c r="A162" s="10">
         <v>159</v>
       </c>
-      <c r="B162" s="17"/>
-      <c r="C162" s="20"/>
-      <c r="D162" s="20" t="s">
+      <c r="B162" s="16"/>
+      <c r="C162" s="19"/>
+      <c r="D162" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="E162" s="11"/>
-      <c r="F162" s="11"/>
-      <c r="G162" s="12"/>
-      <c r="H162" s="11"/>
-      <c r="I162" s="24"/>
+      <c r="E162" s="10"/>
+      <c r="F162" s="10"/>
+      <c r="G162" s="11"/>
+      <c r="H162" s="10"/>
+      <c r="I162" s="23"/>
     </row>
     <row r="163" spans="1:9">
-      <c r="A163" s="11">
+      <c r="A163" s="10">
         <v>160</v>
       </c>
-      <c r="B163" s="17"/>
-      <c r="C163" s="20"/>
-      <c r="D163" s="20" t="s">
+      <c r="B163" s="16"/>
+      <c r="C163" s="19"/>
+      <c r="D163" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="E163" s="11"/>
-      <c r="F163" s="11"/>
-      <c r="G163" s="12"/>
-      <c r="H163" s="11"/>
-      <c r="I163" s="24"/>
+      <c r="E163" s="10"/>
+      <c r="F163" s="10"/>
+      <c r="G163" s="11"/>
+      <c r="H163" s="10"/>
+      <c r="I163" s="23"/>
     </row>
     <row r="164" spans="1:9">
-      <c r="A164" s="11">
+      <c r="A164" s="10">
         <v>161</v>
       </c>
-      <c r="B164" s="17"/>
-      <c r="C164" s="20"/>
-      <c r="D164" s="20" t="s">
+      <c r="B164" s="16"/>
+      <c r="C164" s="19"/>
+      <c r="D164" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="E164" s="11"/>
-      <c r="F164" s="11"/>
-      <c r="G164" s="12"/>
-      <c r="H164" s="11"/>
-      <c r="I164" s="24"/>
+      <c r="E164" s="10"/>
+      <c r="F164" s="10"/>
+      <c r="G164" s="11"/>
+      <c r="H164" s="10"/>
+      <c r="I164" s="23"/>
     </row>
     <row r="165" spans="1:9">
-      <c r="A165" s="11">
+      <c r="A165" s="10">
         <v>162</v>
       </c>
-      <c r="B165" s="17"/>
-      <c r="C165" s="20"/>
-      <c r="D165" s="20" t="s">
+      <c r="B165" s="16"/>
+      <c r="C165" s="19"/>
+      <c r="D165" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="E165" s="11"/>
-      <c r="F165" s="11"/>
-      <c r="G165" s="12"/>
-      <c r="H165" s="11"/>
-      <c r="I165" s="24"/>
+      <c r="E165" s="10"/>
+      <c r="F165" s="10"/>
+      <c r="G165" s="11"/>
+      <c r="H165" s="10"/>
+      <c r="I165" s="23"/>
     </row>
     <row r="166" spans="1:9">
-      <c r="A166" s="11">
+      <c r="A166" s="10">
         <v>163</v>
       </c>
-      <c r="B166" s="17"/>
-      <c r="C166" s="20"/>
-      <c r="D166" s="20" t="s">
+      <c r="B166" s="16"/>
+      <c r="C166" s="19"/>
+      <c r="D166" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="E166" s="11"/>
-      <c r="F166" s="11"/>
-      <c r="G166" s="12"/>
-      <c r="H166" s="11"/>
-      <c r="I166" s="24"/>
+      <c r="E166" s="10"/>
+      <c r="F166" s="10"/>
+      <c r="G166" s="11"/>
+      <c r="H166" s="10"/>
+      <c r="I166" s="23"/>
     </row>
     <row r="167" spans="1:9">
-      <c r="A167" s="11">
+      <c r="A167" s="10">
         <v>164</v>
       </c>
-      <c r="B167" s="17"/>
-      <c r="C167" s="20"/>
-      <c r="D167" s="20" t="s">
+      <c r="B167" s="16"/>
+      <c r="C167" s="19"/>
+      <c r="D167" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="E167" s="11"/>
-      <c r="F167" s="11"/>
-      <c r="G167" s="12"/>
-      <c r="H167" s="11"/>
-      <c r="I167" s="24"/>
+      <c r="E167" s="10"/>
+      <c r="F167" s="10"/>
+      <c r="G167" s="11"/>
+      <c r="H167" s="10"/>
+      <c r="I167" s="23"/>
     </row>
     <row r="168" spans="1:9">
-      <c r="A168" s="11">
+      <c r="A168" s="10">
         <v>165</v>
       </c>
-      <c r="B168" s="17"/>
-      <c r="C168" s="20"/>
-      <c r="D168" s="20" t="s">
+      <c r="B168" s="16"/>
+      <c r="C168" s="19"/>
+      <c r="D168" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="E168" s="11"/>
-      <c r="F168" s="11"/>
-      <c r="G168" s="12"/>
-      <c r="H168" s="11"/>
-      <c r="I168" s="24"/>
+      <c r="E168" s="10"/>
+      <c r="F168" s="10"/>
+      <c r="G168" s="11"/>
+      <c r="H168" s="10"/>
+      <c r="I168" s="23"/>
     </row>
     <row r="169" spans="1:9">
-      <c r="A169" s="11">
+      <c r="A169" s="10">
         <v>166</v>
       </c>
-      <c r="B169" s="17"/>
-      <c r="C169" s="20"/>
-      <c r="D169" s="20" t="s">
+      <c r="B169" s="16"/>
+      <c r="C169" s="19"/>
+      <c r="D169" s="19" t="s">
         <v>219</v>
       </c>
-      <c r="E169" s="11"/>
-      <c r="F169" s="11"/>
-      <c r="G169" s="12"/>
-      <c r="H169" s="11"/>
-      <c r="I169" s="24"/>
+      <c r="E169" s="10"/>
+      <c r="F169" s="10"/>
+      <c r="G169" s="11"/>
+      <c r="H169" s="10"/>
+      <c r="I169" s="23"/>
     </row>
     <row r="170" spans="1:9">
-      <c r="A170" s="11">
+      <c r="A170" s="10">
         <v>167</v>
       </c>
-      <c r="B170" s="17"/>
-      <c r="C170" s="20"/>
-      <c r="D170" s="20" t="s">
+      <c r="B170" s="16"/>
+      <c r="C170" s="19"/>
+      <c r="D170" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="E170" s="11"/>
-      <c r="F170" s="11"/>
-      <c r="G170" s="12"/>
-      <c r="H170" s="11"/>
-      <c r="I170" s="24"/>
+      <c r="E170" s="10"/>
+      <c r="F170" s="10"/>
+      <c r="G170" s="11"/>
+      <c r="H170" s="10"/>
+      <c r="I170" s="23"/>
     </row>
     <row r="171" spans="1:9">
-      <c r="A171" s="11">
+      <c r="A171" s="10">
         <v>168</v>
       </c>
-      <c r="B171" s="17"/>
-      <c r="C171" s="20"/>
-      <c r="D171" s="20" t="s">
+      <c r="B171" s="16"/>
+      <c r="C171" s="19"/>
+      <c r="D171" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="E171" s="11"/>
-      <c r="F171" s="11"/>
-      <c r="G171" s="12"/>
-      <c r="H171" s="11"/>
-      <c r="I171" s="24"/>
+      <c r="E171" s="10"/>
+      <c r="F171" s="10"/>
+      <c r="G171" s="11"/>
+      <c r="H171" s="10"/>
+      <c r="I171" s="23"/>
     </row>
     <row r="172" spans="1:9">
-      <c r="A172" s="11">
+      <c r="A172" s="10">
         <v>169</v>
       </c>
-      <c r="B172" s="17"/>
-      <c r="C172" s="20"/>
-      <c r="D172" s="20" t="s">
+      <c r="B172" s="16"/>
+      <c r="C172" s="19"/>
+      <c r="D172" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="E172" s="11"/>
-      <c r="F172" s="11"/>
-      <c r="G172" s="12"/>
-      <c r="H172" s="11"/>
-      <c r="I172" s="24"/>
+      <c r="E172" s="10"/>
+      <c r="F172" s="10"/>
+      <c r="G172" s="11"/>
+      <c r="H172" s="10"/>
+      <c r="I172" s="23"/>
     </row>
     <row r="173" spans="1:9">
-      <c r="A173" s="11">
+      <c r="A173" s="10">
         <v>170</v>
       </c>
-      <c r="B173" s="17"/>
-      <c r="C173" s="20"/>
-      <c r="D173" s="20" t="s">
+      <c r="B173" s="16"/>
+      <c r="C173" s="19"/>
+      <c r="D173" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="E173" s="11"/>
-      <c r="F173" s="11"/>
-      <c r="G173" s="12"/>
-      <c r="H173" s="11"/>
-      <c r="I173" s="24"/>
+      <c r="E173" s="10"/>
+      <c r="F173" s="10"/>
+      <c r="G173" s="11"/>
+      <c r="H173" s="10"/>
+      <c r="I173" s="23"/>
     </row>
     <row r="174" spans="1:9">
-      <c r="A174" s="11">
+      <c r="A174" s="10">
         <v>171</v>
       </c>
-      <c r="B174" s="17"/>
-      <c r="C174" s="20"/>
-      <c r="D174" s="20" t="s">
+      <c r="B174" s="16"/>
+      <c r="C174" s="19"/>
+      <c r="D174" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="E174" s="11"/>
-      <c r="F174" s="11"/>
-      <c r="G174" s="12"/>
-      <c r="H174" s="11"/>
-      <c r="I174" s="24"/>
+      <c r="E174" s="10"/>
+      <c r="F174" s="10"/>
+      <c r="G174" s="11"/>
+      <c r="H174" s="10"/>
+      <c r="I174" s="23"/>
     </row>
     <row r="175" spans="1:9">
-      <c r="A175" s="11">
+      <c r="A175" s="10">
         <v>172</v>
       </c>
-      <c r="B175" s="17"/>
-      <c r="C175" s="20"/>
-      <c r="D175" s="20" t="s">
+      <c r="B175" s="16"/>
+      <c r="C175" s="19"/>
+      <c r="D175" s="19" t="s">
         <v>225</v>
       </c>
-      <c r="E175" s="11"/>
-      <c r="F175" s="11"/>
-      <c r="G175" s="12"/>
-      <c r="H175" s="11"/>
-      <c r="I175" s="24"/>
+      <c r="E175" s="10"/>
+      <c r="F175" s="10"/>
+      <c r="G175" s="11"/>
+      <c r="H175" s="10"/>
+      <c r="I175" s="23"/>
     </row>
     <row r="176" spans="1:9">
-      <c r="A176" s="11">
+      <c r="A176" s="10">
         <v>173</v>
       </c>
-      <c r="B176" s="17"/>
-      <c r="C176" s="20"/>
-      <c r="D176" s="20" t="s">
+      <c r="B176" s="16"/>
+      <c r="C176" s="19"/>
+      <c r="D176" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="E176" s="11"/>
-      <c r="F176" s="11"/>
-      <c r="G176" s="12"/>
-      <c r="H176" s="11"/>
-      <c r="I176" s="24"/>
+      <c r="E176" s="10"/>
+      <c r="F176" s="10"/>
+      <c r="G176" s="11"/>
+      <c r="H176" s="10"/>
+      <c r="I176" s="23"/>
     </row>
     <row r="177" spans="1:9">
-      <c r="A177" s="11">
+      <c r="A177" s="10">
         <v>174</v>
       </c>
-      <c r="B177" s="17"/>
-      <c r="C177" s="20"/>
-      <c r="D177" s="20" t="s">
+      <c r="B177" s="16"/>
+      <c r="C177" s="19"/>
+      <c r="D177" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="E177" s="11"/>
-      <c r="F177" s="11"/>
-      <c r="G177" s="12"/>
-      <c r="H177" s="11"/>
-      <c r="I177" s="24"/>
+      <c r="E177" s="10"/>
+      <c r="F177" s="10"/>
+      <c r="G177" s="11"/>
+      <c r="H177" s="10"/>
+      <c r="I177" s="23"/>
     </row>
     <row r="178" spans="1:9">
-      <c r="A178" s="11">
+      <c r="A178" s="10">
         <v>175</v>
       </c>
-      <c r="B178" s="17"/>
-      <c r="C178" s="20"/>
-      <c r="D178" s="20" t="s">
+      <c r="B178" s="16"/>
+      <c r="C178" s="19"/>
+      <c r="D178" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="E178" s="11"/>
-      <c r="F178" s="11"/>
-      <c r="G178" s="12"/>
-      <c r="H178" s="11"/>
-      <c r="I178" s="24"/>
+      <c r="E178" s="10"/>
+      <c r="F178" s="10"/>
+      <c r="G178" s="11"/>
+      <c r="H178" s="10"/>
+      <c r="I178" s="23"/>
     </row>
     <row r="179" spans="1:9">
-      <c r="A179" s="11">
+      <c r="A179" s="10">
         <v>176</v>
       </c>
-      <c r="B179" s="17"/>
-      <c r="C179" s="20"/>
-      <c r="D179" s="20" t="s">
+      <c r="B179" s="16"/>
+      <c r="C179" s="19"/>
+      <c r="D179" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="E179" s="11"/>
-      <c r="F179" s="11"/>
-      <c r="G179" s="12"/>
-      <c r="H179" s="11"/>
-      <c r="I179" s="24"/>
+      <c r="E179" s="10"/>
+      <c r="F179" s="10"/>
+      <c r="G179" s="11"/>
+      <c r="H179" s="10"/>
+      <c r="I179" s="23"/>
     </row>
     <row r="180" spans="1:9">
-      <c r="A180" s="11">
+      <c r="A180" s="10">
         <v>177</v>
       </c>
-      <c r="B180" s="17"/>
-      <c r="C180" s="20"/>
-      <c r="D180" s="20" t="s">
+      <c r="B180" s="16"/>
+      <c r="C180" s="19"/>
+      <c r="D180" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="E180" s="11"/>
-      <c r="F180" s="11"/>
-      <c r="G180" s="12"/>
-      <c r="H180" s="11"/>
-      <c r="I180" s="24"/>
+      <c r="E180" s="10"/>
+      <c r="F180" s="10"/>
+      <c r="G180" s="11"/>
+      <c r="H180" s="10"/>
+      <c r="I180" s="23"/>
     </row>
     <row r="181" spans="1:9">
-      <c r="A181" s="11">
+      <c r="A181" s="10">
         <v>178</v>
       </c>
-      <c r="B181" s="17"/>
-      <c r="C181" s="20"/>
-      <c r="D181" s="20" t="s">
+      <c r="B181" s="16"/>
+      <c r="C181" s="19"/>
+      <c r="D181" s="19" t="s">
         <v>231</v>
       </c>
-      <c r="E181" s="11"/>
-      <c r="F181" s="11"/>
-      <c r="G181" s="12"/>
-      <c r="H181" s="11"/>
-      <c r="I181" s="24"/>
+      <c r="E181" s="10"/>
+      <c r="F181" s="10"/>
+      <c r="G181" s="11"/>
+      <c r="H181" s="10"/>
+      <c r="I181" s="23"/>
     </row>
     <row r="182" spans="1:9">
-      <c r="A182" s="11">
+      <c r="A182" s="10">
         <v>179</v>
       </c>
-      <c r="B182" s="17"/>
-      <c r="C182" s="20"/>
-      <c r="D182" s="20" t="s">
+      <c r="B182" s="16"/>
+      <c r="C182" s="19"/>
+      <c r="D182" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="E182" s="11"/>
-      <c r="F182" s="11"/>
-      <c r="G182" s="12"/>
-      <c r="H182" s="11"/>
-      <c r="I182" s="24"/>
+      <c r="E182" s="10"/>
+      <c r="F182" s="10"/>
+      <c r="G182" s="11"/>
+      <c r="H182" s="10"/>
+      <c r="I182" s="23"/>
     </row>
     <row r="183" spans="1:9">
-      <c r="A183" s="11">
+      <c r="A183" s="10">
         <v>180</v>
       </c>
-      <c r="B183" s="17"/>
-      <c r="C183" s="20"/>
-      <c r="D183" s="20" t="s">
+      <c r="B183" s="16"/>
+      <c r="C183" s="19"/>
+      <c r="D183" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="E183" s="11"/>
-      <c r="F183" s="11"/>
-      <c r="G183" s="12"/>
-      <c r="H183" s="11"/>
-      <c r="I183" s="24"/>
+      <c r="E183" s="10"/>
+      <c r="F183" s="10"/>
+      <c r="G183" s="11"/>
+      <c r="H183" s="10"/>
+      <c r="I183" s="23"/>
     </row>
     <row r="184" spans="1:9">
-      <c r="A184" s="11">
+      <c r="A184" s="10">
         <v>181</v>
       </c>
-      <c r="B184" s="17"/>
-      <c r="C184" s="20"/>
-      <c r="D184" s="20" t="s">
+      <c r="B184" s="16"/>
+      <c r="C184" s="19"/>
+      <c r="D184" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="E184" s="11"/>
-      <c r="F184" s="11"/>
-      <c r="G184" s="12"/>
-      <c r="H184" s="11"/>
-      <c r="I184" s="24"/>
+      <c r="E184" s="10"/>
+      <c r="F184" s="10"/>
+      <c r="G184" s="11"/>
+      <c r="H184" s="10"/>
+      <c r="I184" s="23"/>
     </row>
     <row r="185" spans="1:9">
-      <c r="A185" s="11">
+      <c r="A185" s="10">
         <v>182</v>
       </c>
-      <c r="B185" s="17"/>
-      <c r="C185" s="20"/>
-      <c r="D185" s="20" t="s">
+      <c r="B185" s="16"/>
+      <c r="C185" s="19"/>
+      <c r="D185" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="E185" s="11"/>
-      <c r="F185" s="11"/>
-      <c r="G185" s="12"/>
-      <c r="H185" s="11"/>
-      <c r="I185" s="24"/>
+      <c r="E185" s="10"/>
+      <c r="F185" s="10"/>
+      <c r="G185" s="11"/>
+      <c r="H185" s="10"/>
+      <c r="I185" s="23"/>
     </row>
     <row r="186" spans="1:9">
-      <c r="A186" s="11">
+      <c r="A186" s="10">
         <v>183</v>
       </c>
-      <c r="B186" s="17"/>
-      <c r="C186" s="20"/>
-      <c r="D186" s="20" t="s">
+      <c r="B186" s="16"/>
+      <c r="C186" s="19"/>
+      <c r="D186" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="E186" s="11"/>
-      <c r="F186" s="11"/>
-      <c r="G186" s="12"/>
-      <c r="H186" s="11"/>
-      <c r="I186" s="24"/>
+      <c r="E186" s="10"/>
+      <c r="F186" s="10"/>
+      <c r="G186" s="11"/>
+      <c r="H186" s="10"/>
+      <c r="I186" s="23"/>
     </row>
     <row r="187" spans="1:9">
-      <c r="A187" s="11">
+      <c r="A187" s="10">
         <v>184</v>
       </c>
-      <c r="B187" s="17"/>
-      <c r="C187" s="20"/>
-      <c r="D187" s="20" t="s">
+      <c r="B187" s="16"/>
+      <c r="C187" s="19"/>
+      <c r="D187" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="E187" s="11"/>
-      <c r="F187" s="11"/>
-      <c r="G187" s="12"/>
-      <c r="H187" s="11"/>
-      <c r="I187" s="24"/>
+      <c r="E187" s="10"/>
+      <c r="F187" s="10"/>
+      <c r="G187" s="11"/>
+      <c r="H187" s="10"/>
+      <c r="I187" s="23"/>
     </row>
     <row r="188" spans="1:9">
-      <c r="A188" s="11">
+      <c r="A188" s="10">
         <v>185</v>
       </c>
-      <c r="B188" s="17"/>
-      <c r="C188" s="20"/>
-      <c r="D188" s="20" t="s">
+      <c r="B188" s="16"/>
+      <c r="C188" s="19"/>
+      <c r="D188" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="E188" s="11"/>
-      <c r="F188" s="11"/>
-      <c r="G188" s="12"/>
-      <c r="H188" s="11"/>
-      <c r="I188" s="24"/>
+      <c r="E188" s="10"/>
+      <c r="F188" s="10"/>
+      <c r="G188" s="11"/>
+      <c r="H188" s="10"/>
+      <c r="I188" s="23"/>
     </row>
     <row r="189" spans="1:9">
-      <c r="A189" s="11">
+      <c r="A189" s="10">
         <v>186</v>
       </c>
-      <c r="B189" s="17"/>
-      <c r="C189" s="20"/>
-      <c r="D189" s="20" t="s">
+      <c r="B189" s="16"/>
+      <c r="C189" s="19"/>
+      <c r="D189" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="E189" s="11"/>
-      <c r="F189" s="11"/>
-      <c r="G189" s="12"/>
-      <c r="H189" s="11"/>
-      <c r="I189" s="24"/>
+      <c r="E189" s="10"/>
+      <c r="F189" s="10"/>
+      <c r="G189" s="11"/>
+      <c r="H189" s="10"/>
+      <c r="I189" s="23"/>
     </row>
     <row r="190" spans="1:9">
-      <c r="A190" s="11">
+      <c r="A190" s="10">
         <v>187</v>
       </c>
-      <c r="B190" s="17"/>
-      <c r="C190" s="20"/>
-      <c r="D190" s="20" t="s">
+      <c r="B190" s="16"/>
+      <c r="C190" s="19"/>
+      <c r="D190" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="E190" s="11"/>
-      <c r="F190" s="11"/>
-      <c r="G190" s="12"/>
-      <c r="H190" s="11"/>
-      <c r="I190" s="24"/>
+      <c r="E190" s="10"/>
+      <c r="F190" s="10"/>
+      <c r="G190" s="11"/>
+      <c r="H190" s="10"/>
+      <c r="I190" s="23"/>
     </row>
     <row r="191" spans="1:9">
-      <c r="A191" s="11">
+      <c r="A191" s="10">
         <v>188</v>
       </c>
-      <c r="B191" s="17"/>
-      <c r="C191" s="20"/>
-      <c r="D191" s="20" t="s">
+      <c r="B191" s="16"/>
+      <c r="C191" s="19"/>
+      <c r="D191" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="E191" s="11"/>
-      <c r="F191" s="11"/>
-      <c r="G191" s="12"/>
-      <c r="H191" s="11"/>
-      <c r="I191" s="24"/>
+      <c r="E191" s="10"/>
+      <c r="F191" s="10"/>
+      <c r="G191" s="11"/>
+      <c r="H191" s="10"/>
+      <c r="I191" s="23"/>
     </row>
     <row r="192" spans="1:9">
-      <c r="A192" s="11">
+      <c r="A192" s="10">
         <v>189</v>
       </c>
-      <c r="B192" s="17"/>
-      <c r="C192" s="20" t="s">
+      <c r="B192" s="16"/>
+      <c r="C192" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D192" s="20" t="s">
+      <c r="D192" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="E192" s="11"/>
-      <c r="F192" s="11"/>
-      <c r="G192" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H192" s="11"/>
-      <c r="I192" s="24"/>
+      <c r="E192" s="10"/>
+      <c r="F192" s="10"/>
+      <c r="G192" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H192" s="10"/>
+      <c r="I192" s="23"/>
     </row>
     <row r="193" spans="1:9">
-      <c r="A193" s="11">
+      <c r="A193" s="10">
         <v>190</v>
       </c>
-      <c r="B193" s="17"/>
-      <c r="C193" s="20" t="s">
+      <c r="B193" s="16"/>
+      <c r="C193" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D193" s="20" t="s">
+      <c r="D193" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="E193" s="11"/>
-      <c r="F193" s="11"/>
-      <c r="G193" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H193" s="11"/>
-      <c r="I193" s="24"/>
+      <c r="E193" s="10"/>
+      <c r="F193" s="10"/>
+      <c r="G193" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H193" s="10"/>
+      <c r="I193" s="23"/>
     </row>
     <row r="194" spans="1:9">
-      <c r="A194" s="11">
+      <c r="A194" s="10">
         <v>191</v>
       </c>
-      <c r="B194" s="17"/>
-      <c r="C194" s="20" t="s">
+      <c r="B194" s="16"/>
+      <c r="C194" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D194" s="20" t="s">
+      <c r="D194" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="E194" s="11"/>
-      <c r="F194" s="11"/>
-      <c r="G194" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H194" s="11"/>
-      <c r="I194" s="24"/>
+      <c r="E194" s="10"/>
+      <c r="F194" s="10"/>
+      <c r="G194" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H194" s="10"/>
+      <c r="I194" s="23"/>
     </row>
     <row r="195" spans="1:9">
-      <c r="A195" s="11">
+      <c r="A195" s="10">
         <v>192</v>
       </c>
-      <c r="B195" s="17"/>
-      <c r="C195" s="20" t="s">
+      <c r="B195" s="16"/>
+      <c r="C195" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D195" s="20" t="s">
+      <c r="D195" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="E195" s="11"/>
-      <c r="F195" s="11"/>
-      <c r="G195" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H195" s="11"/>
-      <c r="I195" s="24"/>
+      <c r="E195" s="10"/>
+      <c r="F195" s="10"/>
+      <c r="G195" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H195" s="10"/>
+      <c r="I195" s="23"/>
     </row>
     <row r="196" spans="1:9">
-      <c r="A196" s="11">
+      <c r="A196" s="10">
         <v>193</v>
       </c>
-      <c r="B196" s="17"/>
-      <c r="C196" s="20" t="s">
+      <c r="B196" s="16"/>
+      <c r="C196" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D196" s="20" t="s">
+      <c r="D196" s="19" t="s">
         <v>246</v>
       </c>
-      <c r="E196" s="11"/>
-      <c r="F196" s="11"/>
-      <c r="G196" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H196" s="11"/>
-      <c r="I196" s="24"/>
+      <c r="E196" s="10"/>
+      <c r="F196" s="10"/>
+      <c r="G196" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H196" s="10"/>
+      <c r="I196" s="23"/>
     </row>
     <row r="197" spans="1:9">
-      <c r="A197" s="11">
+      <c r="A197" s="10">
         <v>194</v>
       </c>
-      <c r="B197" s="17"/>
-      <c r="C197" s="20" t="s">
+      <c r="B197" s="16"/>
+      <c r="C197" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D197" s="20" t="s">
+      <c r="D197" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="E197" s="11"/>
-      <c r="F197" s="11"/>
-      <c r="G197" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H197" s="11"/>
-      <c r="I197" s="24"/>
+      <c r="E197" s="10"/>
+      <c r="F197" s="10"/>
+      <c r="G197" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H197" s="10"/>
+      <c r="I197" s="23"/>
     </row>
     <row r="198" spans="1:9">
-      <c r="A198" s="11">
+      <c r="A198" s="10">
         <v>195</v>
       </c>
-      <c r="B198" s="17"/>
-      <c r="C198" s="20" t="s">
+      <c r="B198" s="16"/>
+      <c r="C198" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D198" s="20" t="s">
+      <c r="D198" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="E198" s="11"/>
-      <c r="F198" s="11"/>
-      <c r="G198" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H198" s="11"/>
-      <c r="I198" s="24"/>
+      <c r="E198" s="10"/>
+      <c r="F198" s="10"/>
+      <c r="G198" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H198" s="10"/>
+      <c r="I198" s="23"/>
     </row>
     <row r="199" spans="1:9">
-      <c r="A199" s="11">
+      <c r="A199" s="10">
         <v>196</v>
       </c>
-      <c r="B199" s="17"/>
-      <c r="C199" s="20" t="s">
+      <c r="B199" s="16"/>
+      <c r="C199" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D199" s="20" t="s">
+      <c r="D199" s="19" t="s">
         <v>249</v>
       </c>
-      <c r="E199" s="11"/>
-      <c r="F199" s="11"/>
-      <c r="G199" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H199" s="11"/>
-      <c r="I199" s="24"/>
+      <c r="E199" s="10"/>
+      <c r="F199" s="10"/>
+      <c r="G199" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H199" s="10"/>
+      <c r="I199" s="23"/>
     </row>
     <row r="200" spans="1:9">
-      <c r="A200" s="11">
+      <c r="A200" s="10">
         <v>197</v>
       </c>
-      <c r="B200" s="17"/>
-      <c r="C200" s="20" t="s">
+      <c r="B200" s="16"/>
+      <c r="C200" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D200" s="20" t="s">
+      <c r="D200" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="E200" s="11"/>
-      <c r="F200" s="11"/>
-      <c r="G200" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H200" s="11"/>
-      <c r="I200" s="24"/>
+      <c r="E200" s="10"/>
+      <c r="F200" s="10"/>
+      <c r="G200" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H200" s="10"/>
+      <c r="I200" s="23"/>
     </row>
     <row r="201" spans="1:9">
-      <c r="A201" s="11">
+      <c r="A201" s="10">
         <v>198</v>
       </c>
-      <c r="B201" s="17"/>
-      <c r="C201" s="20" t="s">
+      <c r="B201" s="16"/>
+      <c r="C201" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D201" s="20" t="s">
+      <c r="D201" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="E201" s="11"/>
-      <c r="F201" s="11"/>
-      <c r="G201" s="12"/>
-      <c r="H201" s="11"/>
-      <c r="I201" s="24"/>
+      <c r="E201" s="10"/>
+      <c r="F201" s="10"/>
+      <c r="G201" s="11"/>
+      <c r="H201" s="10"/>
+      <c r="I201" s="23"/>
     </row>
     <row r="202" spans="1:9">
-      <c r="A202" s="11">
+      <c r="A202" s="10">
         <v>199</v>
       </c>
-      <c r="B202" s="17"/>
-      <c r="C202" s="20" t="s">
+      <c r="B202" s="16"/>
+      <c r="C202" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D202" s="20" t="s">
+      <c r="D202" s="19" t="s">
         <v>252</v>
       </c>
-      <c r="E202" s="11"/>
-      <c r="F202" s="11"/>
-      <c r="G202" s="12"/>
-      <c r="H202" s="11"/>
-      <c r="I202" s="24"/>
+      <c r="E202" s="10"/>
+      <c r="F202" s="10"/>
+      <c r="G202" s="11"/>
+      <c r="H202" s="10"/>
+      <c r="I202" s="23"/>
     </row>
     <row r="203" spans="1:9">
-      <c r="A203" s="11">
+      <c r="A203" s="10">
         <v>200</v>
       </c>
-      <c r="B203" s="17"/>
-      <c r="C203" s="20" t="s">
+      <c r="B203" s="16"/>
+      <c r="C203" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D203" s="20" t="s">
+      <c r="D203" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="E203" s="11"/>
-      <c r="F203" s="11"/>
-      <c r="G203" s="12"/>
-      <c r="H203" s="11"/>
-      <c r="I203" s="24"/>
+      <c r="E203" s="10"/>
+      <c r="F203" s="10"/>
+      <c r="G203" s="11"/>
+      <c r="H203" s="10"/>
+      <c r="I203" s="23"/>
     </row>
     <row r="204" spans="1:9">
-      <c r="A204" s="11">
+      <c r="A204" s="10">
         <v>201</v>
       </c>
-      <c r="B204" s="17"/>
-      <c r="C204" s="20" t="s">
+      <c r="B204" s="16"/>
+      <c r="C204" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D204" s="20" t="s">
+      <c r="D204" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="E204" s="11"/>
-      <c r="F204" s="11"/>
-      <c r="G204" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H204" s="11"/>
-      <c r="I204" s="24"/>
+      <c r="E204" s="10"/>
+      <c r="F204" s="10"/>
+      <c r="G204" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H204" s="10"/>
+      <c r="I204" s="23"/>
     </row>
     <row r="205" spans="1:9">
-      <c r="A205" s="11">
+      <c r="A205" s="10">
         <v>202</v>
       </c>
-      <c r="B205" s="17"/>
-      <c r="C205" s="20" t="s">
+      <c r="B205" s="16"/>
+      <c r="C205" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D205" s="20" t="s">
+      <c r="D205" s="19" t="s">
         <v>255</v>
       </c>
-      <c r="E205" s="11"/>
-      <c r="F205" s="11"/>
-      <c r="G205" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H205" s="11"/>
-      <c r="I205" s="24"/>
+      <c r="E205" s="10"/>
+      <c r="F205" s="10"/>
+      <c r="G205" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H205" s="10"/>
+      <c r="I205" s="23"/>
     </row>
     <row r="206" spans="1:9">
-      <c r="A206" s="11">
+      <c r="A206" s="10">
         <v>203</v>
       </c>
-      <c r="B206" s="17"/>
-      <c r="C206" s="20" t="s">
+      <c r="B206" s="16"/>
+      <c r="C206" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D206" s="20" t="s">
+      <c r="D206" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="E206" s="11"/>
-      <c r="F206" s="11"/>
-      <c r="G206" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H206" s="11"/>
-      <c r="I206" s="24"/>
+      <c r="E206" s="10"/>
+      <c r="F206" s="10"/>
+      <c r="G206" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H206" s="10"/>
+      <c r="I206" s="23"/>
     </row>
     <row r="207" spans="1:9">
-      <c r="A207" s="11">
+      <c r="A207" s="10">
         <v>204</v>
       </c>
-      <c r="B207" s="17"/>
-      <c r="C207" s="20" t="s">
+      <c r="B207" s="16"/>
+      <c r="C207" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D207" s="20" t="s">
+      <c r="D207" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="E207" s="11"/>
-      <c r="F207" s="11"/>
-      <c r="G207" s="12"/>
-      <c r="H207" s="11"/>
-      <c r="I207" s="24"/>
+      <c r="E207" s="10"/>
+      <c r="F207" s="10"/>
+      <c r="G207" s="11"/>
+      <c r="H207" s="10"/>
+      <c r="I207" s="23"/>
     </row>
     <row r="208" spans="1:9">
-      <c r="A208" s="11">
+      <c r="A208" s="10">
         <v>205</v>
       </c>
-      <c r="B208" s="17"/>
-      <c r="C208" s="20" t="s">
+      <c r="B208" s="16"/>
+      <c r="C208" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D208" s="20" t="s">
+      <c r="D208" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="E208" s="11"/>
-      <c r="F208" s="11"/>
-      <c r="G208" s="12"/>
-      <c r="H208" s="11"/>
-      <c r="I208" s="24"/>
+      <c r="E208" s="10"/>
+      <c r="F208" s="10"/>
+      <c r="G208" s="11"/>
+      <c r="H208" s="10"/>
+      <c r="I208" s="23"/>
     </row>
     <row r="209" spans="1:9">
-      <c r="A209" s="11">
+      <c r="A209" s="10">
         <v>206</v>
       </c>
-      <c r="B209" s="17"/>
-      <c r="C209" s="20" t="s">
+      <c r="B209" s="16"/>
+      <c r="C209" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D209" s="20" t="s">
+      <c r="D209" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="E209" s="11"/>
-      <c r="F209" s="11"/>
-      <c r="G209" s="12"/>
-      <c r="H209" s="11"/>
-      <c r="I209" s="24"/>
+      <c r="E209" s="10"/>
+      <c r="F209" s="10"/>
+      <c r="G209" s="11"/>
+      <c r="H209" s="10"/>
+      <c r="I209" s="23"/>
     </row>
     <row r="210" spans="1:9">
-      <c r="A210" s="11">
+      <c r="A210" s="10">
         <v>207</v>
       </c>
-      <c r="B210" s="17"/>
-      <c r="C210" s="20" t="s">
+      <c r="B210" s="16"/>
+      <c r="C210" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D210" s="20" t="s">
+      <c r="D210" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="E210" s="11"/>
-      <c r="F210" s="11"/>
-      <c r="G210" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H210" s="11"/>
-      <c r="I210" s="24"/>
+      <c r="E210" s="10"/>
+      <c r="F210" s="10"/>
+      <c r="G210" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H210" s="10"/>
+      <c r="I210" s="23"/>
     </row>
     <row r="211" spans="1:9">
-      <c r="A211" s="11">
+      <c r="A211" s="10">
         <v>208</v>
       </c>
-      <c r="B211" s="17"/>
-      <c r="C211" s="20" t="s">
+      <c r="B211" s="16"/>
+      <c r="C211" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D211" s="20" t="s">
+      <c r="D211" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="E211" s="11"/>
-      <c r="F211" s="11"/>
-      <c r="G211" s="12" t="s">
+      <c r="E211" s="10"/>
+      <c r="F211" s="10"/>
+      <c r="G211" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="H211" s="11"/>
-      <c r="I211" s="24"/>
+      <c r="H211" s="10"/>
+      <c r="I211" s="23"/>
     </row>
     <row r="212" spans="1:9">
-      <c r="A212" s="11">
+      <c r="A212" s="10">
         <v>209</v>
       </c>
-      <c r="B212" s="17"/>
-      <c r="C212" s="20" t="s">
+      <c r="B212" s="16"/>
+      <c r="C212" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D212" s="20" t="s">
+      <c r="D212" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="E212" s="11"/>
-      <c r="F212" s="11"/>
-      <c r="G212" s="12"/>
-      <c r="H212" s="11"/>
-      <c r="I212" s="24"/>
+      <c r="E212" s="10"/>
+      <c r="F212" s="10"/>
+      <c r="G212" s="11"/>
+      <c r="H212" s="10"/>
+      <c r="I212" s="23"/>
     </row>
     <row r="213" spans="1:9">
-      <c r="A213" s="11">
+      <c r="A213" s="10">
         <v>210</v>
       </c>
-      <c r="B213" s="17"/>
-      <c r="C213" s="20" t="s">
+      <c r="B213" s="16"/>
+      <c r="C213" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D213" s="20" t="s">
+      <c r="D213" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="E213" s="11"/>
-      <c r="F213" s="11"/>
-      <c r="G213" s="12"/>
-      <c r="H213" s="11"/>
-      <c r="I213" s="24"/>
+      <c r="E213" s="10"/>
+      <c r="F213" s="10"/>
+      <c r="G213" s="11"/>
+      <c r="H213" s="10"/>
+      <c r="I213" s="23"/>
     </row>
     <row r="214" spans="1:9">
-      <c r="A214" s="11">
+      <c r="A214" s="10">
         <v>211</v>
       </c>
-      <c r="B214" s="17"/>
-      <c r="C214" s="20" t="s">
+      <c r="B214" s="16"/>
+      <c r="C214" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D214" s="20" t="s">
+      <c r="D214" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="E214" s="11"/>
-      <c r="F214" s="11"/>
-      <c r="G214" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H214" s="11"/>
-      <c r="I214" s="24"/>
+      <c r="E214" s="10"/>
+      <c r="F214" s="10"/>
+      <c r="G214" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H214" s="10"/>
+      <c r="I214" s="23"/>
     </row>
     <row r="215" spans="1:9">
-      <c r="A215" s="11">
+      <c r="A215" s="10">
         <v>212</v>
       </c>
-      <c r="B215" s="17"/>
-      <c r="C215" s="20" t="s">
+      <c r="B215" s="16"/>
+      <c r="C215" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D215" s="20" t="s">
+      <c r="D215" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="E215" s="11"/>
-      <c r="F215" s="11"/>
-      <c r="G215" s="12"/>
-      <c r="H215" s="11"/>
-      <c r="I215" s="24"/>
+      <c r="E215" s="10"/>
+      <c r="F215" s="10"/>
+      <c r="G215" s="11"/>
+      <c r="H215" s="10"/>
+      <c r="I215" s="23"/>
     </row>
     <row r="216" spans="1:9">
-      <c r="A216" s="11">
+      <c r="A216" s="10">
         <v>213</v>
       </c>
-      <c r="B216" s="17"/>
-      <c r="C216" s="20" t="s">
+      <c r="B216" s="16"/>
+      <c r="C216" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D216" s="20" t="s">
+      <c r="D216" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="E216" s="11"/>
-      <c r="F216" s="11"/>
-      <c r="G216" s="12"/>
-      <c r="H216" s="11"/>
-      <c r="I216" s="24"/>
+      <c r="E216" s="10"/>
+      <c r="F216" s="10"/>
+      <c r="G216" s="11"/>
+      <c r="H216" s="10"/>
+      <c r="I216" s="23"/>
     </row>
     <row r="217" spans="1:9">
-      <c r="A217" s="11">
+      <c r="A217" s="10">
         <v>214</v>
       </c>
-      <c r="B217" s="17"/>
-      <c r="C217" s="20" t="s">
+      <c r="B217" s="16"/>
+      <c r="C217" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D217" s="20" t="s">
+      <c r="D217" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="E217" s="11"/>
-      <c r="F217" s="11"/>
-      <c r="G217" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H217" s="11"/>
-      <c r="I217" s="24"/>
+      <c r="E217" s="10"/>
+      <c r="F217" s="10"/>
+      <c r="G217" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H217" s="10"/>
+      <c r="I217" s="23"/>
     </row>
     <row r="218" spans="1:9">
-      <c r="A218" s="11">
+      <c r="A218" s="10">
         <v>215</v>
       </c>
-      <c r="B218" s="17"/>
-      <c r="C218" s="20" t="s">
+      <c r="B218" s="16"/>
+      <c r="C218" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D218" s="20" t="s">
+      <c r="D218" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="E218" s="11"/>
-      <c r="F218" s="11"/>
-      <c r="G218" s="12"/>
-      <c r="H218" s="11"/>
-      <c r="I218" s="24"/>
+      <c r="E218" s="10"/>
+      <c r="F218" s="10"/>
+      <c r="G218" s="11"/>
+      <c r="H218" s="10"/>
+      <c r="I218" s="23"/>
     </row>
     <row r="219" spans="1:9">
-      <c r="A219" s="11">
+      <c r="A219" s="10">
         <v>216</v>
       </c>
-      <c r="B219" s="17"/>
-      <c r="C219" s="20" t="s">
+      <c r="B219" s="16"/>
+      <c r="C219" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D219" s="20" t="s">
+      <c r="D219" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="E219" s="11"/>
-      <c r="F219" s="11"/>
-      <c r="G219" s="12"/>
-      <c r="H219" s="11"/>
-      <c r="I219" s="24"/>
+      <c r="E219" s="10"/>
+      <c r="F219" s="10"/>
+      <c r="G219" s="11"/>
+      <c r="H219" s="10"/>
+      <c r="I219" s="23"/>
     </row>
     <row r="220" spans="1:9">
-      <c r="A220" s="11">
+      <c r="A220" s="10">
         <v>217</v>
       </c>
-      <c r="B220" s="17"/>
-      <c r="C220" s="20" t="s">
+      <c r="B220" s="16"/>
+      <c r="C220" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D220" s="20" t="s">
+      <c r="D220" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="E220" s="11"/>
-      <c r="F220" s="11"/>
-      <c r="G220" s="12"/>
-      <c r="H220" s="11"/>
-      <c r="I220" s="24"/>
+      <c r="E220" s="10"/>
+      <c r="F220" s="10"/>
+      <c r="G220" s="11"/>
+      <c r="H220" s="10"/>
+      <c r="I220" s="23"/>
     </row>
     <row r="221" spans="1:9">
-      <c r="A221" s="11">
+      <c r="A221" s="10">
         <v>220</v>
       </c>
-      <c r="B221" s="17"/>
-      <c r="C221" s="20"/>
-      <c r="D221" s="20"/>
-      <c r="E221" s="11"/>
-      <c r="F221" s="11"/>
-      <c r="G221" s="12"/>
-      <c r="H221" s="11"/>
-      <c r="I221" s="24"/>
+      <c r="B221" s="16"/>
+      <c r="C221" s="19"/>
+      <c r="D221" s="19"/>
+      <c r="E221" s="10"/>
+      <c r="F221" s="10"/>
+      <c r="G221" s="11"/>
+      <c r="H221" s="10"/>
+      <c r="I221" s="23"/>
     </row>
     <row r="222" spans="1:9">
-      <c r="A222" s="11"/>
-      <c r="B222" s="17"/>
-      <c r="C222" s="20"/>
-      <c r="D222" s="20"/>
-      <c r="E222" s="11"/>
-      <c r="F222" s="11"/>
-      <c r="G222" s="12"/>
-      <c r="H222" s="11"/>
-      <c r="I222" s="24"/>
+      <c r="A222" s="10"/>
+      <c r="B222" s="16"/>
+      <c r="C222" s="19"/>
+      <c r="D222" s="19"/>
+      <c r="E222" s="10"/>
+      <c r="F222" s="10"/>
+      <c r="G222" s="11"/>
+      <c r="H222" s="10"/>
+      <c r="I222" s="23"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I221">
@@ -6652,116 +6674,116 @@
   <dimension ref="A1:H101"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="9"/>
-    <col min="2" max="2" width="33.7109375" style="9" customWidth="1"/>
-    <col min="3" max="4" width="27.140625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="54.140625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" style="9" customWidth="1"/>
-    <col min="7" max="8" width="12.85546875" style="9" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="9"/>
+    <col min="1" max="1" width="9" style="8"/>
+    <col min="2" max="2" width="33.7109375" style="8" customWidth="1"/>
+    <col min="3" max="4" width="27.140625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="54.140625" style="8" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" style="8" customWidth="1"/>
+    <col min="7" max="8" width="12.85546875" style="8" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="33" customFormat="1" ht="30" customHeight="1">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="34" t="s">
         <v>305</v>
       </c>
-      <c r="G1" s="35" t="s">
+      <c r="G1" s="34" t="s">
         <v>304</v>
       </c>
-      <c r="H1" s="35" t="s">
+      <c r="H1" s="34" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="33" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="36">
+    <row r="2" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D2" s="36" t="s">
         <v>311</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="F2" s="36">
+      <c r="F2" s="35">
         <v>2015</v>
       </c>
-      <c r="G2" s="36">
+      <c r="G2" s="35">
         <v>2022</v>
       </c>
-      <c r="H2" s="38" t="s">
+      <c r="H2" s="37" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="33" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
       <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="39" t="s">
+      <c r="B3" s="38" t="s">
         <v>308</v>
       </c>
-      <c r="C3" s="39" t="s">
+      <c r="C3" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="D3" s="39" t="s">
+      <c r="D3" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="E3" s="39" t="s">
+      <c r="E3" s="38" t="s">
         <v>355</v>
       </c>
       <c r="F3" s="5">
         <v>2016</v>
       </c>
-      <c r="G3" s="40">
+      <c r="G3" s="39">
         <v>2022</v>
       </c>
-      <c r="H3" s="40" t="s">
+      <c r="H3" s="39" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="33" customFormat="1" ht="30" customHeight="1">
-      <c r="A4" s="36">
+    <row r="4" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
+      <c r="A4" s="35">
         <v>3</v>
       </c>
-      <c r="B4" s="39" t="s">
+      <c r="B4" s="38" t="s">
         <v>356</v>
       </c>
-      <c r="C4" s="39" t="s">
+      <c r="C4" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="38" t="s">
         <v>371</v>
       </c>
       <c r="F4" s="5">
         <v>2016</v>
       </c>
-      <c r="G4" s="40" t="s">
+      <c r="G4" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="40" t="s">
+      <c r="H4" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6769,42 +6791,42 @@
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>293</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="40" t="s">
         <v>295</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>296</v>
       </c>
       <c r="F5" s="5">
         <v>2016</v>
       </c>
-      <c r="G5" s="40" t="s">
+      <c r="G5" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="40" t="s">
+      <c r="H5" s="39" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" customHeight="1">
-      <c r="A6" s="36">
+      <c r="A6" s="35">
         <v>5</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="40" t="s">
         <v>300</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="7" t="s">
         <v>302</v>
       </c>
       <c r="F6" s="5">
@@ -6813,7 +6835,7 @@
       <c r="G6" s="5">
         <v>2023</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6821,16 +6843,16 @@
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="40" t="s">
         <v>301</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="40" t="s">
         <v>298</v>
       </c>
-      <c r="D7" s="39" t="s">
+      <c r="D7" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="7" t="s">
         <v>302</v>
       </c>
       <c r="F7" s="5">
@@ -6839,33 +6861,33 @@
       <c r="G7" s="5">
         <v>2023</v>
       </c>
-      <c r="H7" s="40" t="s">
+      <c r="H7" s="39" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" customHeight="1">
-      <c r="A8" s="36">
+      <c r="A8" s="35">
         <v>7</v>
       </c>
-      <c r="B8" s="39" t="s">
+      <c r="B8" s="38" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="D8" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="E8" s="39" t="s">
+      <c r="E8" s="38" t="s">
         <v>307</v>
       </c>
       <c r="F8" s="5">
         <v>2022</v>
       </c>
-      <c r="G8" s="40" t="s">
+      <c r="G8" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="40" t="s">
+      <c r="H8" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6873,51 +6895,51 @@
       <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="38" t="s">
         <v>309</v>
       </c>
-      <c r="C9" s="39" t="s">
+      <c r="C9" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="E9" s="39" t="s">
+      <c r="E9" s="38" t="s">
         <v>307</v>
       </c>
       <c r="F9" s="5">
         <v>2022</v>
       </c>
-      <c r="G9" s="40" t="s">
+      <c r="G9" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="40" t="s">
+      <c r="H9" s="39" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="30" customHeight="1">
-      <c r="A10" s="36">
+      <c r="A10" s="35">
         <v>9</v>
       </c>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="E10" s="39" t="s">
+      <c r="E10" s="38" t="s">
         <v>307</v>
       </c>
       <c r="F10" s="5">
         <v>2022</v>
       </c>
-      <c r="G10" s="40" t="s">
+      <c r="G10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="40" t="s">
+      <c r="H10" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6925,51 +6947,51 @@
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="38" t="s">
         <v>317</v>
       </c>
-      <c r="C11" s="39" t="s">
+      <c r="C11" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E11" s="39" t="s">
+      <c r="E11" s="38" t="s">
         <v>307</v>
       </c>
       <c r="F11" s="5">
         <v>2022</v>
       </c>
-      <c r="G11" s="40" t="s">
+      <c r="G11" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="40" t="s">
+      <c r="H11" s="39" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="30" customHeight="1">
-      <c r="A12" s="36">
+      <c r="A12" s="35">
         <v>11</v>
       </c>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="38" t="s">
         <v>313</v>
       </c>
-      <c r="C12" s="39" t="s">
+      <c r="C12" s="38" t="s">
         <v>314</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="38" t="s">
         <v>315</v>
       </c>
-      <c r="E12" s="39" t="s">
+      <c r="E12" s="38" t="s">
         <v>316</v>
       </c>
       <c r="F12" s="5">
         <v>2022</v>
       </c>
-      <c r="G12" s="40" t="s">
+      <c r="G12" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="40" t="s">
+      <c r="H12" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -6977,51 +6999,51 @@
       <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="39" t="s">
+      <c r="B13" s="38" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="39" t="s">
+      <c r="C13" s="38" t="s">
         <v>320</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="E13" s="39" t="s">
+      <c r="E13" s="38" t="s">
         <v>316</v>
       </c>
       <c r="F13" s="5">
         <v>2022</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="40" t="s">
+      <c r="H13" s="39" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" customHeight="1">
-      <c r="A14" s="36">
+      <c r="A14" s="35">
         <v>13</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="38" t="s">
         <v>322</v>
       </c>
-      <c r="C14" s="39" t="s">
+      <c r="C14" s="38" t="s">
         <v>323</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="E14" s="39" t="s">
+      <c r="E14" s="38" t="s">
         <v>316</v>
       </c>
       <c r="F14" s="5">
         <v>2022</v>
       </c>
-      <c r="G14" s="40" t="s">
+      <c r="G14" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="40" t="s">
+      <c r="H14" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7029,51 +7051,51 @@
       <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="38" t="s">
         <v>324</v>
       </c>
-      <c r="C15" s="39" t="s">
+      <c r="C15" s="38" t="s">
         <v>325</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="38" t="s">
         <v>326</v>
       </c>
-      <c r="E15" s="39" t="s">
+      <c r="E15" s="38" t="s">
         <v>316</v>
       </c>
       <c r="F15" s="5">
         <v>2022</v>
       </c>
-      <c r="G15" s="40" t="s">
+      <c r="G15" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H15" s="40" t="s">
+      <c r="H15" s="39" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="30" customHeight="1">
-      <c r="A16" s="36">
-        <v>15</v>
-      </c>
-      <c r="B16" s="37" t="s">
+      <c r="A16" s="35">
+        <v>15</v>
+      </c>
+      <c r="B16" s="36" t="s">
         <v>328</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C16" s="38" t="s">
         <v>327</v>
       </c>
-      <c r="D16" s="39" t="s">
+      <c r="D16" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="E16" s="39" t="s">
+      <c r="E16" s="38" t="s">
         <v>316</v>
       </c>
       <c r="F16" s="5">
         <v>2022</v>
       </c>
-      <c r="G16" s="40" t="s">
+      <c r="G16" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H16" s="40" t="s">
+      <c r="H16" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7081,16 +7103,16 @@
       <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="38" t="s">
         <v>329</v>
       </c>
-      <c r="C17" s="39" t="s">
+      <c r="C17" s="38" t="s">
         <v>330</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="40" t="s">
         <v>311</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E17" s="40" t="s">
         <v>316</v>
       </c>
       <c r="F17" s="5">
@@ -7104,19 +7126,19 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="30" customHeight="1">
-      <c r="A18" s="36">
+      <c r="A18" s="35">
         <v>17</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="40" t="s">
         <v>332</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="40" t="s">
         <v>331</v>
       </c>
-      <c r="D18" s="41" t="s">
+      <c r="D18" s="40" t="s">
         <v>333</v>
       </c>
-      <c r="E18" s="41" t="s">
+      <c r="E18" s="40" t="s">
         <v>316</v>
       </c>
       <c r="F18" s="5">
@@ -7130,45 +7152,45 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="30" customHeight="1">
-      <c r="A19" s="42">
+      <c r="A19" s="41">
         <v>18</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="42" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="43" t="s">
+      <c r="C19" s="42" t="s">
         <v>335</v>
       </c>
-      <c r="D19" s="43" t="s">
+      <c r="D19" s="42" t="s">
         <v>321</v>
       </c>
-      <c r="E19" s="43" t="s">
+      <c r="E19" s="42" t="s">
         <v>316</v>
       </c>
-      <c r="F19" s="42">
+      <c r="F19" s="41">
         <v>2023</v>
       </c>
-      <c r="G19" s="42" t="s">
+      <c r="G19" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="42" t="s">
+      <c r="H19" s="41" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="30" customHeight="1">
-      <c r="A20" s="36">
+      <c r="A20" s="35">
         <v>19</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="40" t="s">
         <v>337</v>
       </c>
-      <c r="D20" s="41" t="s">
+      <c r="D20" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="E20" s="41" t="s">
+      <c r="E20" s="40" t="s">
         <v>316</v>
       </c>
       <c r="F20" s="5">
@@ -7185,16 +7207,16 @@
       <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="40" t="s">
         <v>339</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="40" t="s">
         <v>338</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D21" s="40" t="s">
         <v>311</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="40" t="s">
         <v>316</v>
       </c>
       <c r="F21" s="5">
@@ -7208,19 +7230,19 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="30" customHeight="1">
-      <c r="A22" s="36">
+      <c r="A22" s="35">
         <v>21</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="40" t="s">
         <v>348</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>347</v>
       </c>
-      <c r="D22" s="41" t="s">
+      <c r="D22" s="40" t="s">
         <v>311</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="40" t="s">
         <v>316</v>
       </c>
       <c r="F22" s="5">
@@ -7237,16 +7259,16 @@
       <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="40" t="s">
         <v>341</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="40" t="s">
         <v>340</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="40" t="s">
         <v>316</v>
       </c>
       <c r="F23" s="5">
@@ -7260,19 +7282,19 @@
       </c>
     </row>
     <row r="24" spans="1:8" ht="30" customHeight="1">
-      <c r="A24" s="36">
+      <c r="A24" s="35">
         <v>23</v>
       </c>
-      <c r="B24" s="41" t="s">
+      <c r="B24" s="40" t="s">
         <v>342</v>
       </c>
-      <c r="C24" s="41" t="s">
+      <c r="C24" s="40" t="s">
         <v>343</v>
       </c>
-      <c r="D24" s="41" t="s">
+      <c r="D24" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="E24" s="41" t="s">
+      <c r="E24" s="40" t="s">
         <v>316</v>
       </c>
       <c r="F24" s="5">
@@ -7289,16 +7311,16 @@
       <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="41" t="s">
+      <c r="B25" s="40" t="s">
         <v>344</v>
       </c>
-      <c r="C25" s="41" t="s">
+      <c r="C25" s="40" t="s">
         <v>345</v>
       </c>
-      <c r="D25" s="41" t="s">
+      <c r="D25" s="40" t="s">
         <v>346</v>
       </c>
-      <c r="E25" s="41" t="s">
+      <c r="E25" s="40" t="s">
         <v>316</v>
       </c>
       <c r="F25" s="5">
@@ -7312,19 +7334,19 @@
       </c>
     </row>
     <row r="26" spans="1:8" ht="30" customHeight="1">
-      <c r="A26" s="36">
+      <c r="A26" s="35">
         <v>25</v>
       </c>
-      <c r="B26" s="41" t="s">
+      <c r="B26" s="40" t="s">
         <v>350</v>
       </c>
-      <c r="C26" s="41" t="s">
+      <c r="C26" s="40" t="s">
         <v>351</v>
       </c>
-      <c r="D26" s="41" t="s">
+      <c r="D26" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="E26" s="7" t="s">
         <v>352</v>
       </c>
       <c r="F26" s="5" t="s">
@@ -7341,16 +7363,16 @@
       <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="40" t="s">
         <v>353</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="40" t="s">
         <v>330</v>
       </c>
-      <c r="D27" s="41" t="s">
+      <c r="D27" s="40" t="s">
         <v>311</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="E27" s="40" t="s">
         <v>354</v>
       </c>
       <c r="F27" s="5" t="s">
@@ -7364,28 +7386,28 @@
       </c>
     </row>
     <row r="28" spans="1:8" ht="30" customHeight="1">
-      <c r="A28" s="36">
+      <c r="A28" s="35">
         <v>27</v>
       </c>
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="38" t="s">
         <v>392</v>
       </c>
-      <c r="C28" s="39" t="s">
+      <c r="C28" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="D28" s="39" t="s">
+      <c r="D28" s="38" t="s">
         <v>394</v>
       </c>
-      <c r="E28" s="39" t="s">
+      <c r="E28" s="38" t="s">
         <v>395</v>
       </c>
-      <c r="F28" s="40" t="s">
+      <c r="F28" s="39" t="s">
         <v>349</v>
       </c>
-      <c r="G28" s="40" t="s">
+      <c r="G28" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="H28" s="40" t="s">
+      <c r="H28" s="39" t="s">
         <v>10</v>
       </c>
     </row>
@@ -7393,16 +7415,16 @@
       <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="40" t="s">
         <v>357</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="41" t="s">
+      <c r="D29" s="40" t="s">
         <v>359</v>
       </c>
-      <c r="E29" s="8" t="s">
+      <c r="E29" s="7" t="s">
         <v>360</v>
       </c>
       <c r="F29" s="5">
@@ -7416,19 +7438,19 @@
       </c>
     </row>
     <row r="30" spans="1:8" ht="30" customHeight="1">
-      <c r="A30" s="36">
+      <c r="A30" s="35">
         <v>29</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="40" t="s">
         <v>362</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="40" t="s">
         <v>361</v>
       </c>
-      <c r="D30" s="41" t="s">
+      <c r="D30" s="40" t="s">
         <v>363</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="E30" s="7" t="s">
         <v>364</v>
       </c>
       <c r="F30" s="5">
@@ -7442,19 +7464,19 @@
       </c>
     </row>
     <row r="31" spans="1:8" ht="30" customHeight="1">
-      <c r="A31" s="36">
+      <c r="A31" s="35">
         <v>30</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="40" t="s">
         <v>365</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="40" t="s">
         <v>123</v>
       </c>
-      <c r="D31" s="41" t="s">
+      <c r="D31" s="40" t="s">
         <v>366</v>
       </c>
-      <c r="E31" s="8" t="s">
+      <c r="E31" s="7" t="s">
         <v>367</v>
       </c>
       <c r="F31" s="5">
@@ -7471,16 +7493,16 @@
       <c r="A32" s="5">
         <v>31</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="40" t="s">
         <v>369</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="C32" s="40" t="s">
         <v>368</v>
       </c>
-      <c r="D32" s="41" t="s">
+      <c r="D32" s="40" t="s">
         <v>346</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="E32" s="7" t="s">
         <v>370</v>
       </c>
       <c r="F32" s="5">
@@ -7494,19 +7516,19 @@
       </c>
     </row>
     <row r="33" spans="1:8" ht="30" customHeight="1">
-      <c r="A33" s="36">
+      <c r="A33" s="35">
         <v>32</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="40" t="s">
         <v>373</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="40" t="s">
         <v>372</v>
       </c>
-      <c r="D33" s="41" t="s">
+      <c r="D33" s="40" t="s">
         <v>346</v>
       </c>
-      <c r="E33" s="8"/>
+      <c r="E33" s="7"/>
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
@@ -7515,16 +7537,16 @@
       <c r="A34" s="5">
         <v>33</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>374</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="40" t="s">
         <v>375</v>
       </c>
-      <c r="D34" s="41" t="s">
+      <c r="D34" s="40" t="s">
         <v>376</v>
       </c>
-      <c r="E34" s="8"/>
+      <c r="E34" s="7"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
@@ -7533,907 +7555,907 @@
       <c r="A35" s="5">
         <v>34</v>
       </c>
-      <c r="B35" s="39" t="s">
+      <c r="B35" s="38" t="s">
         <v>378</v>
       </c>
-      <c r="C35" s="39" t="s">
+      <c r="C35" s="38" t="s">
         <v>377</v>
       </c>
-      <c r="D35" s="39" t="s">
+      <c r="D35" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E35" s="44"/>
-      <c r="F35" s="45"/>
-      <c r="G35" s="45"/>
-      <c r="H35" s="45"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="44"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="44"/>
     </row>
     <row r="36" spans="1:8" ht="30" customHeight="1">
       <c r="A36" s="5">
         <v>35</v>
       </c>
-      <c r="B36" s="39" t="s">
+      <c r="B36" s="38" t="s">
         <v>379</v>
       </c>
-      <c r="C36" s="39" t="s">
+      <c r="C36" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D36" s="39" t="s">
+      <c r="D36" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E36" s="45"/>
-      <c r="F36" s="45"/>
-      <c r="G36" s="45"/>
-      <c r="H36" s="45"/>
+      <c r="E36" s="44"/>
+      <c r="F36" s="44"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="44"/>
     </row>
     <row r="37" spans="1:8" ht="30" customHeight="1">
       <c r="A37" s="5">
         <v>36</v>
       </c>
-      <c r="B37" s="39" t="s">
+      <c r="B37" s="38" t="s">
         <v>380</v>
       </c>
-      <c r="C37" s="39" t="s">
+      <c r="C37" s="38" t="s">
         <v>318</v>
       </c>
-      <c r="D37" s="39" t="s">
+      <c r="D37" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E37" s="45"/>
-      <c r="F37" s="45"/>
-      <c r="G37" s="45"/>
-      <c r="H37" s="45"/>
+      <c r="E37" s="44"/>
+      <c r="F37" s="44"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="44"/>
     </row>
     <row r="38" spans="1:8" ht="30" customHeight="1">
       <c r="A38" s="5">
         <v>37</v>
       </c>
-      <c r="B38" s="39" t="s">
+      <c r="B38" s="38" t="s">
         <v>381</v>
       </c>
-      <c r="C38" s="39" t="s">
+      <c r="C38" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="D38" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E38" s="45"/>
-      <c r="F38" s="45"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
+      <c r="E38" s="44"/>
+      <c r="F38" s="44"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="44"/>
     </row>
     <row r="39" spans="1:8" ht="30" customHeight="1">
       <c r="A39" s="5">
         <v>38</v>
       </c>
-      <c r="B39" s="39" t="s">
+      <c r="B39" s="38" t="s">
         <v>383</v>
       </c>
-      <c r="C39" s="39" t="s">
+      <c r="C39" s="38" t="s">
         <v>382</v>
       </c>
-      <c r="D39" s="39" t="s">
+      <c r="D39" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E39" s="45"/>
-      <c r="F39" s="45"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
+      <c r="E39" s="44"/>
+      <c r="F39" s="44"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="44"/>
     </row>
     <row r="40" spans="1:8" ht="30" customHeight="1">
       <c r="A40" s="5">
         <v>39</v>
       </c>
-      <c r="B40" s="39" t="s">
+      <c r="B40" s="38" t="s">
         <v>384</v>
       </c>
-      <c r="C40" s="39" t="s">
+      <c r="C40" s="38" t="s">
         <v>385</v>
       </c>
-      <c r="D40" s="39" t="s">
+      <c r="D40" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
+      <c r="E40" s="44"/>
+      <c r="F40" s="44"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="44"/>
     </row>
     <row r="41" spans="1:8" ht="30" customHeight="1">
       <c r="A41" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="39" t="s">
+      <c r="B41" s="38" t="s">
         <v>387</v>
       </c>
-      <c r="C41" s="39" t="s">
+      <c r="C41" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D41" s="39" t="s">
+      <c r="D41" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="E41" s="45"/>
-      <c r="F41" s="45"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
+      <c r="E41" s="44"/>
+      <c r="F41" s="44"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="44"/>
     </row>
     <row r="42" spans="1:8" ht="30" customHeight="1">
       <c r="A42" s="5">
         <v>41</v>
       </c>
-      <c r="B42" s="39" t="s">
+      <c r="B42" s="38" t="s">
         <v>388</v>
       </c>
-      <c r="C42" s="39" t="s">
+      <c r="C42" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D42" s="39" t="s">
+      <c r="D42" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="E42" s="45"/>
-      <c r="F42" s="45"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
+      <c r="E42" s="44"/>
+      <c r="F42" s="44"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="44"/>
     </row>
     <row r="43" spans="1:8" ht="30" customHeight="1">
       <c r="A43" s="5">
         <v>42</v>
       </c>
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="38" t="s">
         <v>389</v>
       </c>
-      <c r="C43" s="39" t="s">
+      <c r="C43" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D43" s="39" t="s">
+      <c r="D43" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="E43" s="45"/>
-      <c r="F43" s="45"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
+      <c r="E43" s="44"/>
+      <c r="F43" s="44"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="44"/>
     </row>
     <row r="44" spans="1:8" ht="30" customHeight="1">
       <c r="A44" s="5">
         <v>43</v>
       </c>
-      <c r="B44" s="39" t="s">
+      <c r="B44" s="38" t="s">
         <v>390</v>
       </c>
-      <c r="C44" s="39" t="s">
+      <c r="C44" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D44" s="39" t="s">
+      <c r="D44" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="E44" s="45"/>
-      <c r="F44" s="45"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
+      <c r="E44" s="44"/>
+      <c r="F44" s="44"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="44"/>
     </row>
     <row r="45" spans="1:8" ht="30" customHeight="1">
       <c r="A45" s="5">
         <v>44</v>
       </c>
-      <c r="B45" s="39" t="s">
+      <c r="B45" s="38" t="s">
         <v>391</v>
       </c>
-      <c r="C45" s="39" t="s">
+      <c r="C45" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D45" s="39" t="s">
+      <c r="D45" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="E45" s="45"/>
-      <c r="F45" s="45"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
     </row>
     <row r="46" spans="1:8" ht="30" customHeight="1">
       <c r="A46" s="5">
         <v>45</v>
       </c>
-      <c r="B46" s="39" t="s">
+      <c r="B46" s="38" t="s">
         <v>396</v>
       </c>
-      <c r="C46" s="39" t="s">
+      <c r="C46" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D46" s="39" t="s">
+      <c r="D46" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="E46" s="45"/>
-      <c r="F46" s="45"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
+      <c r="E46" s="44"/>
+      <c r="F46" s="44"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="44"/>
     </row>
     <row r="47" spans="1:8" ht="30" customHeight="1">
       <c r="A47" s="5">
         <v>46</v>
       </c>
-      <c r="B47" s="39" t="s">
+      <c r="B47" s="38" t="s">
         <v>397</v>
       </c>
-      <c r="C47" s="39" t="s">
+      <c r="C47" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D47" s="39" t="s">
+      <c r="D47" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
     </row>
     <row r="48" spans="1:8" ht="30" customHeight="1">
       <c r="A48" s="5">
         <v>47</v>
       </c>
-      <c r="B48" s="39" t="s">
+      <c r="B48" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="C48" s="39" t="s">
+      <c r="C48" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D48" s="39" t="s">
+      <c r="D48" s="38" t="s">
         <v>386</v>
       </c>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
     </row>
     <row r="49" spans="1:8" ht="30" customHeight="1">
       <c r="A49" s="5">
         <v>48</v>
       </c>
-      <c r="B49" s="39" t="s">
+      <c r="B49" s="38" t="s">
         <v>398</v>
       </c>
-      <c r="C49" s="39" t="s">
+      <c r="C49" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D49" s="39" t="s">
+      <c r="D49" s="38" t="s">
         <v>399</v>
       </c>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
     </row>
     <row r="50" spans="1:8" ht="30" customHeight="1">
       <c r="A50" s="5">
         <v>49</v>
       </c>
-      <c r="B50" s="39" t="s">
+      <c r="B50" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="C50" s="39" t="s">
+      <c r="C50" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D50" s="39" t="s">
+      <c r="D50" s="38" t="s">
         <v>399</v>
       </c>
-      <c r="E50" s="45"/>
-      <c r="F50" s="45"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
+      <c r="E50" s="44"/>
+      <c r="F50" s="44"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="44"/>
     </row>
     <row r="51" spans="1:8" ht="30" customHeight="1">
       <c r="A51" s="5">
         <v>50</v>
       </c>
-      <c r="B51" s="39" t="s">
+      <c r="B51" s="38" t="s">
         <v>400</v>
       </c>
-      <c r="C51" s="39" t="s">
+      <c r="C51" s="38" t="s">
         <v>358</v>
       </c>
-      <c r="D51" s="39" t="s">
+      <c r="D51" s="38" t="s">
         <v>399</v>
       </c>
-      <c r="E51" s="45"/>
-      <c r="F51" s="45"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="44"/>
     </row>
     <row r="52" spans="1:8" ht="30" customHeight="1">
       <c r="A52" s="5">
         <v>51</v>
       </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="45"/>
-      <c r="F52" s="45"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="45"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="44"/>
+      <c r="D52" s="44"/>
+      <c r="E52" s="44"/>
+      <c r="F52" s="44"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="44"/>
     </row>
     <row r="53" spans="1:8" ht="30" customHeight="1">
       <c r="A53" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="45"/>
-      <c r="F53" s="45"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="44"/>
+      <c r="D53" s="44"/>
+      <c r="E53" s="44"/>
+      <c r="F53" s="44"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="44"/>
     </row>
     <row r="54" spans="1:8" ht="30" customHeight="1">
       <c r="A54" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="45"/>
-      <c r="F54" s="45"/>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="44"/>
+      <c r="F54" s="44"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="44"/>
     </row>
     <row r="55" spans="1:8" ht="30" customHeight="1">
       <c r="A55" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="45"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="44"/>
+      <c r="D55" s="44"/>
+      <c r="E55" s="44"/>
+      <c r="F55" s="44"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="44"/>
     </row>
     <row r="56" spans="1:8" ht="30" customHeight="1">
       <c r="A56" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="45"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="45"/>
-      <c r="F56" s="45"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="44"/>
+      <c r="D56" s="44"/>
+      <c r="E56" s="44"/>
+      <c r="F56" s="44"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="44"/>
     </row>
     <row r="57" spans="1:8" ht="30" customHeight="1">
       <c r="A57" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="45"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="45"/>
-      <c r="F57" s="45"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="44"/>
+      <c r="F57" s="44"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="44"/>
     </row>
     <row r="58" spans="1:8" ht="30" customHeight="1">
       <c r="A58" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="45"/>
-      <c r="C58" s="45"/>
-      <c r="D58" s="45"/>
-      <c r="E58" s="45"/>
-      <c r="F58" s="45"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="44"/>
+      <c r="D58" s="44"/>
+      <c r="E58" s="44"/>
+      <c r="F58" s="44"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="44"/>
     </row>
     <row r="59" spans="1:8" ht="30" customHeight="1">
       <c r="A59" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="45"/>
-      <c r="C59" s="45"/>
-      <c r="D59" s="45"/>
-      <c r="E59" s="45"/>
-      <c r="F59" s="45"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="44"/>
+      <c r="D59" s="44"/>
+      <c r="E59" s="44"/>
+      <c r="F59" s="44"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="44"/>
     </row>
     <row r="60" spans="1:8" ht="30" customHeight="1">
       <c r="A60" s="5">
         <v>59</v>
       </c>
-      <c r="B60" s="45"/>
-      <c r="C60" s="45"/>
-      <c r="D60" s="45"/>
-      <c r="E60" s="45"/>
-      <c r="F60" s="45"/>
-      <c r="G60" s="45"/>
-      <c r="H60" s="45"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="44"/>
+      <c r="D60" s="44"/>
+      <c r="E60" s="44"/>
+      <c r="F60" s="44"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="44"/>
     </row>
     <row r="61" spans="1:8" ht="30" customHeight="1">
       <c r="A61" s="5">
         <v>60</v>
       </c>
-      <c r="B61" s="45"/>
-      <c r="C61" s="45"/>
-      <c r="D61" s="45"/>
-      <c r="E61" s="45"/>
-      <c r="F61" s="45"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
+      <c r="B61" s="44"/>
+      <c r="C61" s="44"/>
+      <c r="D61" s="44"/>
+      <c r="E61" s="44"/>
+      <c r="F61" s="44"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="44"/>
     </row>
     <row r="62" spans="1:8" ht="30" customHeight="1">
       <c r="A62" s="5">
         <v>61</v>
       </c>
-      <c r="B62" s="45"/>
-      <c r="C62" s="45"/>
-      <c r="D62" s="45"/>
-      <c r="E62" s="45"/>
-      <c r="F62" s="45"/>
-      <c r="G62" s="45"/>
-      <c r="H62" s="45"/>
+      <c r="B62" s="44"/>
+      <c r="C62" s="44"/>
+      <c r="D62" s="44"/>
+      <c r="E62" s="44"/>
+      <c r="F62" s="44"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="44"/>
     </row>
     <row r="63" spans="1:8" ht="30" customHeight="1">
       <c r="A63" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="45"/>
-      <c r="C63" s="45"/>
-      <c r="D63" s="45"/>
-      <c r="E63" s="45"/>
-      <c r="F63" s="45"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
+      <c r="B63" s="44"/>
+      <c r="C63" s="44"/>
+      <c r="D63" s="44"/>
+      <c r="E63" s="44"/>
+      <c r="F63" s="44"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="44"/>
     </row>
     <row r="64" spans="1:8" ht="30" customHeight="1">
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="45"/>
-      <c r="C64" s="45"/>
-      <c r="D64" s="45"/>
-      <c r="E64" s="45"/>
-      <c r="F64" s="45"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="45"/>
+      <c r="B64" s="44"/>
+      <c r="C64" s="44"/>
+      <c r="D64" s="44"/>
+      <c r="E64" s="44"/>
+      <c r="F64" s="44"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="44"/>
     </row>
     <row r="65" spans="1:8" ht="30" customHeight="1">
       <c r="A65" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="45"/>
-      <c r="C65" s="45"/>
-      <c r="D65" s="45"/>
-      <c r="E65" s="45"/>
-      <c r="F65" s="45"/>
-      <c r="G65" s="45"/>
-      <c r="H65" s="45"/>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+      <c r="E65" s="44"/>
+      <c r="F65" s="44"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="44"/>
     </row>
     <row r="66" spans="1:8" ht="30" customHeight="1">
       <c r="A66" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="45"/>
-      <c r="C66" s="45"/>
-      <c r="D66" s="45"/>
-      <c r="E66" s="45"/>
-      <c r="F66" s="45"/>
-      <c r="G66" s="45"/>
-      <c r="H66" s="45"/>
+      <c r="B66" s="44"/>
+      <c r="C66" s="44"/>
+      <c r="D66" s="44"/>
+      <c r="E66" s="44"/>
+      <c r="F66" s="44"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="44"/>
     </row>
     <row r="67" spans="1:8" ht="30" customHeight="1">
       <c r="A67" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="45"/>
-      <c r="C67" s="45"/>
-      <c r="D67" s="45"/>
-      <c r="E67" s="45"/>
-      <c r="F67" s="45"/>
-      <c r="G67" s="45"/>
-      <c r="H67" s="45"/>
+      <c r="B67" s="44"/>
+      <c r="C67" s="44"/>
+      <c r="D67" s="44"/>
+      <c r="E67" s="44"/>
+      <c r="F67" s="44"/>
+      <c r="G67" s="44"/>
+      <c r="H67" s="44"/>
     </row>
     <row r="68" spans="1:8" ht="30" customHeight="1">
       <c r="A68" s="5">
         <v>67</v>
       </c>
-      <c r="B68" s="45"/>
-      <c r="C68" s="45"/>
-      <c r="D68" s="45"/>
-      <c r="E68" s="45"/>
-      <c r="F68" s="45"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="45"/>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="44"/>
+      <c r="G68" s="44"/>
+      <c r="H68" s="44"/>
     </row>
     <row r="69" spans="1:8" ht="30" customHeight="1">
       <c r="A69" s="5">
         <v>68</v>
       </c>
-      <c r="B69" s="45"/>
-      <c r="C69" s="45"/>
-      <c r="D69" s="45"/>
-      <c r="E69" s="45"/>
-      <c r="F69" s="45"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="45"/>
+      <c r="B69" s="44"/>
+      <c r="C69" s="44"/>
+      <c r="D69" s="44"/>
+      <c r="E69" s="44"/>
+      <c r="F69" s="44"/>
+      <c r="G69" s="44"/>
+      <c r="H69" s="44"/>
     </row>
     <row r="70" spans="1:8" ht="30" customHeight="1">
       <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="45"/>
-      <c r="C70" s="45"/>
-      <c r="D70" s="45"/>
-      <c r="E70" s="45"/>
-      <c r="F70" s="45"/>
-      <c r="G70" s="45"/>
-      <c r="H70" s="45"/>
+      <c r="B70" s="44"/>
+      <c r="C70" s="44"/>
+      <c r="D70" s="44"/>
+      <c r="E70" s="44"/>
+      <c r="F70" s="44"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="44"/>
     </row>
     <row r="71" spans="1:8" ht="30" customHeight="1">
       <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="45"/>
-      <c r="C71" s="45"/>
-      <c r="D71" s="45"/>
-      <c r="E71" s="45"/>
-      <c r="F71" s="45"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
+      <c r="B71" s="44"/>
+      <c r="C71" s="44"/>
+      <c r="D71" s="44"/>
+      <c r="E71" s="44"/>
+      <c r="F71" s="44"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="44"/>
     </row>
     <row r="72" spans="1:8" ht="30" customHeight="1">
       <c r="A72" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="45"/>
-      <c r="C72" s="45"/>
-      <c r="D72" s="45"/>
-      <c r="E72" s="45"/>
-      <c r="F72" s="45"/>
-      <c r="G72" s="45"/>
-      <c r="H72" s="45"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="44"/>
+      <c r="D72" s="44"/>
+      <c r="E72" s="44"/>
+      <c r="F72" s="44"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="44"/>
     </row>
     <row r="73" spans="1:8" ht="30" customHeight="1">
       <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="45"/>
-      <c r="C73" s="45"/>
-      <c r="D73" s="45"/>
-      <c r="E73" s="45"/>
-      <c r="F73" s="45"/>
-      <c r="G73" s="45"/>
-      <c r="H73" s="45"/>
+      <c r="B73" s="44"/>
+      <c r="C73" s="44"/>
+      <c r="D73" s="44"/>
+      <c r="E73" s="44"/>
+      <c r="F73" s="44"/>
+      <c r="G73" s="44"/>
+      <c r="H73" s="44"/>
     </row>
     <row r="74" spans="1:8" ht="30" customHeight="1">
       <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="45"/>
-      <c r="C74" s="45"/>
-      <c r="D74" s="45"/>
-      <c r="E74" s="45"/>
-      <c r="F74" s="45"/>
-      <c r="G74" s="45"/>
-      <c r="H74" s="45"/>
+      <c r="B74" s="44"/>
+      <c r="C74" s="44"/>
+      <c r="D74" s="44"/>
+      <c r="E74" s="44"/>
+      <c r="F74" s="44"/>
+      <c r="G74" s="44"/>
+      <c r="H74" s="44"/>
     </row>
     <row r="75" spans="1:8" ht="30" customHeight="1">
       <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="45"/>
-      <c r="C75" s="45"/>
-      <c r="D75" s="45"/>
-      <c r="E75" s="45"/>
-      <c r="F75" s="45"/>
-      <c r="G75" s="45"/>
-      <c r="H75" s="45"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="44"/>
+      <c r="D75" s="44"/>
+      <c r="E75" s="44"/>
+      <c r="F75" s="44"/>
+      <c r="G75" s="44"/>
+      <c r="H75" s="44"/>
     </row>
     <row r="76" spans="1:8" ht="30" customHeight="1">
       <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="45"/>
-      <c r="C76" s="45"/>
-      <c r="D76" s="45"/>
-      <c r="E76" s="45"/>
-      <c r="F76" s="45"/>
-      <c r="G76" s="45"/>
-      <c r="H76" s="45"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="44"/>
+      <c r="D76" s="44"/>
+      <c r="E76" s="44"/>
+      <c r="F76" s="44"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="44"/>
     </row>
     <row r="77" spans="1:8" ht="30" customHeight="1">
       <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="45"/>
-      <c r="C77" s="45"/>
-      <c r="D77" s="45"/>
-      <c r="E77" s="45"/>
-      <c r="F77" s="45"/>
-      <c r="G77" s="45"/>
-      <c r="H77" s="45"/>
+      <c r="B77" s="44"/>
+      <c r="C77" s="44"/>
+      <c r="D77" s="44"/>
+      <c r="E77" s="44"/>
+      <c r="F77" s="44"/>
+      <c r="G77" s="44"/>
+      <c r="H77" s="44"/>
     </row>
     <row r="78" spans="1:8" ht="30" customHeight="1">
       <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="45"/>
-      <c r="C78" s="45"/>
-      <c r="D78" s="45"/>
-      <c r="E78" s="45"/>
-      <c r="F78" s="45"/>
-      <c r="G78" s="45"/>
-      <c r="H78" s="45"/>
+      <c r="B78" s="44"/>
+      <c r="C78" s="44"/>
+      <c r="D78" s="44"/>
+      <c r="E78" s="44"/>
+      <c r="F78" s="44"/>
+      <c r="G78" s="44"/>
+      <c r="H78" s="44"/>
     </row>
     <row r="79" spans="1:8" ht="30" customHeight="1">
       <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="45"/>
-      <c r="C79" s="45"/>
-      <c r="D79" s="45"/>
-      <c r="E79" s="45"/>
-      <c r="F79" s="45"/>
-      <c r="G79" s="45"/>
-      <c r="H79" s="45"/>
+      <c r="B79" s="44"/>
+      <c r="C79" s="44"/>
+      <c r="D79" s="44"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="44"/>
     </row>
     <row r="80" spans="1:8" ht="30" customHeight="1">
       <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="45"/>
-      <c r="C80" s="45"/>
-      <c r="D80" s="45"/>
-      <c r="E80" s="45"/>
-      <c r="F80" s="45"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="45"/>
+      <c r="B80" s="44"/>
+      <c r="C80" s="44"/>
+      <c r="D80" s="44"/>
+      <c r="E80" s="44"/>
+      <c r="F80" s="44"/>
+      <c r="G80" s="44"/>
+      <c r="H80" s="44"/>
     </row>
     <row r="81" spans="1:8" ht="30" customHeight="1">
       <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="45"/>
-      <c r="C81" s="45"/>
-      <c r="D81" s="45"/>
-      <c r="E81" s="45"/>
-      <c r="F81" s="45"/>
-      <c r="G81" s="45"/>
-      <c r="H81" s="45"/>
+      <c r="B81" s="44"/>
+      <c r="C81" s="44"/>
+      <c r="D81" s="44"/>
+      <c r="E81" s="44"/>
+      <c r="F81" s="44"/>
+      <c r="G81" s="44"/>
+      <c r="H81" s="44"/>
     </row>
     <row r="82" spans="1:8" ht="30" customHeight="1">
       <c r="A82" s="5">
         <v>81</v>
       </c>
-      <c r="B82" s="45"/>
-      <c r="C82" s="45"/>
-      <c r="D82" s="45"/>
-      <c r="E82" s="45"/>
-      <c r="F82" s="45"/>
-      <c r="G82" s="45"/>
-      <c r="H82" s="45"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="44"/>
+      <c r="D82" s="44"/>
+      <c r="E82" s="44"/>
+      <c r="F82" s="44"/>
+      <c r="G82" s="44"/>
+      <c r="H82" s="44"/>
     </row>
     <row r="83" spans="1:8" ht="30" customHeight="1">
       <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="45"/>
-      <c r="C83" s="45"/>
-      <c r="D83" s="45"/>
-      <c r="E83" s="45"/>
-      <c r="F83" s="45"/>
-      <c r="G83" s="45"/>
-      <c r="H83" s="45"/>
+      <c r="B83" s="44"/>
+      <c r="C83" s="44"/>
+      <c r="D83" s="44"/>
+      <c r="E83" s="44"/>
+      <c r="F83" s="44"/>
+      <c r="G83" s="44"/>
+      <c r="H83" s="44"/>
     </row>
     <row r="84" spans="1:8" ht="30" customHeight="1">
       <c r="A84" s="5">
         <v>83</v>
       </c>
-      <c r="B84" s="45"/>
-      <c r="C84" s="45"/>
-      <c r="D84" s="45"/>
-      <c r="E84" s="45"/>
-      <c r="F84" s="45"/>
-      <c r="G84" s="45"/>
-      <c r="H84" s="45"/>
+      <c r="B84" s="44"/>
+      <c r="C84" s="44"/>
+      <c r="D84" s="44"/>
+      <c r="E84" s="44"/>
+      <c r="F84" s="44"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="44"/>
     </row>
     <row r="85" spans="1:8" ht="30" customHeight="1">
       <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="45"/>
-      <c r="C85" s="45"/>
-      <c r="D85" s="45"/>
-      <c r="E85" s="45"/>
-      <c r="F85" s="45"/>
-      <c r="G85" s="45"/>
-      <c r="H85" s="45"/>
+      <c r="B85" s="44"/>
+      <c r="C85" s="44"/>
+      <c r="D85" s="44"/>
+      <c r="E85" s="44"/>
+      <c r="F85" s="44"/>
+      <c r="G85" s="44"/>
+      <c r="H85" s="44"/>
     </row>
     <row r="86" spans="1:8" ht="30" customHeight="1">
       <c r="A86" s="5">
         <v>85</v>
       </c>
-      <c r="B86" s="45"/>
-      <c r="C86" s="45"/>
-      <c r="D86" s="45"/>
-      <c r="E86" s="45"/>
-      <c r="F86" s="45"/>
-      <c r="G86" s="45"/>
-      <c r="H86" s="45"/>
+      <c r="B86" s="44"/>
+      <c r="C86" s="44"/>
+      <c r="D86" s="44"/>
+      <c r="E86" s="44"/>
+      <c r="F86" s="44"/>
+      <c r="G86" s="44"/>
+      <c r="H86" s="44"/>
     </row>
     <row r="87" spans="1:8" ht="30" customHeight="1">
       <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="45"/>
-      <c r="C87" s="45"/>
-      <c r="D87" s="45"/>
-      <c r="E87" s="45"/>
-      <c r="F87" s="45"/>
-      <c r="G87" s="45"/>
-      <c r="H87" s="45"/>
+      <c r="B87" s="44"/>
+      <c r="C87" s="44"/>
+      <c r="D87" s="44"/>
+      <c r="E87" s="44"/>
+      <c r="F87" s="44"/>
+      <c r="G87" s="44"/>
+      <c r="H87" s="44"/>
     </row>
     <row r="88" spans="1:8" ht="30" customHeight="1">
       <c r="A88" s="5">
         <v>87</v>
       </c>
-      <c r="B88" s="45"/>
-      <c r="C88" s="45"/>
-      <c r="D88" s="45"/>
-      <c r="E88" s="45"/>
-      <c r="F88" s="45"/>
-      <c r="G88" s="45"/>
-      <c r="H88" s="45"/>
+      <c r="B88" s="44"/>
+      <c r="C88" s="44"/>
+      <c r="D88" s="44"/>
+      <c r="E88" s="44"/>
+      <c r="F88" s="44"/>
+      <c r="G88" s="44"/>
+      <c r="H88" s="44"/>
     </row>
     <row r="89" spans="1:8" ht="30" customHeight="1">
       <c r="A89" s="5">
         <v>88</v>
       </c>
-      <c r="B89" s="45"/>
-      <c r="C89" s="45"/>
-      <c r="D89" s="45"/>
-      <c r="E89" s="45"/>
-      <c r="F89" s="45"/>
-      <c r="G89" s="45"/>
-      <c r="H89" s="45"/>
+      <c r="B89" s="44"/>
+      <c r="C89" s="44"/>
+      <c r="D89" s="44"/>
+      <c r="E89" s="44"/>
+      <c r="F89" s="44"/>
+      <c r="G89" s="44"/>
+      <c r="H89" s="44"/>
     </row>
     <row r="90" spans="1:8" ht="30" customHeight="1">
       <c r="A90" s="5">
         <v>89</v>
       </c>
-      <c r="B90" s="45"/>
-      <c r="C90" s="45"/>
-      <c r="D90" s="45"/>
-      <c r="E90" s="45"/>
-      <c r="F90" s="45"/>
-      <c r="G90" s="45"/>
-      <c r="H90" s="45"/>
+      <c r="B90" s="44"/>
+      <c r="C90" s="44"/>
+      <c r="D90" s="44"/>
+      <c r="E90" s="44"/>
+      <c r="F90" s="44"/>
+      <c r="G90" s="44"/>
+      <c r="H90" s="44"/>
     </row>
     <row r="91" spans="1:8" ht="30" customHeight="1">
       <c r="A91" s="5">
         <v>90</v>
       </c>
-      <c r="B91" s="45"/>
-      <c r="C91" s="45"/>
-      <c r="D91" s="45"/>
-      <c r="E91" s="45"/>
-      <c r="F91" s="45"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
+      <c r="B91" s="44"/>
+      <c r="C91" s="44"/>
+      <c r="D91" s="44"/>
+      <c r="E91" s="44"/>
+      <c r="F91" s="44"/>
+      <c r="G91" s="44"/>
+      <c r="H91" s="44"/>
     </row>
     <row r="92" spans="1:8" ht="30" customHeight="1">
       <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="45"/>
-      <c r="C92" s="45"/>
-      <c r="D92" s="45"/>
-      <c r="E92" s="45"/>
-      <c r="F92" s="45"/>
-      <c r="G92" s="45"/>
-      <c r="H92" s="45"/>
+      <c r="B92" s="44"/>
+      <c r="C92" s="44"/>
+      <c r="D92" s="44"/>
+      <c r="E92" s="44"/>
+      <c r="F92" s="44"/>
+      <c r="G92" s="44"/>
+      <c r="H92" s="44"/>
     </row>
     <row r="93" spans="1:8" ht="30" customHeight="1">
       <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="45"/>
-      <c r="C93" s="45"/>
-      <c r="D93" s="45"/>
-      <c r="E93" s="45"/>
-      <c r="F93" s="45"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="45"/>
+      <c r="B93" s="44"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="44"/>
+      <c r="E93" s="44"/>
+      <c r="F93" s="44"/>
+      <c r="G93" s="44"/>
+      <c r="H93" s="44"/>
     </row>
     <row r="94" spans="1:8" ht="30" customHeight="1">
       <c r="A94" s="5">
         <v>93</v>
       </c>
-      <c r="B94" s="45"/>
-      <c r="C94" s="45"/>
-      <c r="D94" s="45"/>
-      <c r="E94" s="45"/>
-      <c r="F94" s="45"/>
-      <c r="G94" s="45"/>
-      <c r="H94" s="45"/>
+      <c r="B94" s="44"/>
+      <c r="C94" s="44"/>
+      <c r="D94" s="44"/>
+      <c r="E94" s="44"/>
+      <c r="F94" s="44"/>
+      <c r="G94" s="44"/>
+      <c r="H94" s="44"/>
     </row>
     <row r="95" spans="1:8" ht="30" customHeight="1">
       <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="B95" s="45"/>
-      <c r="C95" s="45"/>
-      <c r="D95" s="45"/>
-      <c r="E95" s="45"/>
-      <c r="F95" s="45"/>
-      <c r="G95" s="45"/>
-      <c r="H95" s="45"/>
+      <c r="B95" s="44"/>
+      <c r="C95" s="44"/>
+      <c r="D95" s="44"/>
+      <c r="E95" s="44"/>
+      <c r="F95" s="44"/>
+      <c r="G95" s="44"/>
+      <c r="H95" s="44"/>
     </row>
     <row r="96" spans="1:8" ht="30" customHeight="1">
       <c r="A96" s="5">
         <v>95</v>
       </c>
-      <c r="B96" s="45"/>
-      <c r="C96" s="45"/>
-      <c r="D96" s="45"/>
-      <c r="E96" s="45"/>
-      <c r="F96" s="45"/>
-      <c r="G96" s="45"/>
-      <c r="H96" s="45"/>
+      <c r="B96" s="44"/>
+      <c r="C96" s="44"/>
+      <c r="D96" s="44"/>
+      <c r="E96" s="44"/>
+      <c r="F96" s="44"/>
+      <c r="G96" s="44"/>
+      <c r="H96" s="44"/>
     </row>
     <row r="97" spans="1:8" ht="30" customHeight="1">
       <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="45"/>
-      <c r="C97" s="45"/>
-      <c r="D97" s="45"/>
-      <c r="E97" s="45"/>
-      <c r="F97" s="45"/>
-      <c r="G97" s="45"/>
-      <c r="H97" s="45"/>
+      <c r="B97" s="44"/>
+      <c r="C97" s="44"/>
+      <c r="D97" s="44"/>
+      <c r="E97" s="44"/>
+      <c r="F97" s="44"/>
+      <c r="G97" s="44"/>
+      <c r="H97" s="44"/>
     </row>
     <row r="98" spans="1:8" ht="30" customHeight="1">
       <c r="A98" s="5">
         <v>97</v>
       </c>
-      <c r="B98" s="45"/>
-      <c r="C98" s="45"/>
-      <c r="D98" s="45"/>
-      <c r="E98" s="45"/>
-      <c r="F98" s="45"/>
-      <c r="G98" s="45"/>
-      <c r="H98" s="45"/>
+      <c r="B98" s="44"/>
+      <c r="C98" s="44"/>
+      <c r="D98" s="44"/>
+      <c r="E98" s="44"/>
+      <c r="F98" s="44"/>
+      <c r="G98" s="44"/>
+      <c r="H98" s="44"/>
     </row>
     <row r="99" spans="1:8" ht="30" customHeight="1">
       <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="45"/>
-      <c r="C99" s="45"/>
-      <c r="D99" s="45"/>
-      <c r="E99" s="45"/>
-      <c r="F99" s="45"/>
-      <c r="G99" s="45"/>
-      <c r="H99" s="45"/>
+      <c r="B99" s="44"/>
+      <c r="C99" s="44"/>
+      <c r="D99" s="44"/>
+      <c r="E99" s="44"/>
+      <c r="F99" s="44"/>
+      <c r="G99" s="44"/>
+      <c r="H99" s="44"/>
     </row>
     <row r="100" spans="1:8" ht="30" customHeight="1">
       <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="45"/>
-      <c r="C100" s="45"/>
-      <c r="D100" s="45"/>
-      <c r="E100" s="45"/>
-      <c r="F100" s="45"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
+      <c r="B100" s="44"/>
+      <c r="C100" s="44"/>
+      <c r="D100" s="44"/>
+      <c r="E100" s="44"/>
+      <c r="F100" s="44"/>
+      <c r="G100" s="44"/>
+      <c r="H100" s="44"/>
     </row>
     <row r="101" spans="1:8" ht="30" customHeight="1">
       <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="45"/>
-      <c r="C101" s="45"/>
-      <c r="D101" s="45"/>
-      <c r="E101" s="45"/>
-      <c r="F101" s="45"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
+      <c r="B101" s="44"/>
+      <c r="C101" s="44"/>
+      <c r="D101" s="44"/>
+      <c r="E101" s="44"/>
+      <c r="F101" s="44"/>
+      <c r="G101" s="44"/>
+      <c r="H101" s="44"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H101"/>
@@ -8463,8 +8485,8 @@
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="11.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.85546875" style="2" customWidth="1"/>
-    <col min="4" max="11" width="25.42578125" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="4" max="12" width="25.42578125" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1">
@@ -8501,12 +8523,14 @@
       <c r="K1" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="L1" s="4"/>
+      <c r="L1" s="3" t="s">
+        <v>401</v>
+      </c>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
     </row>
-    <row r="2" spans="1:15" ht="30" customHeight="1">
+    <row r="2" spans="1:15" ht="45" customHeight="1">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -8525,11 +8549,12 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="30" customHeight="1">
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" spans="1:15" ht="45" customHeight="1">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -8551,12 +8576,13 @@
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-    </row>
-    <row r="4" spans="1:15" ht="30" customHeight="1">
+      <c r="L3" s="7"/>
+    </row>
+    <row r="4" spans="1:15" ht="45" customHeight="1">
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="32">
+      <c r="B4" s="31">
         <v>46245</v>
       </c>
       <c r="C4" s="5" t="s">
@@ -8578,13 +8604,18 @@
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
-    </row>
-    <row r="5" spans="1:15" ht="30" customHeight="1">
+      <c r="L4" s="7"/>
+    </row>
+    <row r="5" spans="1:15" ht="45" customHeight="1">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
+      <c r="B5" s="31">
+        <v>46259</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
@@ -8593,38 +8624,61 @@
       <c r="I5" s="7"/>
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
-    </row>
-    <row r="6" spans="1:15" ht="30" customHeight="1">
+      <c r="L5" s="7" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="45" customHeight="1">
       <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
+      <c r="B6" s="31">
+        <v>46263</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>403</v>
+      </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
+      <c r="E6" s="7" t="s">
+        <v>288</v>
+      </c>
       <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>404</v>
+      </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-    </row>
-    <row r="7" spans="1:15" ht="30" customHeight="1">
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="1:15" ht="45" customHeight="1">
       <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+      <c r="B7" s="31">
+        <v>46266</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>287</v>
+      </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="H7" s="7" t="s">
+        <v>405</v>
+      </c>
       <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-    </row>
-    <row r="8" spans="1:15" ht="30" customHeight="1">
+      <c r="J7" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="L7" s="7"/>
+    </row>
+    <row r="8" spans="1:15" ht="45" customHeight="1">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -8638,8 +8692,9 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-    </row>
-    <row r="9" spans="1:15" ht="30" customHeight="1">
+      <c r="L8" s="7"/>
+    </row>
+    <row r="9" spans="1:15" ht="45" customHeight="1">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -8653,8 +8708,9 @@
       <c r="I9" s="7"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
-    </row>
-    <row r="10" spans="1:15" ht="30" customHeight="1">
+      <c r="L9" s="7"/>
+    </row>
+    <row r="10" spans="1:15" ht="45" customHeight="1">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -8668,8 +8724,9 @@
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:15" ht="30" customHeight="1">
+      <c r="L10" s="7"/>
+    </row>
+    <row r="11" spans="1:15" ht="45" customHeight="1">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -8683,6 +8740,7 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Другое/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/Кино-Книги-Одежда-Спорт.xlsx
@@ -1,22 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Кино" sheetId="1" r:id="rId1"/>
     <sheet name="Книги" sheetId="2" r:id="rId2"/>
-    <sheet name="Одежда" sheetId="3" r:id="rId3"/>
-    <sheet name="Спорт" sheetId="4" r:id="rId4"/>
+    <sheet name="Текущая книга График" sheetId="5" r:id="rId3"/>
+    <sheet name="Одежда" sheetId="3" r:id="rId4"/>
+    <sheet name="Спорт" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Кино!$A$1:$I$221</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Книги!$A$1:$H$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Книги!$A$1:$H$109</definedName>
   </definedNames>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -34,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="416">
   <si>
     <t>№</t>
   </si>
@@ -1271,23 +1277,55 @@
   <si>
     <t>70 кг - 10 раз
 80 кг - 2 по 10</t>
+  </si>
+  <si>
+    <t>Число</t>
+  </si>
+  <si>
+    <t>Страница</t>
+  </si>
+  <si>
+    <t>Джек Лондон</t>
+  </si>
+  <si>
+    <t>Мартин Иден</t>
+  </si>
+  <si>
+    <t>Зов Предков</t>
+  </si>
+  <si>
+    <t>Острие бритвы</t>
+  </si>
+  <si>
+    <t>Этот неподражаемый Дживс</t>
+  </si>
+  <si>
+    <t>К востоку от Эдема</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="166" formatCode="mmm\.yy"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
@@ -1328,14 +1366,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="6" tint="-0.499984740745262"/>
+      <color rgb="FF00B050"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1375,6 +1413,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBAE18F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1447,13 +1491,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1469,62 +1513,62 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1533,40 +1577,59 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="16" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1591,6 +1654,9 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1882,9 +1948,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I222"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="8"/>
     <col min="2" max="2" width="24.85546875" style="8" customWidth="1"/>
@@ -1897,7 +1963,7 @@
     <col min="10" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1">
+    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1926,7 +1992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>6</v>
       </c>
@@ -1949,7 +2015,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="13"/>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>7</v>
       </c>
@@ -1972,7 +2038,7 @@
       <c r="H3" s="10"/>
       <c r="I3" s="13"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>8</v>
       </c>
@@ -1995,7 +2061,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -2024,7 +2090,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -2047,7 +2113,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="13"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>11</v>
       </c>
@@ -2070,7 +2136,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="13"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>9</v>
       </c>
@@ -2093,7 +2159,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="13"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>12</v>
       </c>
@@ -2116,7 +2182,7 @@
       <c r="H9" s="10"/>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>15</v>
       </c>
@@ -2139,7 +2205,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="13"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -2162,7 +2228,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="13"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>1</v>
       </c>
@@ -2191,7 +2257,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>13</v>
       </c>
@@ -2214,7 +2280,7 @@
       <c r="H13" s="10"/>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>2</v>
       </c>
@@ -2237,7 +2303,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>14</v>
       </c>
@@ -2260,7 +2326,7 @@
       <c r="H15" s="10"/>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>16</v>
       </c>
@@ -2283,7 +2349,7 @@
       <c r="H16" s="10"/>
       <c r="I16" s="13"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>10</v>
       </c>
@@ -2306,7 +2372,7 @@
       <c r="H17" s="10"/>
       <c r="I17" s="13"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -2335,7 +2401,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>18</v>
       </c>
@@ -2358,7 +2424,7 @@
       <c r="H19" s="10"/>
       <c r="I19" s="13"/>
     </row>
-    <row r="20" spans="1:9" ht="29.25">
+    <row r="20" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>36</v>
       </c>
@@ -2387,7 +2453,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>20</v>
       </c>
@@ -2410,7 +2476,7 @@
       <c r="H21" s="10"/>
       <c r="I21" s="13"/>
     </row>
-    <row r="22" spans="1:9" ht="29.25">
+    <row r="22" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>37</v>
       </c>
@@ -2433,7 +2499,7 @@
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>39</v>
       </c>
@@ -2454,7 +2520,7 @@
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>21</v>
       </c>
@@ -2483,7 +2549,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>41</v>
       </c>
@@ -2504,7 +2570,7 @@
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>49</v>
       </c>
@@ -2525,7 +2591,7 @@
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>40</v>
       </c>
@@ -2546,7 +2612,7 @@
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>19</v>
       </c>
@@ -2569,7 +2635,7 @@
       <c r="H28" s="10"/>
       <c r="I28" s="13"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>22</v>
       </c>
@@ -2598,7 +2664,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>42</v>
       </c>
@@ -2619,7 +2685,7 @@
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>23</v>
       </c>
@@ -2642,7 +2708,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="13"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>43</v>
       </c>
@@ -2663,7 +2729,7 @@
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>75</v>
       </c>
@@ -2684,7 +2750,7 @@
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>27</v>
       </c>
@@ -2713,7 +2779,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>48</v>
       </c>
@@ -2734,7 +2800,7 @@
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>44</v>
       </c>
@@ -2755,7 +2821,7 @@
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>24</v>
       </c>
@@ -2778,7 +2844,7 @@
       <c r="H37" s="10"/>
       <c r="I37" s="13"/>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>25</v>
       </c>
@@ -2807,7 +2873,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>38</v>
       </c>
@@ -2830,7 +2896,7 @@
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>76</v>
       </c>
@@ -2851,7 +2917,7 @@
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>28</v>
       </c>
@@ -2880,7 +2946,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>80</v>
       </c>
@@ -2901,7 +2967,7 @@
       <c r="H42" s="19"/>
       <c r="I42" s="19"/>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>51</v>
       </c>
@@ -2928,7 +2994,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>127</v>
       </c>
@@ -2957,7 +3023,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>52</v>
       </c>
@@ -2984,7 +3050,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>26</v>
       </c>
@@ -3013,7 +3079,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>70</v>
       </c>
@@ -3040,7 +3106,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>72</v>
       </c>
@@ -3061,7 +3127,7 @@
       <c r="H48" s="19"/>
       <c r="I48" s="19"/>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>46</v>
       </c>
@@ -3082,7 +3148,7 @@
       <c r="H49" s="19"/>
       <c r="I49" s="19"/>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>53</v>
       </c>
@@ -3109,7 +3175,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>65</v>
       </c>
@@ -3136,7 +3202,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>95</v>
       </c>
@@ -3157,7 +3223,7 @@
       <c r="H52" s="19"/>
       <c r="I52" s="19"/>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>74</v>
       </c>
@@ -3184,7 +3250,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>101</v>
       </c>
@@ -3205,7 +3271,7 @@
       <c r="H54" s="19"/>
       <c r="I54" s="19"/>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>112</v>
       </c>
@@ -3232,7 +3298,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>50</v>
       </c>
@@ -3253,7 +3319,7 @@
       <c r="H56" s="19"/>
       <c r="I56" s="19"/>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>66</v>
       </c>
@@ -3280,7 +3346,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>97</v>
       </c>
@@ -3301,7 +3367,7 @@
       <c r="H58" s="19"/>
       <c r="I58" s="19"/>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>130</v>
       </c>
@@ -3328,7 +3394,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="10">
         <v>92</v>
       </c>
@@ -3349,7 +3415,7 @@
       <c r="H60" s="19"/>
       <c r="I60" s="19"/>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>108</v>
       </c>
@@ -3376,7 +3442,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>113</v>
       </c>
@@ -3403,7 +3469,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>47</v>
       </c>
@@ -3430,7 +3496,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>77</v>
       </c>
@@ -3451,7 +3517,7 @@
       <c r="H64" s="19"/>
       <c r="I64" s="19"/>
     </row>
-    <row r="65" spans="1:9" ht="42.75">
+    <row r="65" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>31</v>
       </c>
@@ -3480,7 +3546,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>63</v>
       </c>
@@ -3501,7 +3567,7 @@
       <c r="H66" s="19"/>
       <c r="I66" s="19"/>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>102</v>
       </c>
@@ -3528,7 +3594,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>54</v>
       </c>
@@ -3549,7 +3615,7 @@
       <c r="H68" s="19"/>
       <c r="I68" s="19"/>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>89</v>
       </c>
@@ -3570,7 +3636,7 @@
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>218</v>
       </c>
@@ -3589,7 +3655,7 @@
       <c r="H70" s="10"/>
       <c r="I70" s="23"/>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>29</v>
       </c>
@@ -3618,7 +3684,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>55</v>
       </c>
@@ -3639,7 +3705,7 @@
       <c r="H72" s="19"/>
       <c r="I72" s="19"/>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>91</v>
       </c>
@@ -3660,7 +3726,7 @@
       <c r="H73" s="19"/>
       <c r="I73" s="19"/>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>103</v>
       </c>
@@ -3687,7 +3753,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>114</v>
       </c>
@@ -3714,7 +3780,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="57">
+    <row r="76" spans="1:9" ht="57" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>30</v>
       </c>
@@ -3743,7 +3809,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>104</v>
       </c>
@@ -3770,7 +3836,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>56</v>
       </c>
@@ -3791,7 +3857,7 @@
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>71</v>
       </c>
@@ -3818,7 +3884,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>73</v>
       </c>
@@ -3845,7 +3911,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>94</v>
       </c>
@@ -3872,7 +3938,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="29.25">
+    <row r="82" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>62</v>
       </c>
@@ -3899,7 +3965,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>78</v>
       </c>
@@ -3920,7 +3986,7 @@
       <c r="H83" s="19"/>
       <c r="I83" s="19"/>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>111</v>
       </c>
@@ -3947,7 +4013,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>115</v>
       </c>
@@ -3974,7 +4040,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>131</v>
       </c>
@@ -4003,7 +4069,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>33</v>
       </c>
@@ -4032,7 +4098,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>57</v>
       </c>
@@ -4059,7 +4125,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>116</v>
       </c>
@@ -4080,7 +4146,7 @@
       <c r="H89" s="10"/>
       <c r="I89" s="19"/>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>58</v>
       </c>
@@ -4107,7 +4173,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>69</v>
       </c>
@@ -4128,7 +4194,7 @@
       <c r="H91" s="19"/>
       <c r="I91" s="19"/>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>79</v>
       </c>
@@ -4149,7 +4215,7 @@
       <c r="H92" s="19"/>
       <c r="I92" s="19"/>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>82</v>
       </c>
@@ -4170,7 +4236,7 @@
       <c r="H93" s="19"/>
       <c r="I93" s="19"/>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>109</v>
       </c>
@@ -4197,7 +4263,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>219</v>
       </c>
@@ -4226,7 +4292,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>67</v>
       </c>
@@ -4247,7 +4313,7 @@
       <c r="H96" s="19"/>
       <c r="I96" s="19"/>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>117</v>
       </c>
@@ -4268,7 +4334,7 @@
       <c r="H97" s="10"/>
       <c r="I97" s="19"/>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>99</v>
       </c>
@@ -4289,7 +4355,7 @@
       <c r="H98" s="19"/>
       <c r="I98" s="19"/>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>107</v>
       </c>
@@ -4316,7 +4382,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>126</v>
       </c>
@@ -4345,7 +4411,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="42.75">
+    <row r="101" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>32</v>
       </c>
@@ -4374,7 +4440,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>81</v>
       </c>
@@ -4395,7 +4461,7 @@
       <c r="H102" s="19"/>
       <c r="I102" s="19"/>
     </row>
-    <row r="103" spans="1:9">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>125</v>
       </c>
@@ -4424,7 +4490,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>68</v>
       </c>
@@ -4451,7 +4517,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>106</v>
       </c>
@@ -4480,7 +4546,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="28.5">
+    <row r="106" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>128</v>
       </c>
@@ -4507,7 +4573,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>59</v>
       </c>
@@ -4534,7 +4600,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>87</v>
       </c>
@@ -4555,7 +4621,7 @@
       <c r="H108" s="19"/>
       <c r="I108" s="19"/>
     </row>
-    <row r="109" spans="1:9">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="10">
         <v>118</v>
       </c>
@@ -4582,7 +4648,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>86</v>
       </c>
@@ -4609,7 +4675,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>88</v>
       </c>
@@ -4630,7 +4696,7 @@
       <c r="H111" s="19"/>
       <c r="I111" s="19"/>
     </row>
-    <row r="112" spans="1:9">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="10">
         <v>85</v>
       </c>
@@ -4651,7 +4717,7 @@
       <c r="H112" s="26"/>
       <c r="I112" s="26"/>
     </row>
-    <row r="113" spans="1:9">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>96</v>
       </c>
@@ -4672,7 +4738,7 @@
       <c r="H113" s="19"/>
       <c r="I113" s="19"/>
     </row>
-    <row r="114" spans="1:9">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="10">
         <v>105</v>
       </c>
@@ -4693,7 +4759,7 @@
       <c r="H114" s="19"/>
       <c r="I114" s="19"/>
     </row>
-    <row r="115" spans="1:9" ht="28.5">
+    <row r="115" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A115" s="10">
         <v>34</v>
       </c>
@@ -4716,7 +4782,7 @@
       <c r="H115" s="10"/>
       <c r="I115" s="13"/>
     </row>
-    <row r="116" spans="1:9">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="10">
         <v>60</v>
       </c>
@@ -4743,7 +4809,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="117" spans="1:9">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="10">
         <v>119</v>
       </c>
@@ -4772,7 +4838,7 @@
         <v>46260</v>
       </c>
     </row>
-    <row r="118" spans="1:9">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="10">
         <v>129</v>
       </c>
@@ -4799,7 +4865,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="10">
         <v>61</v>
       </c>
@@ -4820,7 +4886,7 @@
       <c r="H119" s="19"/>
       <c r="I119" s="19"/>
     </row>
-    <row r="120" spans="1:9">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="10">
         <v>100</v>
       </c>
@@ -4841,7 +4907,7 @@
       <c r="H120" s="19"/>
       <c r="I120" s="19"/>
     </row>
-    <row r="121" spans="1:9">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="10">
         <v>83</v>
       </c>
@@ -4862,7 +4928,7 @@
       <c r="H121" s="19"/>
       <c r="I121" s="19"/>
     </row>
-    <row r="122" spans="1:9">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="10">
         <v>98</v>
       </c>
@@ -4883,7 +4949,7 @@
       <c r="H122" s="19"/>
       <c r="I122" s="19"/>
     </row>
-    <row r="123" spans="1:9">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="10">
         <v>120</v>
       </c>
@@ -4910,7 +4976,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="124" spans="1:9">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="10">
         <v>90</v>
       </c>
@@ -4931,7 +4997,7 @@
       <c r="H124" s="19"/>
       <c r="I124" s="19"/>
     </row>
-    <row r="125" spans="1:9">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="10">
         <v>121</v>
       </c>
@@ -4958,7 +5024,7 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="29.25">
+    <row r="126" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
       <c r="A126" s="10">
         <v>122</v>
       </c>
@@ -4979,7 +5045,7 @@
       <c r="H126" s="10"/>
       <c r="I126" s="19"/>
     </row>
-    <row r="127" spans="1:9" ht="42.75">
+    <row r="127" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A127" s="10">
         <v>35</v>
       </c>
@@ -5008,7 +5074,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="128" spans="1:9">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="10">
         <v>64</v>
       </c>
@@ -5029,7 +5095,7 @@
       <c r="H128" s="19"/>
       <c r="I128" s="19"/>
     </row>
-    <row r="129" spans="1:9">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="10">
         <v>110</v>
       </c>
@@ -5056,7 +5122,7 @@
         <v>45231</v>
       </c>
     </row>
-    <row r="130" spans="1:9">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="10">
         <v>84</v>
       </c>
@@ -5077,7 +5143,7 @@
       <c r="H130" s="19"/>
       <c r="I130" s="19"/>
     </row>
-    <row r="131" spans="1:9">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="10">
         <v>123</v>
       </c>
@@ -5098,7 +5164,7 @@
       <c r="H131" s="10"/>
       <c r="I131" s="19"/>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="10">
         <v>93</v>
       </c>
@@ -5125,7 +5191,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="10">
         <v>124</v>
       </c>
@@ -5152,7 +5218,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="10">
         <v>45</v>
       </c>
@@ -5173,7 +5239,7 @@
       <c r="H134" s="19"/>
       <c r="I134" s="19"/>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="10">
         <v>132</v>
       </c>
@@ -5192,7 +5258,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="10">
         <v>133</v>
       </c>
@@ -5211,7 +5277,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="10">
         <v>134</v>
       </c>
@@ -5230,7 +5296,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="10">
         <v>135</v>
       </c>
@@ -5249,7 +5315,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="10">
         <v>136</v>
       </c>
@@ -5268,7 +5334,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="10">
         <v>137</v>
       </c>
@@ -5287,7 +5353,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="10">
         <v>138</v>
       </c>
@@ -5306,7 +5372,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="10">
         <v>139</v>
       </c>
@@ -5325,7 +5391,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="10">
         <v>140</v>
       </c>
@@ -5344,7 +5410,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="10">
         <v>141</v>
       </c>
@@ -5363,7 +5429,7 @@
         <v>45859</v>
       </c>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="10">
         <v>142</v>
       </c>
@@ -5382,7 +5448,7 @@
       <c r="H145" s="10"/>
       <c r="I145" s="23"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="10">
         <v>143</v>
       </c>
@@ -5399,7 +5465,7 @@
       <c r="H146" s="10"/>
       <c r="I146" s="23"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="10">
         <v>144</v>
       </c>
@@ -5416,7 +5482,7 @@
       <c r="H147" s="10"/>
       <c r="I147" s="23"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="10">
         <v>145</v>
       </c>
@@ -5433,7 +5499,7 @@
       <c r="H148" s="10"/>
       <c r="I148" s="23"/>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="10">
         <v>146</v>
       </c>
@@ -5452,7 +5518,7 @@
       <c r="H149" s="10"/>
       <c r="I149" s="23"/>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="10">
         <v>147</v>
       </c>
@@ -5469,7 +5535,7 @@
       <c r="H150" s="10"/>
       <c r="I150" s="23"/>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="10">
         <v>148</v>
       </c>
@@ -5486,7 +5552,7 @@
       <c r="H151" s="10"/>
       <c r="I151" s="23"/>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="10">
         <v>149</v>
       </c>
@@ -5503,7 +5569,7 @@
       <c r="H152" s="10"/>
       <c r="I152" s="23"/>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="10">
         <v>150</v>
       </c>
@@ -5520,7 +5586,7 @@
       <c r="H153" s="10"/>
       <c r="I153" s="23"/>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="10">
         <v>151</v>
       </c>
@@ -5537,7 +5603,7 @@
       <c r="H154" s="10"/>
       <c r="I154" s="23"/>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="10">
         <v>152</v>
       </c>
@@ -5554,7 +5620,7 @@
       <c r="H155" s="10"/>
       <c r="I155" s="23"/>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="10">
         <v>153</v>
       </c>
@@ -5571,7 +5637,7 @@
       <c r="H156" s="10"/>
       <c r="I156" s="23"/>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="10">
         <v>154</v>
       </c>
@@ -5588,7 +5654,7 @@
       <c r="H157" s="10"/>
       <c r="I157" s="23"/>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="10">
         <v>155</v>
       </c>
@@ -5605,7 +5671,7 @@
       <c r="H158" s="10"/>
       <c r="I158" s="23"/>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="10">
         <v>156</v>
       </c>
@@ -5622,7 +5688,7 @@
       <c r="H159" s="10"/>
       <c r="I159" s="23"/>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="10">
         <v>157</v>
       </c>
@@ -5639,7 +5705,7 @@
       <c r="H160" s="10"/>
       <c r="I160" s="23"/>
     </row>
-    <row r="161" spans="1:9">
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="10">
         <v>158</v>
       </c>
@@ -5656,7 +5722,7 @@
       <c r="H161" s="10"/>
       <c r="I161" s="23"/>
     </row>
-    <row r="162" spans="1:9">
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="10">
         <v>159</v>
       </c>
@@ -5671,7 +5737,7 @@
       <c r="H162" s="10"/>
       <c r="I162" s="23"/>
     </row>
-    <row r="163" spans="1:9">
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="10">
         <v>160</v>
       </c>
@@ -5686,7 +5752,7 @@
       <c r="H163" s="10"/>
       <c r="I163" s="23"/>
     </row>
-    <row r="164" spans="1:9">
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="10">
         <v>161</v>
       </c>
@@ -5701,7 +5767,7 @@
       <c r="H164" s="10"/>
       <c r="I164" s="23"/>
     </row>
-    <row r="165" spans="1:9">
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="10">
         <v>162</v>
       </c>
@@ -5716,7 +5782,7 @@
       <c r="H165" s="10"/>
       <c r="I165" s="23"/>
     </row>
-    <row r="166" spans="1:9">
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="10">
         <v>163</v>
       </c>
@@ -5731,7 +5797,7 @@
       <c r="H166" s="10"/>
       <c r="I166" s="23"/>
     </row>
-    <row r="167" spans="1:9">
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="10">
         <v>164</v>
       </c>
@@ -5746,7 +5812,7 @@
       <c r="H167" s="10"/>
       <c r="I167" s="23"/>
     </row>
-    <row r="168" spans="1:9">
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="10">
         <v>165</v>
       </c>
@@ -5761,7 +5827,7 @@
       <c r="H168" s="10"/>
       <c r="I168" s="23"/>
     </row>
-    <row r="169" spans="1:9">
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="10">
         <v>166</v>
       </c>
@@ -5776,7 +5842,7 @@
       <c r="H169" s="10"/>
       <c r="I169" s="23"/>
     </row>
-    <row r="170" spans="1:9">
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="10">
         <v>167</v>
       </c>
@@ -5791,7 +5857,7 @@
       <c r="H170" s="10"/>
       <c r="I170" s="23"/>
     </row>
-    <row r="171" spans="1:9">
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="10">
         <v>168</v>
       </c>
@@ -5806,7 +5872,7 @@
       <c r="H171" s="10"/>
       <c r="I171" s="23"/>
     </row>
-    <row r="172" spans="1:9">
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="10">
         <v>169</v>
       </c>
@@ -5821,7 +5887,7 @@
       <c r="H172" s="10"/>
       <c r="I172" s="23"/>
     </row>
-    <row r="173" spans="1:9">
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="10">
         <v>170</v>
       </c>
@@ -5836,7 +5902,7 @@
       <c r="H173" s="10"/>
       <c r="I173" s="23"/>
     </row>
-    <row r="174" spans="1:9">
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="10">
         <v>171</v>
       </c>
@@ -5851,7 +5917,7 @@
       <c r="H174" s="10"/>
       <c r="I174" s="23"/>
     </row>
-    <row r="175" spans="1:9">
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="10">
         <v>172</v>
       </c>
@@ -5866,7 +5932,7 @@
       <c r="H175" s="10"/>
       <c r="I175" s="23"/>
     </row>
-    <row r="176" spans="1:9">
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="10">
         <v>173</v>
       </c>
@@ -5881,7 +5947,7 @@
       <c r="H176" s="10"/>
       <c r="I176" s="23"/>
     </row>
-    <row r="177" spans="1:9">
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="10">
         <v>174</v>
       </c>
@@ -5896,7 +5962,7 @@
       <c r="H177" s="10"/>
       <c r="I177" s="23"/>
     </row>
-    <row r="178" spans="1:9">
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="10">
         <v>175</v>
       </c>
@@ -5911,7 +5977,7 @@
       <c r="H178" s="10"/>
       <c r="I178" s="23"/>
     </row>
-    <row r="179" spans="1:9">
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="10">
         <v>176</v>
       </c>
@@ -5926,7 +5992,7 @@
       <c r="H179" s="10"/>
       <c r="I179" s="23"/>
     </row>
-    <row r="180" spans="1:9">
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="10">
         <v>177</v>
       </c>
@@ -5941,7 +6007,7 @@
       <c r="H180" s="10"/>
       <c r="I180" s="23"/>
     </row>
-    <row r="181" spans="1:9">
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="10">
         <v>178</v>
       </c>
@@ -5956,7 +6022,7 @@
       <c r="H181" s="10"/>
       <c r="I181" s="23"/>
     </row>
-    <row r="182" spans="1:9">
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="10">
         <v>179</v>
       </c>
@@ -5971,7 +6037,7 @@
       <c r="H182" s="10"/>
       <c r="I182" s="23"/>
     </row>
-    <row r="183" spans="1:9">
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="10">
         <v>180</v>
       </c>
@@ -5986,7 +6052,7 @@
       <c r="H183" s="10"/>
       <c r="I183" s="23"/>
     </row>
-    <row r="184" spans="1:9">
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="10">
         <v>181</v>
       </c>
@@ -6001,7 +6067,7 @@
       <c r="H184" s="10"/>
       <c r="I184" s="23"/>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="10">
         <v>182</v>
       </c>
@@ -6016,7 +6082,7 @@
       <c r="H185" s="10"/>
       <c r="I185" s="23"/>
     </row>
-    <row r="186" spans="1:9">
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="10">
         <v>183</v>
       </c>
@@ -6031,7 +6097,7 @@
       <c r="H186" s="10"/>
       <c r="I186" s="23"/>
     </row>
-    <row r="187" spans="1:9">
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="10">
         <v>184</v>
       </c>
@@ -6046,7 +6112,7 @@
       <c r="H187" s="10"/>
       <c r="I187" s="23"/>
     </row>
-    <row r="188" spans="1:9">
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="10">
         <v>185</v>
       </c>
@@ -6061,7 +6127,7 @@
       <c r="H188" s="10"/>
       <c r="I188" s="23"/>
     </row>
-    <row r="189" spans="1:9">
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="10">
         <v>186</v>
       </c>
@@ -6076,7 +6142,7 @@
       <c r="H189" s="10"/>
       <c r="I189" s="23"/>
     </row>
-    <row r="190" spans="1:9">
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="10">
         <v>187</v>
       </c>
@@ -6091,7 +6157,7 @@
       <c r="H190" s="10"/>
       <c r="I190" s="23"/>
     </row>
-    <row r="191" spans="1:9">
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="10">
         <v>188</v>
       </c>
@@ -6106,7 +6172,7 @@
       <c r="H191" s="10"/>
       <c r="I191" s="23"/>
     </row>
-    <row r="192" spans="1:9">
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="10">
         <v>189</v>
       </c>
@@ -6125,7 +6191,7 @@
       <c r="H192" s="10"/>
       <c r="I192" s="23"/>
     </row>
-    <row r="193" spans="1:9">
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="10">
         <v>190</v>
       </c>
@@ -6144,7 +6210,7 @@
       <c r="H193" s="10"/>
       <c r="I193" s="23"/>
     </row>
-    <row r="194" spans="1:9">
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="10">
         <v>191</v>
       </c>
@@ -6163,7 +6229,7 @@
       <c r="H194" s="10"/>
       <c r="I194" s="23"/>
     </row>
-    <row r="195" spans="1:9">
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="10">
         <v>192</v>
       </c>
@@ -6182,7 +6248,7 @@
       <c r="H195" s="10"/>
       <c r="I195" s="23"/>
     </row>
-    <row r="196" spans="1:9">
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="10">
         <v>193</v>
       </c>
@@ -6201,7 +6267,7 @@
       <c r="H196" s="10"/>
       <c r="I196" s="23"/>
     </row>
-    <row r="197" spans="1:9">
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="10">
         <v>194</v>
       </c>
@@ -6220,7 +6286,7 @@
       <c r="H197" s="10"/>
       <c r="I197" s="23"/>
     </row>
-    <row r="198" spans="1:9">
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="10">
         <v>195</v>
       </c>
@@ -6239,7 +6305,7 @@
       <c r="H198" s="10"/>
       <c r="I198" s="23"/>
     </row>
-    <row r="199" spans="1:9">
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="10">
         <v>196</v>
       </c>
@@ -6258,7 +6324,7 @@
       <c r="H199" s="10"/>
       <c r="I199" s="23"/>
     </row>
-    <row r="200" spans="1:9">
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="10">
         <v>197</v>
       </c>
@@ -6277,7 +6343,7 @@
       <c r="H200" s="10"/>
       <c r="I200" s="23"/>
     </row>
-    <row r="201" spans="1:9">
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="10">
         <v>198</v>
       </c>
@@ -6294,7 +6360,7 @@
       <c r="H201" s="10"/>
       <c r="I201" s="23"/>
     </row>
-    <row r="202" spans="1:9">
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="10">
         <v>199</v>
       </c>
@@ -6311,7 +6377,7 @@
       <c r="H202" s="10"/>
       <c r="I202" s="23"/>
     </row>
-    <row r="203" spans="1:9">
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="10">
         <v>200</v>
       </c>
@@ -6328,7 +6394,7 @@
       <c r="H203" s="10"/>
       <c r="I203" s="23"/>
     </row>
-    <row r="204" spans="1:9">
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="10">
         <v>201</v>
       </c>
@@ -6347,7 +6413,7 @@
       <c r="H204" s="10"/>
       <c r="I204" s="23"/>
     </row>
-    <row r="205" spans="1:9">
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="10">
         <v>202</v>
       </c>
@@ -6366,7 +6432,7 @@
       <c r="H205" s="10"/>
       <c r="I205" s="23"/>
     </row>
-    <row r="206" spans="1:9">
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="10">
         <v>203</v>
       </c>
@@ -6385,7 +6451,7 @@
       <c r="H206" s="10"/>
       <c r="I206" s="23"/>
     </row>
-    <row r="207" spans="1:9">
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="10">
         <v>204</v>
       </c>
@@ -6402,7 +6468,7 @@
       <c r="H207" s="10"/>
       <c r="I207" s="23"/>
     </row>
-    <row r="208" spans="1:9">
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="10">
         <v>205</v>
       </c>
@@ -6419,7 +6485,7 @@
       <c r="H208" s="10"/>
       <c r="I208" s="23"/>
     </row>
-    <row r="209" spans="1:9">
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="10">
         <v>206</v>
       </c>
@@ -6436,7 +6502,7 @@
       <c r="H209" s="10"/>
       <c r="I209" s="23"/>
     </row>
-    <row r="210" spans="1:9">
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="10">
         <v>207</v>
       </c>
@@ -6455,7 +6521,7 @@
       <c r="H210" s="10"/>
       <c r="I210" s="23"/>
     </row>
-    <row r="211" spans="1:9">
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="10">
         <v>208</v>
       </c>
@@ -6474,7 +6540,7 @@
       <c r="H211" s="10"/>
       <c r="I211" s="23"/>
     </row>
-    <row r="212" spans="1:9">
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="10">
         <v>209</v>
       </c>
@@ -6491,7 +6557,7 @@
       <c r="H212" s="10"/>
       <c r="I212" s="23"/>
     </row>
-    <row r="213" spans="1:9">
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="10">
         <v>210</v>
       </c>
@@ -6508,7 +6574,7 @@
       <c r="H213" s="10"/>
       <c r="I213" s="23"/>
     </row>
-    <row r="214" spans="1:9">
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="10">
         <v>211</v>
       </c>
@@ -6527,7 +6593,7 @@
       <c r="H214" s="10"/>
       <c r="I214" s="23"/>
     </row>
-    <row r="215" spans="1:9">
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="10">
         <v>212</v>
       </c>
@@ -6544,7 +6610,7 @@
       <c r="H215" s="10"/>
       <c r="I215" s="23"/>
     </row>
-    <row r="216" spans="1:9">
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="10">
         <v>213</v>
       </c>
@@ -6561,7 +6627,7 @@
       <c r="H216" s="10"/>
       <c r="I216" s="23"/>
     </row>
-    <row r="217" spans="1:9">
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="10">
         <v>214</v>
       </c>
@@ -6580,7 +6646,7 @@
       <c r="H217" s="10"/>
       <c r="I217" s="23"/>
     </row>
-    <row r="218" spans="1:9">
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="10">
         <v>215</v>
       </c>
@@ -6597,7 +6663,7 @@
       <c r="H218" s="10"/>
       <c r="I218" s="23"/>
     </row>
-    <row r="219" spans="1:9">
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="10">
         <v>216</v>
       </c>
@@ -6614,7 +6680,7 @@
       <c r="H219" s="10"/>
       <c r="I219" s="23"/>
     </row>
-    <row r="220" spans="1:9">
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="10">
         <v>217</v>
       </c>
@@ -6631,7 +6697,7 @@
       <c r="H220" s="10"/>
       <c r="I220" s="23"/>
     </row>
-    <row r="221" spans="1:9">
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="10">
         <v>220</v>
       </c>
@@ -6644,7 +6710,7 @@
       <c r="H221" s="10"/>
       <c r="I221" s="23"/>
     </row>
-    <row r="222" spans="1:9">
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="10"/>
       <c r="B222" s="16"/>
       <c r="C222" s="19"/>
@@ -6656,9 +6722,7 @@
       <c r="I222" s="23"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I221">
-    <extLst/>
-  </autoFilter>
+  <autoFilter ref="A1:I221"/>
   <conditionalFormatting sqref="A2:I222">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2="Просмотрен"</formula>
@@ -6670,9 +6734,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H101"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:H109"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
     <col min="2" max="2" width="33.7109375" style="8" customWidth="1"/>
@@ -6683,7 +6747,7 @@
     <col min="9" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
@@ -6709,7 +6773,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
+    <row r="2" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -6735,7 +6799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
+    <row r="3" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -6761,7 +6825,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
+    <row r="4" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35">
         <v>3</v>
       </c>
@@ -6787,7 +6851,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1">
+    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -6813,7 +6877,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1">
+    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -6839,7 +6903,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1">
+    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -6865,7 +6929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1">
+    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -6891,7 +6955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1">
+    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -6917,7 +6981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1">
+    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -6943,7 +7007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1">
+    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -6969,7 +7033,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1">
+    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -6995,7 +7059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1">
+    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -7021,7 +7085,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1">
+    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -7047,7 +7111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1">
+    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -7073,7 +7137,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1">
+    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -7099,7 +7163,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1">
+    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -7125,7 +7189,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1">
+    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="35">
         <v>17</v>
       </c>
@@ -7151,33 +7215,33 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1">
-      <c r="A19" s="41">
+    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="35">
         <v>18</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B19" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C19" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D19" s="40" t="s">
         <v>321</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="40" t="s">
         <v>316</v>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="5">
         <v>2023</v>
       </c>
-      <c r="G19" s="41" t="s">
+      <c r="G19" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="41" t="s">
+      <c r="H19" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1">
+    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="35">
         <v>19</v>
       </c>
@@ -7203,7 +7267,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1">
+    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
@@ -7229,7 +7293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1">
+    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="35">
         <v>21</v>
       </c>
@@ -7255,7 +7319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1">
+    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
@@ -7281,7 +7345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1">
+    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="35">
         <v>23</v>
       </c>
@@ -7307,7 +7371,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1">
+    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -7333,7 +7397,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1">
+    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="35">
         <v>25</v>
       </c>
@@ -7359,7 +7423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1">
+    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -7385,7 +7449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1">
+    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="35">
         <v>27</v>
       </c>
@@ -7411,7 +7475,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1">
+    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -7437,7 +7501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1">
+    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="35">
         <v>29</v>
       </c>
@@ -7463,7 +7527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1">
+    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="35">
         <v>30</v>
       </c>
@@ -7489,7 +7553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1">
+    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -7515,950 +7579,1060 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1">
-      <c r="A33" s="35">
+    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="43">
         <v>32</v>
       </c>
-      <c r="B33" s="40" t="s">
+      <c r="B33" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="C33" s="40" t="s">
+      <c r="C33" s="44" t="s">
         <v>372</v>
       </c>
-      <c r="D33" s="40" t="s">
+      <c r="D33" s="44" t="s">
         <v>346</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-    </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1">
-      <c r="A34" s="5">
-        <v>33</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>376</v>
+      <c r="E33" s="45"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+    </row>
+    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="52" t="s">
+        <v>411</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>410</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>346</v>
       </c>
       <c r="E34" s="7"/>
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
     </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1">
-      <c r="A35" s="5">
-        <v>34</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>378</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>377</v>
-      </c>
-      <c r="D35" s="38" t="s">
+    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="5"/>
+      <c r="B35" s="52" t="s">
+        <v>412</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>410</v>
+      </c>
+      <c r="D35" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="E35" s="43"/>
-      <c r="F35" s="44"/>
-      <c r="G35" s="44"/>
-      <c r="H35" s="44"/>
-    </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1">
-      <c r="A36" s="5">
-        <v>35</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>379</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>318</v>
-      </c>
-      <c r="D36" s="38" t="s">
+      <c r="E35" s="7"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="5"/>
+      <c r="B36" s="52" t="s">
+        <v>413</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>382</v>
+      </c>
+      <c r="D36" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="E36" s="44"/>
-      <c r="F36" s="44"/>
-      <c r="G36" s="44"/>
-      <c r="H36" s="44"/>
-    </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1">
-      <c r="A37" s="5">
-        <v>36</v>
-      </c>
+      <c r="E36" s="7"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
       <c r="B37" s="38" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C37" s="38" t="s">
-        <v>318</v>
+        <v>382</v>
       </c>
       <c r="D37" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E37" s="44"/>
-      <c r="F37" s="44"/>
-      <c r="G37" s="44"/>
-      <c r="H37" s="44"/>
-    </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1">
-      <c r="A38" s="5">
-        <v>37</v>
-      </c>
+      <c r="E37" s="7"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="53"/>
       <c r="B38" s="38" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>382</v>
+        <v>318</v>
       </c>
       <c r="D38" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E38" s="44"/>
-      <c r="F38" s="44"/>
-      <c r="G38" s="44"/>
-      <c r="H38" s="44"/>
-    </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1">
-      <c r="A39" s="5">
-        <v>38</v>
-      </c>
+      <c r="E38" s="7"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5"/>
       <c r="B39" s="38" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C39" s="38" t="s">
-        <v>382</v>
+        <v>318</v>
       </c>
       <c r="D39" s="38" t="s">
         <v>346</v>
       </c>
-      <c r="E39" s="44"/>
-      <c r="F39" s="44"/>
-      <c r="G39" s="44"/>
-      <c r="H39" s="44"/>
-    </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1">
-      <c r="A40" s="5">
-        <v>39</v>
-      </c>
-      <c r="B40" s="38" t="s">
-        <v>384</v>
+      <c r="E39" s="7"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="5"/>
+      <c r="B40" s="51" t="s">
+        <v>414</v>
       </c>
       <c r="C40" s="38" t="s">
         <v>385</v>
       </c>
-      <c r="D40" s="38" t="s">
+      <c r="D40" s="51" t="s">
         <v>346</v>
       </c>
-      <c r="E40" s="44"/>
-      <c r="F40" s="44"/>
-      <c r="G40" s="44"/>
-      <c r="H40" s="44"/>
-    </row>
-    <row r="41" spans="1:8" ht="30" customHeight="1">
-      <c r="A41" s="5">
+      <c r="E40" s="7"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="5"/>
+      <c r="B41" s="51" t="s">
+        <v>378</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>377</v>
+      </c>
+      <c r="D41" s="51" t="s">
+        <v>346</v>
+      </c>
+      <c r="E41" s="7"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="5"/>
+      <c r="B42" s="51" t="s">
+        <v>415</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>368</v>
+      </c>
+      <c r="D42" s="51" t="s">
+        <v>346</v>
+      </c>
+      <c r="E42" s="7"/>
+      <c r="F42" s="5"/>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="5"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="51"/>
+      <c r="D43" s="51"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="5"/>
+      <c r="B44" s="38"/>
+      <c r="C44" s="38"/>
+      <c r="D44" s="38"/>
+      <c r="E44" s="7"/>
+      <c r="F44" s="5"/>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="5">
+        <v>33</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C45" s="40" t="s">
+        <v>375</v>
+      </c>
+      <c r="D45" s="40" t="s">
+        <v>376</v>
+      </c>
+      <c r="E45" s="7"/>
+      <c r="F45" s="5"/>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5">
+        <v>34</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>378</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>377</v>
+      </c>
+      <c r="D46" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="E46" s="41"/>
+      <c r="F46" s="42"/>
+      <c r="G46" s="42"/>
+      <c r="H46" s="42"/>
+    </row>
+    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5">
+        <v>38</v>
+      </c>
+      <c r="B47" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="C47" s="38" t="s">
+        <v>382</v>
+      </c>
+      <c r="D47" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42"/>
+    </row>
+    <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5">
+        <v>39</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>384</v>
+      </c>
+      <c r="C48" s="38" t="s">
+        <v>385</v>
+      </c>
+      <c r="D48" s="38" t="s">
+        <v>346</v>
+      </c>
+      <c r="E48" s="42"/>
+      <c r="F48" s="42"/>
+      <c r="G48" s="42"/>
+      <c r="H48" s="42"/>
+    </row>
+    <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5">
         <v>40</v>
       </c>
-      <c r="B41" s="38" t="s">
+      <c r="B49" s="38" t="s">
         <v>387</v>
-      </c>
-      <c r="C41" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D41" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="E41" s="44"/>
-      <c r="F41" s="44"/>
-      <c r="G41" s="44"/>
-      <c r="H41" s="44"/>
-    </row>
-    <row r="42" spans="1:8" ht="30" customHeight="1">
-      <c r="A42" s="5">
-        <v>41</v>
-      </c>
-      <c r="B42" s="38" t="s">
-        <v>388</v>
-      </c>
-      <c r="C42" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D42" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="E42" s="44"/>
-      <c r="F42" s="44"/>
-      <c r="G42" s="44"/>
-      <c r="H42" s="44"/>
-    </row>
-    <row r="43" spans="1:8" ht="30" customHeight="1">
-      <c r="A43" s="5">
-        <v>42</v>
-      </c>
-      <c r="B43" s="38" t="s">
-        <v>389</v>
-      </c>
-      <c r="C43" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D43" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="E43" s="44"/>
-      <c r="F43" s="44"/>
-      <c r="G43" s="44"/>
-      <c r="H43" s="44"/>
-    </row>
-    <row r="44" spans="1:8" ht="30" customHeight="1">
-      <c r="A44" s="5">
-        <v>43</v>
-      </c>
-      <c r="B44" s="38" t="s">
-        <v>390</v>
-      </c>
-      <c r="C44" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D44" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="E44" s="44"/>
-      <c r="F44" s="44"/>
-      <c r="G44" s="44"/>
-      <c r="H44" s="44"/>
-    </row>
-    <row r="45" spans="1:8" ht="30" customHeight="1">
-      <c r="A45" s="5">
-        <v>44</v>
-      </c>
-      <c r="B45" s="38" t="s">
-        <v>391</v>
-      </c>
-      <c r="C45" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D45" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="E45" s="44"/>
-      <c r="F45" s="44"/>
-      <c r="G45" s="44"/>
-      <c r="H45" s="44"/>
-    </row>
-    <row r="46" spans="1:8" ht="30" customHeight="1">
-      <c r="A46" s="5">
-        <v>45</v>
-      </c>
-      <c r="B46" s="38" t="s">
-        <v>396</v>
-      </c>
-      <c r="C46" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D46" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="E46" s="44"/>
-      <c r="F46" s="44"/>
-      <c r="G46" s="44"/>
-      <c r="H46" s="44"/>
-    </row>
-    <row r="47" spans="1:8" ht="30" customHeight="1">
-      <c r="A47" s="5">
-        <v>46</v>
-      </c>
-      <c r="B47" s="38" t="s">
-        <v>397</v>
-      </c>
-      <c r="C47" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D47" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="E47" s="44"/>
-      <c r="F47" s="44"/>
-      <c r="G47" s="44"/>
-      <c r="H47" s="44"/>
-    </row>
-    <row r="48" spans="1:8" ht="30" customHeight="1">
-      <c r="A48" s="5">
-        <v>47</v>
-      </c>
-      <c r="B48" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="C48" s="38" t="s">
-        <v>358</v>
-      </c>
-      <c r="D48" s="38" t="s">
-        <v>386</v>
-      </c>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-    </row>
-    <row r="49" spans="1:8" ht="30" customHeight="1">
-      <c r="A49" s="5">
-        <v>48</v>
-      </c>
-      <c r="B49" s="38" t="s">
-        <v>398</v>
       </c>
       <c r="C49" s="38" t="s">
         <v>358</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>399</v>
-      </c>
-      <c r="E49" s="44"/>
-      <c r="F49" s="44"/>
-      <c r="G49" s="44"/>
-      <c r="H49" s="44"/>
-    </row>
-    <row r="50" spans="1:8" ht="30" customHeight="1">
+        <v>386</v>
+      </c>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="42"/>
+      <c r="H49" s="42"/>
+    </row>
+    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>48</v>
+        <v>388</v>
       </c>
       <c r="C50" s="38" t="s">
         <v>358</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>399</v>
-      </c>
-      <c r="E50" s="44"/>
-      <c r="F50" s="44"/>
-      <c r="G50" s="44"/>
-      <c r="H50" s="44"/>
-    </row>
-    <row r="51" spans="1:8" ht="30" customHeight="1">
+        <v>386</v>
+      </c>
+      <c r="E50" s="42"/>
+      <c r="F50" s="42"/>
+      <c r="G50" s="42"/>
+      <c r="H50" s="42"/>
+    </row>
+    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>400</v>
+        <v>389</v>
       </c>
       <c r="C51" s="38" t="s">
         <v>358</v>
       </c>
       <c r="D51" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="E51" s="42"/>
+      <c r="F51" s="42"/>
+      <c r="G51" s="42"/>
+      <c r="H51" s="42"/>
+    </row>
+    <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5">
+        <v>43</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>390</v>
+      </c>
+      <c r="C52" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D52" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="E52" s="42"/>
+      <c r="F52" s="42"/>
+      <c r="G52" s="42"/>
+      <c r="H52" s="42"/>
+    </row>
+    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5">
+        <v>44</v>
+      </c>
+      <c r="B53" s="38" t="s">
+        <v>391</v>
+      </c>
+      <c r="C53" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="E53" s="42"/>
+      <c r="F53" s="42"/>
+      <c r="G53" s="42"/>
+      <c r="H53" s="42"/>
+    </row>
+    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5">
+        <v>45</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>396</v>
+      </c>
+      <c r="C54" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="42"/>
+      <c r="H54" s="42"/>
+    </row>
+    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5">
+        <v>46</v>
+      </c>
+      <c r="B55" s="38" t="s">
+        <v>397</v>
+      </c>
+      <c r="C55" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="E55" s="42"/>
+      <c r="F55" s="42"/>
+      <c r="G55" s="42"/>
+      <c r="H55" s="42"/>
+    </row>
+    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5">
+        <v>47</v>
+      </c>
+      <c r="B56" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="C56" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D56" s="38" t="s">
+        <v>386</v>
+      </c>
+      <c r="E56" s="42"/>
+      <c r="F56" s="42"/>
+      <c r="G56" s="42"/>
+      <c r="H56" s="42"/>
+    </row>
+    <row r="57" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5">
+        <v>48</v>
+      </c>
+      <c r="B57" s="38" t="s">
+        <v>398</v>
+      </c>
+      <c r="C57" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D57" s="38" t="s">
         <v>399</v>
       </c>
-      <c r="E51" s="44"/>
-      <c r="F51" s="44"/>
-      <c r="G51" s="44"/>
-      <c r="H51" s="44"/>
-    </row>
-    <row r="52" spans="1:8" ht="30" customHeight="1">
-      <c r="A52" s="5">
+      <c r="E57" s="42"/>
+      <c r="F57" s="42"/>
+      <c r="G57" s="42"/>
+      <c r="H57" s="42"/>
+    </row>
+    <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>49</v>
+      </c>
+      <c r="B58" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D58" s="38" t="s">
+        <v>399</v>
+      </c>
+      <c r="E58" s="42"/>
+      <c r="F58" s="42"/>
+      <c r="G58" s="42"/>
+      <c r="H58" s="42"/>
+    </row>
+    <row r="59" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>50</v>
+      </c>
+      <c r="B59" s="38" t="s">
+        <v>400</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>358</v>
+      </c>
+      <c r="D59" s="38" t="s">
+        <v>399</v>
+      </c>
+      <c r="E59" s="42"/>
+      <c r="F59" s="42"/>
+      <c r="G59" s="42"/>
+      <c r="H59" s="42"/>
+    </row>
+    <row r="60" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
         <v>51</v>
       </c>
-      <c r="B52" s="44"/>
-      <c r="C52" s="44"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="44"/>
-      <c r="G52" s="44"/>
-      <c r="H52" s="44"/>
-    </row>
-    <row r="53" spans="1:8" ht="30" customHeight="1">
-      <c r="A53" s="5">
+      <c r="B60" s="42"/>
+      <c r="C60" s="42"/>
+      <c r="D60" s="42"/>
+      <c r="E60" s="42"/>
+      <c r="F60" s="42"/>
+      <c r="G60" s="42"/>
+      <c r="H60" s="42"/>
+    </row>
+    <row r="61" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
         <v>52</v>
       </c>
-      <c r="B53" s="44"/>
-      <c r="C53" s="44"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="44"/>
-      <c r="G53" s="44"/>
-      <c r="H53" s="44"/>
-    </row>
-    <row r="54" spans="1:8" ht="30" customHeight="1">
-      <c r="A54" s="5">
+      <c r="B61" s="42"/>
+      <c r="C61" s="42"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="42"/>
+      <c r="H61" s="42"/>
+    </row>
+    <row r="62" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
         <v>53</v>
       </c>
-      <c r="B54" s="44"/>
-      <c r="C54" s="44"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="44"/>
-      <c r="F54" s="44"/>
-      <c r="G54" s="44"/>
-      <c r="H54" s="44"/>
-    </row>
-    <row r="55" spans="1:8" ht="30" customHeight="1">
-      <c r="A55" s="5">
+      <c r="B62" s="42"/>
+      <c r="C62" s="42"/>
+      <c r="D62" s="42"/>
+      <c r="E62" s="42"/>
+      <c r="F62" s="42"/>
+      <c r="G62" s="42"/>
+      <c r="H62" s="42"/>
+    </row>
+    <row r="63" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
         <v>54</v>
       </c>
-      <c r="B55" s="44"/>
-      <c r="C55" s="44"/>
-      <c r="D55" s="44"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="44"/>
-      <c r="G55" s="44"/>
-      <c r="H55" s="44"/>
-    </row>
-    <row r="56" spans="1:8" ht="30" customHeight="1">
-      <c r="A56" s="5">
+      <c r="B63" s="42"/>
+      <c r="C63" s="42"/>
+      <c r="D63" s="42"/>
+      <c r="E63" s="42"/>
+      <c r="F63" s="42"/>
+      <c r="G63" s="42"/>
+      <c r="H63" s="42"/>
+    </row>
+    <row r="64" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
         <v>55</v>
       </c>
-      <c r="B56" s="44"/>
-      <c r="C56" s="44"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="44"/>
-      <c r="G56" s="44"/>
-      <c r="H56" s="44"/>
-    </row>
-    <row r="57" spans="1:8" ht="30" customHeight="1">
-      <c r="A57" s="5">
+      <c r="B64" s="42"/>
+      <c r="C64" s="42"/>
+      <c r="D64" s="42"/>
+      <c r="E64" s="42"/>
+      <c r="F64" s="42"/>
+      <c r="G64" s="42"/>
+      <c r="H64" s="42"/>
+    </row>
+    <row r="65" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
         <v>56</v>
       </c>
-      <c r="B57" s="44"/>
-      <c r="C57" s="44"/>
-      <c r="D57" s="44"/>
-      <c r="E57" s="44"/>
-      <c r="F57" s="44"/>
-      <c r="G57" s="44"/>
-      <c r="H57" s="44"/>
-    </row>
-    <row r="58" spans="1:8" ht="30" customHeight="1">
-      <c r="A58" s="5">
+      <c r="B65" s="42"/>
+      <c r="C65" s="42"/>
+      <c r="D65" s="42"/>
+      <c r="E65" s="42"/>
+      <c r="F65" s="42"/>
+      <c r="G65" s="42"/>
+      <c r="H65" s="42"/>
+    </row>
+    <row r="66" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
         <v>57</v>
       </c>
-      <c r="B58" s="44"/>
-      <c r="C58" s="44"/>
-      <c r="D58" s="44"/>
-      <c r="E58" s="44"/>
-      <c r="F58" s="44"/>
-      <c r="G58" s="44"/>
-      <c r="H58" s="44"/>
-    </row>
-    <row r="59" spans="1:8" ht="30" customHeight="1">
-      <c r="A59" s="5">
+      <c r="B66" s="42"/>
+      <c r="C66" s="42"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="F66" s="42"/>
+      <c r="G66" s="42"/>
+      <c r="H66" s="42"/>
+    </row>
+    <row r="67" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
         <v>58</v>
       </c>
-      <c r="B59" s="44"/>
-      <c r="C59" s="44"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="44"/>
-      <c r="F59" s="44"/>
-      <c r="G59" s="44"/>
-      <c r="H59" s="44"/>
-    </row>
-    <row r="60" spans="1:8" ht="30" customHeight="1">
-      <c r="A60" s="5">
+      <c r="B67" s="42"/>
+      <c r="C67" s="42"/>
+      <c r="D67" s="42"/>
+      <c r="E67" s="42"/>
+      <c r="F67" s="42"/>
+      <c r="G67" s="42"/>
+      <c r="H67" s="42"/>
+    </row>
+    <row r="68" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
         <v>59</v>
       </c>
-      <c r="B60" s="44"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="44"/>
-      <c r="G60" s="44"/>
-      <c r="H60" s="44"/>
-    </row>
-    <row r="61" spans="1:8" ht="30" customHeight="1">
-      <c r="A61" s="5">
+      <c r="B68" s="42"/>
+      <c r="C68" s="42"/>
+      <c r="D68" s="42"/>
+      <c r="E68" s="42"/>
+      <c r="F68" s="42"/>
+      <c r="G68" s="42"/>
+      <c r="H68" s="42"/>
+    </row>
+    <row r="69" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
         <v>60</v>
       </c>
-      <c r="B61" s="44"/>
-      <c r="C61" s="44"/>
-      <c r="D61" s="44"/>
-      <c r="E61" s="44"/>
-      <c r="F61" s="44"/>
-      <c r="G61" s="44"/>
-      <c r="H61" s="44"/>
-    </row>
-    <row r="62" spans="1:8" ht="30" customHeight="1">
-      <c r="A62" s="5">
+      <c r="B69" s="42"/>
+      <c r="C69" s="42"/>
+      <c r="D69" s="42"/>
+      <c r="E69" s="42"/>
+      <c r="F69" s="42"/>
+      <c r="G69" s="42"/>
+      <c r="H69" s="42"/>
+    </row>
+    <row r="70" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
         <v>61</v>
       </c>
-      <c r="B62" s="44"/>
-      <c r="C62" s="44"/>
-      <c r="D62" s="44"/>
-      <c r="E62" s="44"/>
-      <c r="F62" s="44"/>
-      <c r="G62" s="44"/>
-      <c r="H62" s="44"/>
-    </row>
-    <row r="63" spans="1:8" ht="30" customHeight="1">
-      <c r="A63" s="5">
+      <c r="B70" s="42"/>
+      <c r="C70" s="42"/>
+      <c r="D70" s="42"/>
+      <c r="E70" s="42"/>
+      <c r="F70" s="42"/>
+      <c r="G70" s="42"/>
+      <c r="H70" s="42"/>
+    </row>
+    <row r="71" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
         <v>62</v>
       </c>
-      <c r="B63" s="44"/>
-      <c r="C63" s="44"/>
-      <c r="D63" s="44"/>
-      <c r="E63" s="44"/>
-      <c r="F63" s="44"/>
-      <c r="G63" s="44"/>
-      <c r="H63" s="44"/>
-    </row>
-    <row r="64" spans="1:8" ht="30" customHeight="1">
-      <c r="A64" s="5">
+      <c r="B71" s="42"/>
+      <c r="C71" s="42"/>
+      <c r="D71" s="42"/>
+      <c r="E71" s="42"/>
+      <c r="F71" s="42"/>
+      <c r="G71" s="42"/>
+      <c r="H71" s="42"/>
+    </row>
+    <row r="72" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="44"/>
-      <c r="C64" s="44"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="44"/>
-      <c r="F64" s="44"/>
-      <c r="G64" s="44"/>
-      <c r="H64" s="44"/>
-    </row>
-    <row r="65" spans="1:8" ht="30" customHeight="1">
-      <c r="A65" s="5">
+      <c r="B72" s="42"/>
+      <c r="C72" s="42"/>
+      <c r="D72" s="42"/>
+      <c r="E72" s="42"/>
+      <c r="F72" s="42"/>
+      <c r="G72" s="42"/>
+      <c r="H72" s="42"/>
+    </row>
+    <row r="73" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
         <v>64</v>
       </c>
-      <c r="B65" s="44"/>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-    </row>
-    <row r="66" spans="1:8" ht="30" customHeight="1">
-      <c r="A66" s="5">
+      <c r="B73" s="42"/>
+      <c r="C73" s="42"/>
+      <c r="D73" s="42"/>
+      <c r="E73" s="42"/>
+      <c r="F73" s="42"/>
+      <c r="G73" s="42"/>
+      <c r="H73" s="42"/>
+    </row>
+    <row r="74" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
         <v>65</v>
       </c>
-      <c r="B66" s="44"/>
-      <c r="C66" s="44"/>
-      <c r="D66" s="44"/>
-      <c r="E66" s="44"/>
-      <c r="F66" s="44"/>
-      <c r="G66" s="44"/>
-      <c r="H66" s="44"/>
-    </row>
-    <row r="67" spans="1:8" ht="30" customHeight="1">
-      <c r="A67" s="5">
+      <c r="B74" s="42"/>
+      <c r="C74" s="42"/>
+      <c r="D74" s="42"/>
+      <c r="E74" s="42"/>
+      <c r="F74" s="42"/>
+      <c r="G74" s="42"/>
+      <c r="H74" s="42"/>
+    </row>
+    <row r="75" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
         <v>66</v>
       </c>
-      <c r="B67" s="44"/>
-      <c r="C67" s="44"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="44"/>
-      <c r="F67" s="44"/>
-      <c r="G67" s="44"/>
-      <c r="H67" s="44"/>
-    </row>
-    <row r="68" spans="1:8" ht="30" customHeight="1">
-      <c r="A68" s="5">
+      <c r="B75" s="42"/>
+      <c r="C75" s="42"/>
+      <c r="D75" s="42"/>
+      <c r="E75" s="42"/>
+      <c r="F75" s="42"/>
+      <c r="G75" s="42"/>
+      <c r="H75" s="42"/>
+    </row>
+    <row r="76" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
         <v>67</v>
       </c>
-      <c r="B68" s="44"/>
-      <c r="C68" s="44"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="44"/>
-      <c r="F68" s="44"/>
-      <c r="G68" s="44"/>
-      <c r="H68" s="44"/>
-    </row>
-    <row r="69" spans="1:8" ht="30" customHeight="1">
-      <c r="A69" s="5">
+      <c r="B76" s="42"/>
+      <c r="C76" s="42"/>
+      <c r="D76" s="42"/>
+      <c r="E76" s="42"/>
+      <c r="F76" s="42"/>
+      <c r="G76" s="42"/>
+      <c r="H76" s="42"/>
+    </row>
+    <row r="77" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
         <v>68</v>
       </c>
-      <c r="B69" s="44"/>
-      <c r="C69" s="44"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="44"/>
-      <c r="F69" s="44"/>
-      <c r="G69" s="44"/>
-      <c r="H69" s="44"/>
-    </row>
-    <row r="70" spans="1:8" ht="30" customHeight="1">
-      <c r="A70" s="5">
+      <c r="B77" s="42"/>
+      <c r="C77" s="42"/>
+      <c r="D77" s="42"/>
+      <c r="E77" s="42"/>
+      <c r="F77" s="42"/>
+      <c r="G77" s="42"/>
+      <c r="H77" s="42"/>
+    </row>
+    <row r="78" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="44"/>
-      <c r="C70" s="44"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="44"/>
-      <c r="F70" s="44"/>
-      <c r="G70" s="44"/>
-      <c r="H70" s="44"/>
-    </row>
-    <row r="71" spans="1:8" ht="30" customHeight="1">
-      <c r="A71" s="5">
+      <c r="B78" s="42"/>
+      <c r="C78" s="42"/>
+      <c r="D78" s="42"/>
+      <c r="E78" s="42"/>
+      <c r="F78" s="42"/>
+      <c r="G78" s="42"/>
+      <c r="H78" s="42"/>
+    </row>
+    <row r="79" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="44"/>
-      <c r="F71" s="44"/>
-      <c r="G71" s="44"/>
-      <c r="H71" s="44"/>
-    </row>
-    <row r="72" spans="1:8" ht="30" customHeight="1">
-      <c r="A72" s="5">
+      <c r="B79" s="42"/>
+      <c r="C79" s="42"/>
+      <c r="D79" s="42"/>
+      <c r="E79" s="42"/>
+      <c r="F79" s="42"/>
+      <c r="G79" s="42"/>
+      <c r="H79" s="42"/>
+    </row>
+    <row r="80" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="5">
         <v>71</v>
       </c>
-      <c r="B72" s="44"/>
-      <c r="C72" s="44"/>
-      <c r="D72" s="44"/>
-      <c r="E72" s="44"/>
-      <c r="F72" s="44"/>
-      <c r="G72" s="44"/>
-      <c r="H72" s="44"/>
-    </row>
-    <row r="73" spans="1:8" ht="30" customHeight="1">
-      <c r="A73" s="5">
+      <c r="B80" s="42"/>
+      <c r="C80" s="42"/>
+      <c r="D80" s="42"/>
+      <c r="E80" s="42"/>
+      <c r="F80" s="42"/>
+      <c r="G80" s="42"/>
+      <c r="H80" s="42"/>
+    </row>
+    <row r="81" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="44"/>
-      <c r="C73" s="44"/>
-      <c r="D73" s="44"/>
-      <c r="E73" s="44"/>
-      <c r="F73" s="44"/>
-      <c r="G73" s="44"/>
-      <c r="H73" s="44"/>
-    </row>
-    <row r="74" spans="1:8" ht="30" customHeight="1">
-      <c r="A74" s="5">
+      <c r="B81" s="42"/>
+      <c r="C81" s="42"/>
+      <c r="D81" s="42"/>
+      <c r="E81" s="42"/>
+      <c r="F81" s="42"/>
+      <c r="G81" s="42"/>
+      <c r="H81" s="42"/>
+    </row>
+    <row r="82" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="44"/>
-      <c r="C74" s="44"/>
-      <c r="D74" s="44"/>
-      <c r="E74" s="44"/>
-      <c r="F74" s="44"/>
-      <c r="G74" s="44"/>
-      <c r="H74" s="44"/>
-    </row>
-    <row r="75" spans="1:8" ht="30" customHeight="1">
-      <c r="A75" s="5">
+      <c r="B82" s="42"/>
+      <c r="C82" s="42"/>
+      <c r="D82" s="42"/>
+      <c r="E82" s="42"/>
+      <c r="F82" s="42"/>
+      <c r="G82" s="42"/>
+      <c r="H82" s="42"/>
+    </row>
+    <row r="83" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="44"/>
-      <c r="C75" s="44"/>
-      <c r="D75" s="44"/>
-      <c r="E75" s="44"/>
-      <c r="F75" s="44"/>
-      <c r="G75" s="44"/>
-      <c r="H75" s="44"/>
-    </row>
-    <row r="76" spans="1:8" ht="30" customHeight="1">
-      <c r="A76" s="5">
+      <c r="B83" s="42"/>
+      <c r="C83" s="42"/>
+      <c r="D83" s="42"/>
+      <c r="E83" s="42"/>
+      <c r="F83" s="42"/>
+      <c r="G83" s="42"/>
+      <c r="H83" s="42"/>
+    </row>
+    <row r="84" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="44"/>
-      <c r="C76" s="44"/>
-      <c r="D76" s="44"/>
-      <c r="E76" s="44"/>
-      <c r="F76" s="44"/>
-      <c r="G76" s="44"/>
-      <c r="H76" s="44"/>
-    </row>
-    <row r="77" spans="1:8" ht="30" customHeight="1">
-      <c r="A77" s="5">
+      <c r="B84" s="42"/>
+      <c r="C84" s="42"/>
+      <c r="D84" s="42"/>
+      <c r="E84" s="42"/>
+      <c r="F84" s="42"/>
+      <c r="G84" s="42"/>
+      <c r="H84" s="42"/>
+    </row>
+    <row r="85" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="44"/>
-      <c r="C77" s="44"/>
-      <c r="D77" s="44"/>
-      <c r="E77" s="44"/>
-      <c r="F77" s="44"/>
-      <c r="G77" s="44"/>
-      <c r="H77" s="44"/>
-    </row>
-    <row r="78" spans="1:8" ht="30" customHeight="1">
-      <c r="A78" s="5">
+      <c r="B85" s="42"/>
+      <c r="C85" s="42"/>
+      <c r="D85" s="42"/>
+      <c r="E85" s="42"/>
+      <c r="F85" s="42"/>
+      <c r="G85" s="42"/>
+      <c r="H85" s="42"/>
+    </row>
+    <row r="86" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="44"/>
-      <c r="C78" s="44"/>
-      <c r="D78" s="44"/>
-      <c r="E78" s="44"/>
-      <c r="F78" s="44"/>
-      <c r="G78" s="44"/>
-      <c r="H78" s="44"/>
-    </row>
-    <row r="79" spans="1:8" ht="30" customHeight="1">
-      <c r="A79" s="5">
+      <c r="B86" s="42"/>
+      <c r="C86" s="42"/>
+      <c r="D86" s="42"/>
+      <c r="E86" s="42"/>
+      <c r="F86" s="42"/>
+      <c r="G86" s="42"/>
+      <c r="H86" s="42"/>
+    </row>
+    <row r="87" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="44"/>
-      <c r="C79" s="44"/>
-      <c r="D79" s="44"/>
-      <c r="E79" s="44"/>
-      <c r="F79" s="44"/>
-      <c r="G79" s="44"/>
-      <c r="H79" s="44"/>
-    </row>
-    <row r="80" spans="1:8" ht="30" customHeight="1">
-      <c r="A80" s="5">
+      <c r="B87" s="42"/>
+      <c r="C87" s="42"/>
+      <c r="D87" s="42"/>
+      <c r="E87" s="42"/>
+      <c r="F87" s="42"/>
+      <c r="G87" s="42"/>
+      <c r="H87" s="42"/>
+    </row>
+    <row r="88" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="44"/>
-      <c r="C80" s="44"/>
-      <c r="D80" s="44"/>
-      <c r="E80" s="44"/>
-      <c r="F80" s="44"/>
-      <c r="G80" s="44"/>
-      <c r="H80" s="44"/>
-    </row>
-    <row r="81" spans="1:8" ht="30" customHeight="1">
-      <c r="A81" s="5">
+      <c r="B88" s="42"/>
+      <c r="C88" s="42"/>
+      <c r="D88" s="42"/>
+      <c r="E88" s="42"/>
+      <c r="F88" s="42"/>
+      <c r="G88" s="42"/>
+      <c r="H88" s="42"/>
+    </row>
+    <row r="89" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="44"/>
-      <c r="C81" s="44"/>
-      <c r="D81" s="44"/>
-      <c r="E81" s="44"/>
-      <c r="F81" s="44"/>
-      <c r="G81" s="44"/>
-      <c r="H81" s="44"/>
-    </row>
-    <row r="82" spans="1:8" ht="30" customHeight="1">
-      <c r="A82" s="5">
+      <c r="B89" s="42"/>
+      <c r="C89" s="42"/>
+      <c r="D89" s="42"/>
+      <c r="E89" s="42"/>
+      <c r="F89" s="42"/>
+      <c r="G89" s="42"/>
+      <c r="H89" s="42"/>
+    </row>
+    <row r="90" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="5">
         <v>81</v>
       </c>
-      <c r="B82" s="44"/>
-      <c r="C82" s="44"/>
-      <c r="D82" s="44"/>
-      <c r="E82" s="44"/>
-      <c r="F82" s="44"/>
-      <c r="G82" s="44"/>
-      <c r="H82" s="44"/>
-    </row>
-    <row r="83" spans="1:8" ht="30" customHeight="1">
-      <c r="A83" s="5">
+      <c r="B90" s="42"/>
+      <c r="C90" s="42"/>
+      <c r="D90" s="42"/>
+      <c r="E90" s="42"/>
+      <c r="F90" s="42"/>
+      <c r="G90" s="42"/>
+      <c r="H90" s="42"/>
+    </row>
+    <row r="91" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="44"/>
-      <c r="C83" s="44"/>
-      <c r="D83" s="44"/>
-      <c r="E83" s="44"/>
-      <c r="F83" s="44"/>
-      <c r="G83" s="44"/>
-      <c r="H83" s="44"/>
-    </row>
-    <row r="84" spans="1:8" ht="30" customHeight="1">
-      <c r="A84" s="5">
+      <c r="B91" s="42"/>
+      <c r="C91" s="42"/>
+      <c r="D91" s="42"/>
+      <c r="E91" s="42"/>
+      <c r="F91" s="42"/>
+      <c r="G91" s="42"/>
+      <c r="H91" s="42"/>
+    </row>
+    <row r="92" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="5">
         <v>83</v>
       </c>
-      <c r="B84" s="44"/>
-      <c r="C84" s="44"/>
-      <c r="D84" s="44"/>
-      <c r="E84" s="44"/>
-      <c r="F84" s="44"/>
-      <c r="G84" s="44"/>
-      <c r="H84" s="44"/>
-    </row>
-    <row r="85" spans="1:8" ht="30" customHeight="1">
-      <c r="A85" s="5">
+      <c r="B92" s="42"/>
+      <c r="C92" s="42"/>
+      <c r="D92" s="42"/>
+      <c r="E92" s="42"/>
+      <c r="F92" s="42"/>
+      <c r="G92" s="42"/>
+      <c r="H92" s="42"/>
+    </row>
+    <row r="93" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="44"/>
-      <c r="C85" s="44"/>
-      <c r="D85" s="44"/>
-      <c r="E85" s="44"/>
-      <c r="F85" s="44"/>
-      <c r="G85" s="44"/>
-      <c r="H85" s="44"/>
-    </row>
-    <row r="86" spans="1:8" ht="30" customHeight="1">
-      <c r="A86" s="5">
+      <c r="B93" s="42"/>
+      <c r="C93" s="42"/>
+      <c r="D93" s="42"/>
+      <c r="E93" s="42"/>
+      <c r="F93" s="42"/>
+      <c r="G93" s="42"/>
+      <c r="H93" s="42"/>
+    </row>
+    <row r="94" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="5">
         <v>85</v>
       </c>
-      <c r="B86" s="44"/>
-      <c r="C86" s="44"/>
-      <c r="D86" s="44"/>
-      <c r="E86" s="44"/>
-      <c r="F86" s="44"/>
-      <c r="G86" s="44"/>
-      <c r="H86" s="44"/>
-    </row>
-    <row r="87" spans="1:8" ht="30" customHeight="1">
-      <c r="A87" s="5">
+      <c r="B94" s="42"/>
+      <c r="C94" s="42"/>
+      <c r="D94" s="42"/>
+      <c r="E94" s="42"/>
+      <c r="F94" s="42"/>
+      <c r="G94" s="42"/>
+      <c r="H94" s="42"/>
+    </row>
+    <row r="95" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="44"/>
-      <c r="C87" s="44"/>
-      <c r="D87" s="44"/>
-      <c r="E87" s="44"/>
-      <c r="F87" s="44"/>
-      <c r="G87" s="44"/>
-      <c r="H87" s="44"/>
-    </row>
-    <row r="88" spans="1:8" ht="30" customHeight="1">
-      <c r="A88" s="5">
+      <c r="B95" s="42"/>
+      <c r="C95" s="42"/>
+      <c r="D95" s="42"/>
+      <c r="E95" s="42"/>
+      <c r="F95" s="42"/>
+      <c r="G95" s="42"/>
+      <c r="H95" s="42"/>
+    </row>
+    <row r="96" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="5">
         <v>87</v>
       </c>
-      <c r="B88" s="44"/>
-      <c r="C88" s="44"/>
-      <c r="D88" s="44"/>
-      <c r="E88" s="44"/>
-      <c r="F88" s="44"/>
-      <c r="G88" s="44"/>
-      <c r="H88" s="44"/>
-    </row>
-    <row r="89" spans="1:8" ht="30" customHeight="1">
-      <c r="A89" s="5">
+      <c r="B96" s="42"/>
+      <c r="C96" s="42"/>
+      <c r="D96" s="42"/>
+      <c r="E96" s="42"/>
+      <c r="F96" s="42"/>
+      <c r="G96" s="42"/>
+      <c r="H96" s="42"/>
+    </row>
+    <row r="97" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="5">
         <v>88</v>
       </c>
-      <c r="B89" s="44"/>
-      <c r="C89" s="44"/>
-      <c r="D89" s="44"/>
-      <c r="E89" s="44"/>
-      <c r="F89" s="44"/>
-      <c r="G89" s="44"/>
-      <c r="H89" s="44"/>
-    </row>
-    <row r="90" spans="1:8" ht="30" customHeight="1">
-      <c r="A90" s="5">
+      <c r="B97" s="42"/>
+      <c r="C97" s="42"/>
+      <c r="D97" s="42"/>
+      <c r="E97" s="42"/>
+      <c r="F97" s="42"/>
+      <c r="G97" s="42"/>
+      <c r="H97" s="42"/>
+    </row>
+    <row r="98" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="5">
         <v>89</v>
       </c>
-      <c r="B90" s="44"/>
-      <c r="C90" s="44"/>
-      <c r="D90" s="44"/>
-      <c r="E90" s="44"/>
-      <c r="F90" s="44"/>
-      <c r="G90" s="44"/>
-      <c r="H90" s="44"/>
-    </row>
-    <row r="91" spans="1:8" ht="30" customHeight="1">
-      <c r="A91" s="5">
+      <c r="B98" s="42"/>
+      <c r="C98" s="42"/>
+      <c r="D98" s="42"/>
+      <c r="E98" s="42"/>
+      <c r="F98" s="42"/>
+      <c r="G98" s="42"/>
+      <c r="H98" s="42"/>
+    </row>
+    <row r="99" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="5">
         <v>90</v>
       </c>
-      <c r="B91" s="44"/>
-      <c r="C91" s="44"/>
-      <c r="D91" s="44"/>
-      <c r="E91" s="44"/>
-      <c r="F91" s="44"/>
-      <c r="G91" s="44"/>
-      <c r="H91" s="44"/>
-    </row>
-    <row r="92" spans="1:8" ht="30" customHeight="1">
-      <c r="A92" s="5">
+      <c r="B99" s="42"/>
+      <c r="C99" s="42"/>
+      <c r="D99" s="42"/>
+      <c r="E99" s="42"/>
+      <c r="F99" s="42"/>
+      <c r="G99" s="42"/>
+      <c r="H99" s="42"/>
+    </row>
+    <row r="100" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="44"/>
-      <c r="C92" s="44"/>
-      <c r="D92" s="44"/>
-      <c r="E92" s="44"/>
-      <c r="F92" s="44"/>
-      <c r="G92" s="44"/>
-      <c r="H92" s="44"/>
-    </row>
-    <row r="93" spans="1:8" ht="30" customHeight="1">
-      <c r="A93" s="5">
+      <c r="B100" s="42"/>
+      <c r="C100" s="42"/>
+      <c r="D100" s="42"/>
+      <c r="E100" s="42"/>
+      <c r="F100" s="42"/>
+      <c r="G100" s="42"/>
+      <c r="H100" s="42"/>
+    </row>
+    <row r="101" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="44"/>
-      <c r="C93" s="44"/>
-      <c r="D93" s="44"/>
-      <c r="E93" s="44"/>
-      <c r="F93" s="44"/>
-      <c r="G93" s="44"/>
-      <c r="H93" s="44"/>
-    </row>
-    <row r="94" spans="1:8" ht="30" customHeight="1">
-      <c r="A94" s="5">
+      <c r="B101" s="42"/>
+      <c r="C101" s="42"/>
+      <c r="D101" s="42"/>
+      <c r="E101" s="42"/>
+      <c r="F101" s="42"/>
+      <c r="G101" s="42"/>
+      <c r="H101" s="42"/>
+    </row>
+    <row r="102" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="5">
         <v>93</v>
       </c>
-      <c r="B94" s="44"/>
-      <c r="C94" s="44"/>
-      <c r="D94" s="44"/>
-      <c r="E94" s="44"/>
-      <c r="F94" s="44"/>
-      <c r="G94" s="44"/>
-      <c r="H94" s="44"/>
-    </row>
-    <row r="95" spans="1:8" ht="30" customHeight="1">
-      <c r="A95" s="5">
+      <c r="B102" s="42"/>
+      <c r="C102" s="42"/>
+      <c r="D102" s="42"/>
+      <c r="E102" s="42"/>
+      <c r="F102" s="42"/>
+      <c r="G102" s="42"/>
+      <c r="H102" s="42"/>
+    </row>
+    <row r="103" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="5">
         <v>94</v>
       </c>
-      <c r="B95" s="44"/>
-      <c r="C95" s="44"/>
-      <c r="D95" s="44"/>
-      <c r="E95" s="44"/>
-      <c r="F95" s="44"/>
-      <c r="G95" s="44"/>
-      <c r="H95" s="44"/>
-    </row>
-    <row r="96" spans="1:8" ht="30" customHeight="1">
-      <c r="A96" s="5">
+      <c r="B103" s="42"/>
+      <c r="C103" s="42"/>
+      <c r="D103" s="42"/>
+      <c r="E103" s="42"/>
+      <c r="F103" s="42"/>
+      <c r="G103" s="42"/>
+      <c r="H103" s="42"/>
+    </row>
+    <row r="104" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="5">
         <v>95</v>
       </c>
-      <c r="B96" s="44"/>
-      <c r="C96" s="44"/>
-      <c r="D96" s="44"/>
-      <c r="E96" s="44"/>
-      <c r="F96" s="44"/>
-      <c r="G96" s="44"/>
-      <c r="H96" s="44"/>
-    </row>
-    <row r="97" spans="1:8" ht="30" customHeight="1">
-      <c r="A97" s="5">
+      <c r="B104" s="42"/>
+      <c r="C104" s="42"/>
+      <c r="D104" s="42"/>
+      <c r="E104" s="42"/>
+      <c r="F104" s="42"/>
+      <c r="G104" s="42"/>
+      <c r="H104" s="42"/>
+    </row>
+    <row r="105" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="44"/>
-      <c r="C97" s="44"/>
-      <c r="D97" s="44"/>
-      <c r="E97" s="44"/>
-      <c r="F97" s="44"/>
-      <c r="G97" s="44"/>
-      <c r="H97" s="44"/>
-    </row>
-    <row r="98" spans="1:8" ht="30" customHeight="1">
-      <c r="A98" s="5">
+      <c r="B105" s="42"/>
+      <c r="C105" s="42"/>
+      <c r="D105" s="42"/>
+      <c r="E105" s="42"/>
+      <c r="F105" s="42"/>
+      <c r="G105" s="42"/>
+      <c r="H105" s="42"/>
+    </row>
+    <row r="106" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="5">
         <v>97</v>
       </c>
-      <c r="B98" s="44"/>
-      <c r="C98" s="44"/>
-      <c r="D98" s="44"/>
-      <c r="E98" s="44"/>
-      <c r="F98" s="44"/>
-      <c r="G98" s="44"/>
-      <c r="H98" s="44"/>
-    </row>
-    <row r="99" spans="1:8" ht="30" customHeight="1">
-      <c r="A99" s="5">
+      <c r="B106" s="42"/>
+      <c r="C106" s="42"/>
+      <c r="D106" s="42"/>
+      <c r="E106" s="42"/>
+      <c r="F106" s="42"/>
+      <c r="G106" s="42"/>
+      <c r="H106" s="42"/>
+    </row>
+    <row r="107" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="44"/>
-      <c r="C99" s="44"/>
-      <c r="D99" s="44"/>
-      <c r="E99" s="44"/>
-      <c r="F99" s="44"/>
-      <c r="G99" s="44"/>
-      <c r="H99" s="44"/>
-    </row>
-    <row r="100" spans="1:8" ht="30" customHeight="1">
-      <c r="A100" s="5">
+      <c r="B107" s="42"/>
+      <c r="C107" s="42"/>
+      <c r="D107" s="42"/>
+      <c r="E107" s="42"/>
+      <c r="F107" s="42"/>
+      <c r="G107" s="42"/>
+      <c r="H107" s="42"/>
+    </row>
+    <row r="108" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="44"/>
-      <c r="C100" s="44"/>
-      <c r="D100" s="44"/>
-      <c r="E100" s="44"/>
-      <c r="F100" s="44"/>
-      <c r="G100" s="44"/>
-      <c r="H100" s="44"/>
-    </row>
-    <row r="101" spans="1:8" ht="30" customHeight="1">
-      <c r="A101" s="5">
+      <c r="B108" s="42"/>
+      <c r="C108" s="42"/>
+      <c r="D108" s="42"/>
+      <c r="E108" s="42"/>
+      <c r="F108" s="42"/>
+      <c r="G108" s="42"/>
+      <c r="H108" s="42"/>
+    </row>
+    <row r="109" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="44"/>
-      <c r="C101" s="44"/>
-      <c r="D101" s="44"/>
-      <c r="E101" s="44"/>
-      <c r="F101" s="44"/>
-      <c r="G101" s="44"/>
-      <c r="H101" s="44"/>
+      <c r="B109" s="42"/>
+      <c r="C109" s="42"/>
+      <c r="D109" s="42"/>
+      <c r="E109" s="42"/>
+      <c r="F109" s="42"/>
+      <c r="G109" s="42"/>
+      <c r="H109" s="42"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H101"/>
+  <autoFilter ref="A1:H109"/>
   <hyperlinks>
     <hyperlink ref="C11" r:id="rId1" display="https://yandex.ru/search/?srm=1&amp;text=%D0%AD%D1%80%D0%B8%D1%85%20%D0%9C%D0%B0%D1%80%D0%B8%D1%8F%20%D0%A0%D0%B5%D0%BC%D0%B0%D1%80%D0%BA&amp;lr=14&amp;clid=2270455&amp;win=687&amp;primary_reqid=1786517055526639-14999433768309566645-balancer-l7leveler-kubr-yp-klg-171-BAL&amp;noreask=1&amp;ento=0oCghydXcyMzA3MhgCKglydXcyMzEzNDdqF9Ci0YDQuCDRgtC-0LLQsNGA0LjRidCwcgrQkNCy0YLQvtGAyYrrdg"/>
   </hyperlinks>
@@ -8468,19 +8642,295 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="8"/>
+    <col min="3" max="3" width="19.85546875" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="47" t="s">
+        <v>408</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="48">
+        <v>46271</v>
+      </c>
+      <c r="C2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="48">
+        <v>46272</v>
+      </c>
+      <c r="C3">
+        <f>C2+20</f>
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="48">
+        <v>46273</v>
+      </c>
+      <c r="C4">
+        <f>C3+20</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="48">
+        <v>46274</v>
+      </c>
+      <c r="C5">
+        <f>C4+20</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="48">
+        <v>46275</v>
+      </c>
+      <c r="C6">
+        <f t="shared" ref="C6:C20" si="0">C5+20</f>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="48">
+        <v>46276</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>340</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="48">
+        <v>46277</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="48">
+        <v>46278</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="48">
+        <v>46279</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="48">
+        <v>46280</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>420</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="48">
+        <v>46281</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="48">
+        <v>46282</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>460</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="48">
+        <v>46283</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="48">
+        <v>46284</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="48">
+        <v>46285</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="48">
+        <v>46286</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>540</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="48">
+        <v>46287</v>
+      </c>
+      <c r="C18">
+        <f t="shared" si="0"/>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="48">
+        <v>46288</v>
+      </c>
+      <c r="C19">
+        <f t="shared" si="0"/>
+        <v>580</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="48">
+        <v>46289</v>
+      </c>
+      <c r="C20">
+        <f t="shared" si="0"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="48">
+        <v>46290</v>
+      </c>
+      <c r="C21">
+        <f>C20+20</f>
+        <v>620</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="49">
+        <v>21</v>
+      </c>
+      <c r="B22" s="50">
+        <v>46291</v>
+      </c>
+      <c r="C22" s="49">
+        <v>637</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="11.5703125" style="2" customWidth="1"/>
@@ -8489,7 +8939,7 @@
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8530,7 +8980,7 @@
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
     </row>
-    <row r="2" spans="1:15" ht="45" customHeight="1">
+    <row r="2" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -8554,7 +9004,7 @@
       </c>
       <c r="L2" s="7"/>
     </row>
-    <row r="3" spans="1:15" ht="45" customHeight="1">
+    <row r="3" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -8578,7 +9028,7 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:15" ht="45" customHeight="1">
+    <row r="4" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -8606,7 +9056,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:15" ht="45" customHeight="1">
+    <row r="5" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -8628,7 +9078,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="45" customHeight="1">
+    <row r="6" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -8652,7 +9102,7 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:15" ht="45" customHeight="1">
+    <row r="7" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -8678,7 +9128,7 @@
       </c>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:15" ht="45" customHeight="1">
+    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -8694,7 +9144,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:15" ht="45" customHeight="1">
+    <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -8710,7 +9160,7 @@
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" spans="1:15" ht="45" customHeight="1">
+    <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -8726,7 +9176,7 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" spans="1:15" ht="45" customHeight="1">
+    <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>

--- a/Другое/Кино-Книги-Одежда-Спорт.xlsx
+++ b/Другое/Кино-Книги-Одежда-Спорт.xlsx
@@ -1,13 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="5" rupBuild="4507"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROG\Git\Repository_1\Другое\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="24000" windowHeight="10980" activeTab="1"/>
   </bookViews>
@@ -20,9 +15,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Кино!$A$1:$I$221</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Книги!$A$1:$H$109</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Книги!$A$1:$H$110</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="125725"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -40,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="415">
   <si>
     <t>№</t>
   </si>
@@ -1048,9 +1043,6 @@
   </si>
   <si>
     <t>Трое в лодке, не считая собаки</t>
-  </si>
-  <si>
-    <t>Юмористическая повесть</t>
   </si>
   <si>
     <t>Тонкое искусство пофигизма</t>
@@ -1306,14 +1298,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="dd\.mmm"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="166" formatCode="mmm\.yy"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1737,7 +1729,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1772,7 +1763,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Стандартная">
@@ -1948,9 +1938,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I222"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="8"/>
     <col min="2" max="2" width="24.85546875" style="8" customWidth="1"/>
@@ -1963,7 +1953,7 @@
     <col min="10" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -1992,7 +1982,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="10">
         <v>6</v>
       </c>
@@ -2015,7 +2005,7 @@
       <c r="H2" s="10"/>
       <c r="I2" s="13"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="10">
         <v>7</v>
       </c>
@@ -2038,7 +2028,7 @@
       <c r="H3" s="10"/>
       <c r="I3" s="13"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="10">
         <v>8</v>
       </c>
@@ -2061,7 +2051,7 @@
       <c r="H4" s="10"/>
       <c r="I4" s="13"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="10">
         <v>3</v>
       </c>
@@ -2090,7 +2080,7 @@
         <v>46187</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="10">
         <v>5</v>
       </c>
@@ -2113,7 +2103,7 @@
       <c r="H6" s="10"/>
       <c r="I6" s="13"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="10">
         <v>11</v>
       </c>
@@ -2136,7 +2126,7 @@
       <c r="H7" s="10"/>
       <c r="I7" s="13"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="10">
         <v>9</v>
       </c>
@@ -2159,7 +2149,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="13"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="10">
         <v>12</v>
       </c>
@@ -2182,7 +2172,7 @@
       <c r="H9" s="10"/>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="10">
         <v>15</v>
       </c>
@@ -2205,7 +2195,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="13"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="A11" s="10">
         <v>4</v>
       </c>
@@ -2228,7 +2218,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="13"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9">
       <c r="A12" s="10">
         <v>1</v>
       </c>
@@ -2257,7 +2247,7 @@
         <v>46184</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9">
       <c r="A13" s="10">
         <v>13</v>
       </c>
@@ -2280,7 +2270,7 @@
       <c r="H13" s="10"/>
       <c r="I13" s="13"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9">
       <c r="A14" s="10">
         <v>2</v>
       </c>
@@ -2303,7 +2293,7 @@
       <c r="H14" s="10"/>
       <c r="I14" s="13"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9">
       <c r="A15" s="10">
         <v>14</v>
       </c>
@@ -2326,7 +2316,7 @@
       <c r="H15" s="10"/>
       <c r="I15" s="13"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9">
       <c r="A16" s="10">
         <v>16</v>
       </c>
@@ -2349,7 +2339,7 @@
       <c r="H16" s="10"/>
       <c r="I16" s="13"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9">
       <c r="A17" s="10">
         <v>10</v>
       </c>
@@ -2372,7 +2362,7 @@
       <c r="H17" s="10"/>
       <c r="I17" s="13"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9">
       <c r="A18" s="10">
         <v>17</v>
       </c>
@@ -2401,7 +2391,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9">
       <c r="A19" s="10">
         <v>18</v>
       </c>
@@ -2424,7 +2414,7 @@
       <c r="H19" s="10"/>
       <c r="I19" s="13"/>
     </row>
-    <row r="20" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="29.25">
       <c r="A20" s="10">
         <v>36</v>
       </c>
@@ -2453,7 +2443,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9">
       <c r="A21" s="10">
         <v>20</v>
       </c>
@@ -2476,7 +2466,7 @@
       <c r="H21" s="10"/>
       <c r="I21" s="13"/>
     </row>
-    <row r="22" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="29.25">
       <c r="A22" s="10">
         <v>37</v>
       </c>
@@ -2499,7 +2489,7 @@
       <c r="H22" s="19"/>
       <c r="I22" s="19"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9">
       <c r="A23" s="10">
         <v>39</v>
       </c>
@@ -2520,7 +2510,7 @@
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9">
       <c r="A24" s="10">
         <v>21</v>
       </c>
@@ -2549,7 +2539,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9">
       <c r="A25" s="10">
         <v>41</v>
       </c>
@@ -2570,7 +2560,7 @@
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9">
       <c r="A26" s="10">
         <v>49</v>
       </c>
@@ -2591,7 +2581,7 @@
       <c r="H26" s="19"/>
       <c r="I26" s="19"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9">
       <c r="A27" s="10">
         <v>40</v>
       </c>
@@ -2612,7 +2602,7 @@
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9">
       <c r="A28" s="10">
         <v>19</v>
       </c>
@@ -2635,7 +2625,7 @@
       <c r="H28" s="10"/>
       <c r="I28" s="13"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9">
       <c r="A29" s="10">
         <v>22</v>
       </c>
@@ -2664,7 +2654,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9">
       <c r="A30" s="10">
         <v>42</v>
       </c>
@@ -2685,7 +2675,7 @@
       <c r="H30" s="19"/>
       <c r="I30" s="19"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9">
       <c r="A31" s="10">
         <v>23</v>
       </c>
@@ -2708,7 +2698,7 @@
       <c r="H31" s="10"/>
       <c r="I31" s="13"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9">
       <c r="A32" s="10">
         <v>43</v>
       </c>
@@ -2729,7 +2719,7 @@
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9">
       <c r="A33" s="10">
         <v>75</v>
       </c>
@@ -2750,7 +2740,7 @@
       <c r="H33" s="19"/>
       <c r="I33" s="19"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9">
       <c r="A34" s="10">
         <v>27</v>
       </c>
@@ -2779,7 +2769,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9">
       <c r="A35" s="10">
         <v>48</v>
       </c>
@@ -2800,7 +2790,7 @@
       <c r="H35" s="19"/>
       <c r="I35" s="19"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9">
       <c r="A36" s="10">
         <v>44</v>
       </c>
@@ -2821,7 +2811,7 @@
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9">
       <c r="A37" s="10">
         <v>24</v>
       </c>
@@ -2844,7 +2834,7 @@
       <c r="H37" s="10"/>
       <c r="I37" s="13"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9">
       <c r="A38" s="10">
         <v>25</v>
       </c>
@@ -2873,7 +2863,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9">
       <c r="A39" s="10">
         <v>38</v>
       </c>
@@ -2896,7 +2886,7 @@
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9">
       <c r="A40" s="10">
         <v>76</v>
       </c>
@@ -2917,7 +2907,7 @@
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9">
       <c r="A41" s="10">
         <v>28</v>
       </c>
@@ -2946,7 +2936,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9">
       <c r="A42" s="10">
         <v>80</v>
       </c>
@@ -2967,7 +2957,7 @@
       <c r="H42" s="19"/>
       <c r="I42" s="19"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9">
       <c r="A43" s="10">
         <v>51</v>
       </c>
@@ -2994,7 +2984,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9">
       <c r="A44" s="10">
         <v>127</v>
       </c>
@@ -3023,7 +3013,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9">
       <c r="A45" s="10">
         <v>52</v>
       </c>
@@ -3050,7 +3040,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9">
       <c r="A46" s="10">
         <v>26</v>
       </c>
@@ -3079,7 +3069,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9">
       <c r="A47" s="10">
         <v>70</v>
       </c>
@@ -3106,7 +3096,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9">
       <c r="A48" s="10">
         <v>72</v>
       </c>
@@ -3127,7 +3117,7 @@
       <c r="H48" s="19"/>
       <c r="I48" s="19"/>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9">
       <c r="A49" s="10">
         <v>46</v>
       </c>
@@ -3148,7 +3138,7 @@
       <c r="H49" s="19"/>
       <c r="I49" s="19"/>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9">
       <c r="A50" s="10">
         <v>53</v>
       </c>
@@ -3175,7 +3165,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9">
       <c r="A51" s="10">
         <v>65</v>
       </c>
@@ -3202,7 +3192,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9">
       <c r="A52" s="10">
         <v>95</v>
       </c>
@@ -3223,7 +3213,7 @@
       <c r="H52" s="19"/>
       <c r="I52" s="19"/>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9">
       <c r="A53" s="10">
         <v>74</v>
       </c>
@@ -3250,7 +3240,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9">
       <c r="A54" s="10">
         <v>101</v>
       </c>
@@ -3271,7 +3261,7 @@
       <c r="H54" s="19"/>
       <c r="I54" s="19"/>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9">
       <c r="A55" s="10">
         <v>112</v>
       </c>
@@ -3298,7 +3288,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9">
       <c r="A56" s="10">
         <v>50</v>
       </c>
@@ -3319,7 +3309,7 @@
       <c r="H56" s="19"/>
       <c r="I56" s="19"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9">
       <c r="A57" s="10">
         <v>66</v>
       </c>
@@ -3346,7 +3336,7 @@
         <v>46023</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9">
       <c r="A58" s="10">
         <v>97</v>
       </c>
@@ -3367,7 +3357,7 @@
       <c r="H58" s="19"/>
       <c r="I58" s="19"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9">
       <c r="A59" s="10">
         <v>130</v>
       </c>
@@ -3394,7 +3384,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9">
       <c r="A60" s="10">
         <v>92</v>
       </c>
@@ -3415,7 +3405,7 @@
       <c r="H60" s="19"/>
       <c r="I60" s="19"/>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9">
       <c r="A61" s="10">
         <v>108</v>
       </c>
@@ -3442,7 +3432,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9">
       <c r="A62" s="10">
         <v>113</v>
       </c>
@@ -3469,7 +3459,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9">
       <c r="A63" s="10">
         <v>47</v>
       </c>
@@ -3496,7 +3486,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9">
       <c r="A64" s="10">
         <v>77</v>
       </c>
@@ -3517,7 +3507,7 @@
       <c r="H64" s="19"/>
       <c r="I64" s="19"/>
     </row>
-    <row r="65" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="42.75">
       <c r="A65" s="10">
         <v>31</v>
       </c>
@@ -3546,7 +3536,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9">
       <c r="A66" s="10">
         <v>63</v>
       </c>
@@ -3567,7 +3557,7 @@
       <c r="H66" s="19"/>
       <c r="I66" s="19"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9">
       <c r="A67" s="10">
         <v>102</v>
       </c>
@@ -3594,7 +3584,7 @@
         <v>46143</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9">
       <c r="A68" s="10">
         <v>54</v>
       </c>
@@ -3615,7 +3605,7 @@
       <c r="H68" s="19"/>
       <c r="I68" s="19"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9">
       <c r="A69" s="10">
         <v>89</v>
       </c>
@@ -3636,7 +3626,7 @@
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9">
       <c r="A70" s="10">
         <v>218</v>
       </c>
@@ -3655,7 +3645,7 @@
       <c r="H70" s="10"/>
       <c r="I70" s="23"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9">
       <c r="A71" s="10">
         <v>29</v>
       </c>
@@ -3684,7 +3674,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9">
       <c r="A72" s="10">
         <v>55</v>
       </c>
@@ -3705,7 +3695,7 @@
       <c r="H72" s="19"/>
       <c r="I72" s="19"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9">
       <c r="A73" s="10">
         <v>91</v>
       </c>
@@ -3726,7 +3716,7 @@
       <c r="H73" s="19"/>
       <c r="I73" s="19"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9">
       <c r="A74" s="10">
         <v>103</v>
       </c>
@@ -3753,7 +3743,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9">
       <c r="A75" s="10">
         <v>114</v>
       </c>
@@ -3780,7 +3770,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="57" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="57">
       <c r="A76" s="10">
         <v>30</v>
       </c>
@@ -3809,7 +3799,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9">
       <c r="A77" s="10">
         <v>104</v>
       </c>
@@ -3836,7 +3826,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9">
       <c r="A78" s="10">
         <v>56</v>
       </c>
@@ -3857,7 +3847,7 @@
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9">
       <c r="A79" s="10">
         <v>71</v>
       </c>
@@ -3884,7 +3874,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9">
       <c r="A80" s="10">
         <v>73</v>
       </c>
@@ -3911,7 +3901,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9">
       <c r="A81" s="10">
         <v>94</v>
       </c>
@@ -3938,7 +3928,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="29.25">
       <c r="A82" s="10">
         <v>62</v>
       </c>
@@ -3965,7 +3955,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9">
       <c r="A83" s="10">
         <v>78</v>
       </c>
@@ -3986,7 +3976,7 @@
       <c r="H83" s="19"/>
       <c r="I83" s="19"/>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9">
       <c r="A84" s="10">
         <v>111</v>
       </c>
@@ -4013,7 +4003,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9">
       <c r="A85" s="10">
         <v>115</v>
       </c>
@@ -4040,7 +4030,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9">
       <c r="A86" s="10">
         <v>131</v>
       </c>
@@ -4069,7 +4059,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9">
       <c r="A87" s="10">
         <v>33</v>
       </c>
@@ -4098,7 +4088,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9">
       <c r="A88" s="10">
         <v>57</v>
       </c>
@@ -4125,7 +4115,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9">
       <c r="A89" s="10">
         <v>116</v>
       </c>
@@ -4146,7 +4136,7 @@
       <c r="H89" s="10"/>
       <c r="I89" s="19"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9">
       <c r="A90" s="10">
         <v>58</v>
       </c>
@@ -4173,7 +4163,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9">
       <c r="A91" s="10">
         <v>69</v>
       </c>
@@ -4194,7 +4184,7 @@
       <c r="H91" s="19"/>
       <c r="I91" s="19"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9">
       <c r="A92" s="10">
         <v>79</v>
       </c>
@@ -4215,7 +4205,7 @@
       <c r="H92" s="19"/>
       <c r="I92" s="19"/>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9">
       <c r="A93" s="10">
         <v>82</v>
       </c>
@@ -4236,7 +4226,7 @@
       <c r="H93" s="19"/>
       <c r="I93" s="19"/>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9">
       <c r="A94" s="10">
         <v>109</v>
       </c>
@@ -4263,7 +4253,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9">
       <c r="A95" s="10">
         <v>219</v>
       </c>
@@ -4292,7 +4282,7 @@
         <v>46200</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9">
       <c r="A96" s="10">
         <v>67</v>
       </c>
@@ -4313,7 +4303,7 @@
       <c r="H96" s="19"/>
       <c r="I96" s="19"/>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9">
       <c r="A97" s="10">
         <v>117</v>
       </c>
@@ -4334,7 +4324,7 @@
       <c r="H97" s="10"/>
       <c r="I97" s="19"/>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9">
       <c r="A98" s="10">
         <v>99</v>
       </c>
@@ -4355,7 +4345,7 @@
       <c r="H98" s="19"/>
       <c r="I98" s="19"/>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9">
       <c r="A99" s="10">
         <v>107</v>
       </c>
@@ -4382,7 +4372,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9">
       <c r="A100" s="10">
         <v>126</v>
       </c>
@@ -4411,7 +4401,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="42.75">
       <c r="A101" s="10">
         <v>32</v>
       </c>
@@ -4440,7 +4430,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9">
       <c r="A102" s="10">
         <v>81</v>
       </c>
@@ -4461,7 +4451,7 @@
       <c r="H102" s="19"/>
       <c r="I102" s="19"/>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9">
       <c r="A103" s="10">
         <v>125</v>
       </c>
@@ -4490,7 +4480,7 @@
         <v>45658</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9">
       <c r="A104" s="10">
         <v>68</v>
       </c>
@@ -4517,7 +4507,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9">
       <c r="A105" s="10">
         <v>106</v>
       </c>
@@ -4546,7 +4536,7 @@
         <v>46082</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="28.5">
       <c r="A106" s="10">
         <v>128</v>
       </c>
@@ -4573,7 +4563,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9">
       <c r="A107" s="10">
         <v>59</v>
       </c>
@@ -4600,7 +4590,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9">
       <c r="A108" s="10">
         <v>87</v>
       </c>
@@ -4621,7 +4611,7 @@
       <c r="H108" s="19"/>
       <c r="I108" s="19"/>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9">
       <c r="A109" s="10">
         <v>118</v>
       </c>
@@ -4648,7 +4638,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9">
       <c r="A110" s="10">
         <v>86</v>
       </c>
@@ -4675,7 +4665,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9">
       <c r="A111" s="10">
         <v>88</v>
       </c>
@@ -4696,7 +4686,7 @@
       <c r="H111" s="19"/>
       <c r="I111" s="19"/>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9">
       <c r="A112" s="10">
         <v>85</v>
       </c>
@@ -4717,7 +4707,7 @@
       <c r="H112" s="26"/>
       <c r="I112" s="26"/>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9">
       <c r="A113" s="10">
         <v>96</v>
       </c>
@@ -4738,7 +4728,7 @@
       <c r="H113" s="19"/>
       <c r="I113" s="19"/>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9">
       <c r="A114" s="10">
         <v>105</v>
       </c>
@@ -4759,7 +4749,7 @@
       <c r="H114" s="19"/>
       <c r="I114" s="19"/>
     </row>
-    <row r="115" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="28.5">
       <c r="A115" s="10">
         <v>34</v>
       </c>
@@ -4782,7 +4772,7 @@
       <c r="H115" s="10"/>
       <c r="I115" s="13"/>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9">
       <c r="A116" s="10">
         <v>60</v>
       </c>
@@ -4809,7 +4799,7 @@
         <v>45748</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9">
       <c r="A117" s="10">
         <v>119</v>
       </c>
@@ -4838,7 +4828,7 @@
         <v>46260</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9">
       <c r="A118" s="10">
         <v>129</v>
       </c>
@@ -4865,7 +4855,7 @@
         <v>45778</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9">
       <c r="A119" s="10">
         <v>61</v>
       </c>
@@ -4886,7 +4876,7 @@
       <c r="H119" s="19"/>
       <c r="I119" s="19"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9">
       <c r="A120" s="10">
         <v>100</v>
       </c>
@@ -4907,7 +4897,7 @@
       <c r="H120" s="19"/>
       <c r="I120" s="19"/>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9">
       <c r="A121" s="10">
         <v>83</v>
       </c>
@@ -4928,7 +4918,7 @@
       <c r="H121" s="19"/>
       <c r="I121" s="19"/>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9">
       <c r="A122" s="10">
         <v>98</v>
       </c>
@@ -4949,7 +4939,7 @@
       <c r="H122" s="19"/>
       <c r="I122" s="19"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9">
       <c r="A123" s="10">
         <v>120</v>
       </c>
@@ -4976,7 +4966,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9">
       <c r="A124" s="10">
         <v>90</v>
       </c>
@@ -4997,7 +4987,7 @@
       <c r="H124" s="19"/>
       <c r="I124" s="19"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9">
       <c r="A125" s="10">
         <v>121</v>
       </c>
@@ -5024,7 +5014,7 @@
         <v>44713</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="29.25" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="29.25">
       <c r="A126" s="10">
         <v>122</v>
       </c>
@@ -5045,7 +5035,7 @@
       <c r="H126" s="10"/>
       <c r="I126" s="19"/>
     </row>
-    <row r="127" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="42.75">
       <c r="A127" s="10">
         <v>35</v>
       </c>
@@ -5074,7 +5064,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9">
       <c r="A128" s="10">
         <v>64</v>
       </c>
@@ -5095,7 +5085,7 @@
       <c r="H128" s="19"/>
       <c r="I128" s="19"/>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9">
       <c r="A129" s="10">
         <v>110</v>
       </c>
@@ -5122,7 +5112,7 @@
         <v>45231</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9">
       <c r="A130" s="10">
         <v>84</v>
       </c>
@@ -5143,7 +5133,7 @@
       <c r="H130" s="19"/>
       <c r="I130" s="19"/>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9">
       <c r="A131" s="10">
         <v>123</v>
       </c>
@@ -5164,7 +5154,7 @@
       <c r="H131" s="10"/>
       <c r="I131" s="19"/>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9">
       <c r="A132" s="10">
         <v>93</v>
       </c>
@@ -5191,7 +5181,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9">
       <c r="A133" s="10">
         <v>124</v>
       </c>
@@ -5218,7 +5208,7 @@
         <v>46171</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9">
       <c r="A134" s="10">
         <v>45</v>
       </c>
@@ -5239,7 +5229,7 @@
       <c r="H134" s="19"/>
       <c r="I134" s="19"/>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9">
       <c r="A135" s="10">
         <v>132</v>
       </c>
@@ -5258,7 +5248,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9">
       <c r="A136" s="10">
         <v>133</v>
       </c>
@@ -5277,7 +5267,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9">
       <c r="A137" s="10">
         <v>134</v>
       </c>
@@ -5296,7 +5286,7 @@
         <v>45809</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9">
       <c r="A138" s="10">
         <v>135</v>
       </c>
@@ -5315,7 +5305,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9">
       <c r="A139" s="10">
         <v>136</v>
       </c>
@@ -5334,7 +5324,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9">
       <c r="A140" s="10">
         <v>137</v>
       </c>
@@ -5353,7 +5343,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9">
       <c r="A141" s="10">
         <v>138</v>
       </c>
@@ -5372,7 +5362,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9">
       <c r="A142" s="10">
         <v>139</v>
       </c>
@@ -5391,7 +5381,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9">
       <c r="A143" s="10">
         <v>140</v>
       </c>
@@ -5410,7 +5400,7 @@
         <v>45839</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9">
       <c r="A144" s="10">
         <v>141</v>
       </c>
@@ -5429,7 +5419,7 @@
         <v>45859</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9">
       <c r="A145" s="10">
         <v>142</v>
       </c>
@@ -5448,7 +5438,7 @@
       <c r="H145" s="10"/>
       <c r="I145" s="23"/>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9">
       <c r="A146" s="10">
         <v>143</v>
       </c>
@@ -5465,7 +5455,7 @@
       <c r="H146" s="10"/>
       <c r="I146" s="23"/>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9">
       <c r="A147" s="10">
         <v>144</v>
       </c>
@@ -5482,7 +5472,7 @@
       <c r="H147" s="10"/>
       <c r="I147" s="23"/>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9">
       <c r="A148" s="10">
         <v>145</v>
       </c>
@@ -5499,7 +5489,7 @@
       <c r="H148" s="10"/>
       <c r="I148" s="23"/>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9">
       <c r="A149" s="10">
         <v>146</v>
       </c>
@@ -5518,7 +5508,7 @@
       <c r="H149" s="10"/>
       <c r="I149" s="23"/>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9">
       <c r="A150" s="10">
         <v>147</v>
       </c>
@@ -5535,7 +5525,7 @@
       <c r="H150" s="10"/>
       <c r="I150" s="23"/>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9">
       <c r="A151" s="10">
         <v>148</v>
       </c>
@@ -5552,7 +5542,7 @@
       <c r="H151" s="10"/>
       <c r="I151" s="23"/>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:9">
       <c r="A152" s="10">
         <v>149</v>
       </c>
@@ -5569,7 +5559,7 @@
       <c r="H152" s="10"/>
       <c r="I152" s="23"/>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9">
       <c r="A153" s="10">
         <v>150</v>
       </c>
@@ -5586,7 +5576,7 @@
       <c r="H153" s="10"/>
       <c r="I153" s="23"/>
     </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9">
       <c r="A154" s="10">
         <v>151</v>
       </c>
@@ -5603,7 +5593,7 @@
       <c r="H154" s="10"/>
       <c r="I154" s="23"/>
     </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9">
       <c r="A155" s="10">
         <v>152</v>
       </c>
@@ -5620,7 +5610,7 @@
       <c r="H155" s="10"/>
       <c r="I155" s="23"/>
     </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9">
       <c r="A156" s="10">
         <v>153</v>
       </c>
@@ -5637,7 +5627,7 @@
       <c r="H156" s="10"/>
       <c r="I156" s="23"/>
     </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9">
       <c r="A157" s="10">
         <v>154</v>
       </c>
@@ -5654,7 +5644,7 @@
       <c r="H157" s="10"/>
       <c r="I157" s="23"/>
     </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9">
       <c r="A158" s="10">
         <v>155</v>
       </c>
@@ -5671,7 +5661,7 @@
       <c r="H158" s="10"/>
       <c r="I158" s="23"/>
     </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9">
       <c r="A159" s="10">
         <v>156</v>
       </c>
@@ -5688,7 +5678,7 @@
       <c r="H159" s="10"/>
       <c r="I159" s="23"/>
     </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9">
       <c r="A160" s="10">
         <v>157</v>
       </c>
@@ -5705,7 +5695,7 @@
       <c r="H160" s="10"/>
       <c r="I160" s="23"/>
     </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9">
       <c r="A161" s="10">
         <v>158</v>
       </c>
@@ -5722,7 +5712,7 @@
       <c r="H161" s="10"/>
       <c r="I161" s="23"/>
     </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9">
       <c r="A162" s="10">
         <v>159</v>
       </c>
@@ -5737,7 +5727,7 @@
       <c r="H162" s="10"/>
       <c r="I162" s="23"/>
     </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9">
       <c r="A163" s="10">
         <v>160</v>
       </c>
@@ -5752,7 +5742,7 @@
       <c r="H163" s="10"/>
       <c r="I163" s="23"/>
     </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9">
       <c r="A164" s="10">
         <v>161</v>
       </c>
@@ -5767,7 +5757,7 @@
       <c r="H164" s="10"/>
       <c r="I164" s="23"/>
     </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9">
       <c r="A165" s="10">
         <v>162</v>
       </c>
@@ -5782,7 +5772,7 @@
       <c r="H165" s="10"/>
       <c r="I165" s="23"/>
     </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9">
       <c r="A166" s="10">
         <v>163</v>
       </c>
@@ -5797,7 +5787,7 @@
       <c r="H166" s="10"/>
       <c r="I166" s="23"/>
     </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9">
       <c r="A167" s="10">
         <v>164</v>
       </c>
@@ -5812,7 +5802,7 @@
       <c r="H167" s="10"/>
       <c r="I167" s="23"/>
     </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9">
       <c r="A168" s="10">
         <v>165</v>
       </c>
@@ -5827,7 +5817,7 @@
       <c r="H168" s="10"/>
       <c r="I168" s="23"/>
     </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:9">
       <c r="A169" s="10">
         <v>166</v>
       </c>
@@ -5842,7 +5832,7 @@
       <c r="H169" s="10"/>
       <c r="I169" s="23"/>
     </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9">
       <c r="A170" s="10">
         <v>167</v>
       </c>
@@ -5857,7 +5847,7 @@
       <c r="H170" s="10"/>
       <c r="I170" s="23"/>
     </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9">
       <c r="A171" s="10">
         <v>168</v>
       </c>
@@ -5872,7 +5862,7 @@
       <c r="H171" s="10"/>
       <c r="I171" s="23"/>
     </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9">
       <c r="A172" s="10">
         <v>169</v>
       </c>
@@ -5887,7 +5877,7 @@
       <c r="H172" s="10"/>
       <c r="I172" s="23"/>
     </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9">
       <c r="A173" s="10">
         <v>170</v>
       </c>
@@ -5902,7 +5892,7 @@
       <c r="H173" s="10"/>
       <c r="I173" s="23"/>
     </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9">
       <c r="A174" s="10">
         <v>171</v>
       </c>
@@ -5917,7 +5907,7 @@
       <c r="H174" s="10"/>
       <c r="I174" s="23"/>
     </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9">
       <c r="A175" s="10">
         <v>172</v>
       </c>
@@ -5932,7 +5922,7 @@
       <c r="H175" s="10"/>
       <c r="I175" s="23"/>
     </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9">
       <c r="A176" s="10">
         <v>173</v>
       </c>
@@ -5947,7 +5937,7 @@
       <c r="H176" s="10"/>
       <c r="I176" s="23"/>
     </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9">
       <c r="A177" s="10">
         <v>174</v>
       </c>
@@ -5962,7 +5952,7 @@
       <c r="H177" s="10"/>
       <c r="I177" s="23"/>
     </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9">
       <c r="A178" s="10">
         <v>175</v>
       </c>
@@ -5977,7 +5967,7 @@
       <c r="H178" s="10"/>
       <c r="I178" s="23"/>
     </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9">
       <c r="A179" s="10">
         <v>176</v>
       </c>
@@ -5992,7 +5982,7 @@
       <c r="H179" s="10"/>
       <c r="I179" s="23"/>
     </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9">
       <c r="A180" s="10">
         <v>177</v>
       </c>
@@ -6007,7 +5997,7 @@
       <c r="H180" s="10"/>
       <c r="I180" s="23"/>
     </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9">
       <c r="A181" s="10">
         <v>178</v>
       </c>
@@ -6022,7 +6012,7 @@
       <c r="H181" s="10"/>
       <c r="I181" s="23"/>
     </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9">
       <c r="A182" s="10">
         <v>179</v>
       </c>
@@ -6037,7 +6027,7 @@
       <c r="H182" s="10"/>
       <c r="I182" s="23"/>
     </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9">
       <c r="A183" s="10">
         <v>180</v>
       </c>
@@ -6052,7 +6042,7 @@
       <c r="H183" s="10"/>
       <c r="I183" s="23"/>
     </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9">
       <c r="A184" s="10">
         <v>181</v>
       </c>
@@ -6067,7 +6057,7 @@
       <c r="H184" s="10"/>
       <c r="I184" s="23"/>
     </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9">
       <c r="A185" s="10">
         <v>182</v>
       </c>
@@ -6082,7 +6072,7 @@
       <c r="H185" s="10"/>
       <c r="I185" s="23"/>
     </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9">
       <c r="A186" s="10">
         <v>183</v>
       </c>
@@ -6097,7 +6087,7 @@
       <c r="H186" s="10"/>
       <c r="I186" s="23"/>
     </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9">
       <c r="A187" s="10">
         <v>184</v>
       </c>
@@ -6112,7 +6102,7 @@
       <c r="H187" s="10"/>
       <c r="I187" s="23"/>
     </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9">
       <c r="A188" s="10">
         <v>185</v>
       </c>
@@ -6127,7 +6117,7 @@
       <c r="H188" s="10"/>
       <c r="I188" s="23"/>
     </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9">
       <c r="A189" s="10">
         <v>186</v>
       </c>
@@ -6142,7 +6132,7 @@
       <c r="H189" s="10"/>
       <c r="I189" s="23"/>
     </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9">
       <c r="A190" s="10">
         <v>187</v>
       </c>
@@ -6157,7 +6147,7 @@
       <c r="H190" s="10"/>
       <c r="I190" s="23"/>
     </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9">
       <c r="A191" s="10">
         <v>188</v>
       </c>
@@ -6172,7 +6162,7 @@
       <c r="H191" s="10"/>
       <c r="I191" s="23"/>
     </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9">
       <c r="A192" s="10">
         <v>189</v>
       </c>
@@ -6191,7 +6181,7 @@
       <c r="H192" s="10"/>
       <c r="I192" s="23"/>
     </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9">
       <c r="A193" s="10">
         <v>190</v>
       </c>
@@ -6210,7 +6200,7 @@
       <c r="H193" s="10"/>
       <c r="I193" s="23"/>
     </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9">
       <c r="A194" s="10">
         <v>191</v>
       </c>
@@ -6229,7 +6219,7 @@
       <c r="H194" s="10"/>
       <c r="I194" s="23"/>
     </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9">
       <c r="A195" s="10">
         <v>192</v>
       </c>
@@ -6248,7 +6238,7 @@
       <c r="H195" s="10"/>
       <c r="I195" s="23"/>
     </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9">
       <c r="A196" s="10">
         <v>193</v>
       </c>
@@ -6267,7 +6257,7 @@
       <c r="H196" s="10"/>
       <c r="I196" s="23"/>
     </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9">
       <c r="A197" s="10">
         <v>194</v>
       </c>
@@ -6286,7 +6276,7 @@
       <c r="H197" s="10"/>
       <c r="I197" s="23"/>
     </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9">
       <c r="A198" s="10">
         <v>195</v>
       </c>
@@ -6305,7 +6295,7 @@
       <c r="H198" s="10"/>
       <c r="I198" s="23"/>
     </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9">
       <c r="A199" s="10">
         <v>196</v>
       </c>
@@ -6324,7 +6314,7 @@
       <c r="H199" s="10"/>
       <c r="I199" s="23"/>
     </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9">
       <c r="A200" s="10">
         <v>197</v>
       </c>
@@ -6343,7 +6333,7 @@
       <c r="H200" s="10"/>
       <c r="I200" s="23"/>
     </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9">
       <c r="A201" s="10">
         <v>198</v>
       </c>
@@ -6360,7 +6350,7 @@
       <c r="H201" s="10"/>
       <c r="I201" s="23"/>
     </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9">
       <c r="A202" s="10">
         <v>199</v>
       </c>
@@ -6377,7 +6367,7 @@
       <c r="H202" s="10"/>
       <c r="I202" s="23"/>
     </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9">
       <c r="A203" s="10">
         <v>200</v>
       </c>
@@ -6394,7 +6384,7 @@
       <c r="H203" s="10"/>
       <c r="I203" s="23"/>
     </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9">
       <c r="A204" s="10">
         <v>201</v>
       </c>
@@ -6413,7 +6403,7 @@
       <c r="H204" s="10"/>
       <c r="I204" s="23"/>
     </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9">
       <c r="A205" s="10">
         <v>202</v>
       </c>
@@ -6432,7 +6422,7 @@
       <c r="H205" s="10"/>
       <c r="I205" s="23"/>
     </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9">
       <c r="A206" s="10">
         <v>203</v>
       </c>
@@ -6451,7 +6441,7 @@
       <c r="H206" s="10"/>
       <c r="I206" s="23"/>
     </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9">
       <c r="A207" s="10">
         <v>204</v>
       </c>
@@ -6468,7 +6458,7 @@
       <c r="H207" s="10"/>
       <c r="I207" s="23"/>
     </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9">
       <c r="A208" s="10">
         <v>205</v>
       </c>
@@ -6485,7 +6475,7 @@
       <c r="H208" s="10"/>
       <c r="I208" s="23"/>
     </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9">
       <c r="A209" s="10">
         <v>206</v>
       </c>
@@ -6502,7 +6492,7 @@
       <c r="H209" s="10"/>
       <c r="I209" s="23"/>
     </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9">
       <c r="A210" s="10">
         <v>207</v>
       </c>
@@ -6521,7 +6511,7 @@
       <c r="H210" s="10"/>
       <c r="I210" s="23"/>
     </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9">
       <c r="A211" s="10">
         <v>208</v>
       </c>
@@ -6540,7 +6530,7 @@
       <c r="H211" s="10"/>
       <c r="I211" s="23"/>
     </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9">
       <c r="A212" s="10">
         <v>209</v>
       </c>
@@ -6557,7 +6547,7 @@
       <c r="H212" s="10"/>
       <c r="I212" s="23"/>
     </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9">
       <c r="A213" s="10">
         <v>210</v>
       </c>
@@ -6574,7 +6564,7 @@
       <c r="H213" s="10"/>
       <c r="I213" s="23"/>
     </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9">
       <c r="A214" s="10">
         <v>211</v>
       </c>
@@ -6593,7 +6583,7 @@
       <c r="H214" s="10"/>
       <c r="I214" s="23"/>
     </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9">
       <c r="A215" s="10">
         <v>212</v>
       </c>
@@ -6610,7 +6600,7 @@
       <c r="H215" s="10"/>
       <c r="I215" s="23"/>
     </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9">
       <c r="A216" s="10">
         <v>213</v>
       </c>
@@ -6627,7 +6617,7 @@
       <c r="H216" s="10"/>
       <c r="I216" s="23"/>
     </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9">
       <c r="A217" s="10">
         <v>214</v>
       </c>
@@ -6646,7 +6636,7 @@
       <c r="H217" s="10"/>
       <c r="I217" s="23"/>
     </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9">
       <c r="A218" s="10">
         <v>215</v>
       </c>
@@ -6663,7 +6653,7 @@
       <c r="H218" s="10"/>
       <c r="I218" s="23"/>
     </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9">
       <c r="A219" s="10">
         <v>216</v>
       </c>
@@ -6680,7 +6670,7 @@
       <c r="H219" s="10"/>
       <c r="I219" s="23"/>
     </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9">
       <c r="A220" s="10">
         <v>217</v>
       </c>
@@ -6697,7 +6687,7 @@
       <c r="H220" s="10"/>
       <c r="I220" s="23"/>
     </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9">
       <c r="A221" s="10">
         <v>220</v>
       </c>
@@ -6710,7 +6700,7 @@
       <c r="H221" s="10"/>
       <c r="I221" s="23"/>
     </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9">
       <c r="A222" s="10"/>
       <c r="B222" s="16"/>
       <c r="C222" s="19"/>
@@ -6734,9 +6724,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H109"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H110"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="8"/>
     <col min="2" max="2" width="33.7109375" style="8" customWidth="1"/>
@@ -6747,7 +6737,7 @@
     <col min="9" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
@@ -6773,7 +6763,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -6799,7 +6789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -6813,7 +6803,7 @@
         <v>311</v>
       </c>
       <c r="E3" s="38" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F3" s="5">
         <v>2016</v>
@@ -6825,12 +6815,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" s="32" customFormat="1" ht="30" customHeight="1">
       <c r="A4" s="35">
         <v>3</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>298</v>
@@ -6839,7 +6829,7 @@
         <v>311</v>
       </c>
       <c r="E4" s="38" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F4" s="5">
         <v>2016</v>
@@ -6851,7 +6841,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="30" customHeight="1">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -6862,7 +6852,7 @@
         <v>295</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>296</v>
@@ -6877,7 +6867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="30" customHeight="1">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -6903,7 +6893,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="30" customHeight="1">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -6929,7 +6919,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="30" customHeight="1">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -6955,7 +6945,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="30" customHeight="1">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -6981,7 +6971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="30" customHeight="1">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -7007,7 +6997,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="30" customHeight="1">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -7018,7 +7008,7 @@
         <v>318</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E11" s="38" t="s">
         <v>307</v>
@@ -7033,7 +7023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="30" customHeight="1">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -7059,7 +7049,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="30" customHeight="1">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -7085,7 +7075,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="30" customHeight="1">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -7111,7 +7101,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="30" customHeight="1">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -7137,7 +7127,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="30" customHeight="1">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -7163,7 +7153,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" ht="30" customHeight="1">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -7189,7 +7179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" ht="30" customHeight="1">
       <c r="A18" s="35">
         <v>17</v>
       </c>
@@ -7200,7 +7190,7 @@
         <v>331</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="E18" s="40" t="s">
         <v>316</v>
@@ -7215,15 +7205,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="30" customHeight="1">
       <c r="A19" s="35">
         <v>18</v>
       </c>
       <c r="B19" s="40" t="s">
+        <v>333</v>
+      </c>
+      <c r="C19" s="40" t="s">
         <v>334</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>335</v>
       </c>
       <c r="D19" s="40" t="s">
         <v>321</v>
@@ -7241,15 +7231,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" ht="30" customHeight="1">
       <c r="A20" s="35">
         <v>19</v>
       </c>
       <c r="B20" s="40" t="s">
+        <v>335</v>
+      </c>
+      <c r="C20" s="40" t="s">
         <v>336</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>337</v>
       </c>
       <c r="D20" s="40" t="s">
         <v>321</v>
@@ -7267,15 +7257,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" ht="30" customHeight="1">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D21" s="40" t="s">
         <v>311</v>
@@ -7293,15 +7283,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" ht="30" customHeight="1">
       <c r="A22" s="35">
         <v>21</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D22" s="40" t="s">
         <v>311</v>
@@ -7319,15 +7309,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" ht="30" customHeight="1">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D23" s="40" t="s">
         <v>321</v>
@@ -7345,15 +7335,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="30" customHeight="1">
       <c r="A24" s="35">
         <v>23</v>
       </c>
       <c r="B24" s="40" t="s">
+        <v>341</v>
+      </c>
+      <c r="C24" s="40" t="s">
         <v>342</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>343</v>
       </c>
       <c r="D24" s="40" t="s">
         <v>321</v>
@@ -7371,18 +7361,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="30" customHeight="1">
       <c r="A25" s="5">
         <v>24</v>
       </c>
       <c r="B25" s="40" t="s">
+        <v>343</v>
+      </c>
+      <c r="C25" s="40" t="s">
         <v>344</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="D25" s="40" t="s">
         <v>345</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>346</v>
       </c>
       <c r="E25" s="40" t="s">
         <v>316</v>
@@ -7397,24 +7387,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="30" customHeight="1">
       <c r="A26" s="35">
         <v>25</v>
       </c>
       <c r="B26" s="40" t="s">
+        <v>349</v>
+      </c>
+      <c r="C26" s="40" t="s">
         <v>350</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>351</v>
       </c>
       <c r="D26" s="40" t="s">
         <v>321</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G26" s="5" t="s">
         <v>10</v>
@@ -7423,12 +7413,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="30" customHeight="1">
       <c r="A27" s="5">
         <v>26</v>
       </c>
       <c r="B27" s="40" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C27" s="40" t="s">
         <v>330</v>
@@ -7437,10 +7427,10 @@
         <v>311</v>
       </c>
       <c r="E27" s="40" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G27" s="5" t="s">
         <v>10</v>
@@ -7449,24 +7439,24 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" ht="30" customHeight="1">
       <c r="A28" s="35">
         <v>27</v>
       </c>
       <c r="B28" s="38" t="s">
+        <v>391</v>
+      </c>
+      <c r="C28" s="38" t="s">
         <v>392</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="D28" s="38" t="s">
         <v>393</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="E28" s="38" t="s">
         <v>394</v>
       </c>
-      <c r="E28" s="38" t="s">
-        <v>395</v>
-      </c>
       <c r="F28" s="39" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G28" s="39" t="s">
         <v>10</v>
@@ -7475,21 +7465,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="30" customHeight="1">
       <c r="A29" s="5">
         <v>28</v>
       </c>
       <c r="B29" s="40" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="40" t="s">
         <v>357</v>
       </c>
-      <c r="C29" s="40" t="s">
+      <c r="D29" s="40" t="s">
         <v>358</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="E29" s="7" t="s">
         <v>359</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>360</v>
       </c>
       <c r="F29" s="5">
         <v>2024</v>
@@ -7501,21 +7491,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="30" customHeight="1">
       <c r="A30" s="35">
         <v>29</v>
       </c>
       <c r="B30" s="40" t="s">
+        <v>361</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>360</v>
+      </c>
+      <c r="D30" s="40" t="s">
         <v>362</v>
       </c>
-      <c r="C30" s="40" t="s">
-        <v>361</v>
-      </c>
-      <c r="D30" s="40" t="s">
+      <c r="E30" s="7" t="s">
         <v>363</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>364</v>
       </c>
       <c r="F30" s="5">
         <v>2025</v>
@@ -7527,21 +7517,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="30" customHeight="1">
       <c r="A31" s="35">
         <v>30</v>
       </c>
       <c r="B31" s="40" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C31" s="40" t="s">
         <v>123</v>
       </c>
       <c r="D31" s="40" t="s">
+        <v>365</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>366</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>367</v>
       </c>
       <c r="F31" s="5">
         <v>2025</v>
@@ -7553,21 +7543,21 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" ht="30" customHeight="1">
       <c r="A32" s="5">
         <v>31</v>
       </c>
       <c r="B32" s="40" t="s">
+        <v>368</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>345</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>369</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>368</v>
-      </c>
-      <c r="D32" s="40" t="s">
-        <v>346</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>370</v>
       </c>
       <c r="F32" s="5">
         <v>2026</v>
@@ -7579,473 +7569,479 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="30" customHeight="1">
       <c r="A33" s="43">
         <v>32</v>
       </c>
       <c r="B33" s="44" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C33" s="44" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E33" s="45"/>
       <c r="F33" s="46"/>
       <c r="G33" s="46"/>
       <c r="H33" s="46"/>
     </row>
-    <row r="34" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="5"/>
-      <c r="B34" s="52" t="s">
-        <v>411</v>
-      </c>
-      <c r="C34" s="51" t="s">
-        <v>410</v>
-      </c>
-      <c r="D34" s="51" t="s">
-        <v>346</v>
-      </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="5"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
-    </row>
-    <row r="35" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="30" customHeight="1">
+      <c r="A34" s="43">
+        <v>33</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>413</v>
+      </c>
+      <c r="C34" s="44" t="s">
+        <v>384</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>345</v>
+      </c>
+      <c r="E34" s="45"/>
+      <c r="F34" s="46"/>
+      <c r="G34" s="46"/>
+      <c r="H34" s="46"/>
+    </row>
+    <row r="35" spans="1:8" ht="30" customHeight="1">
       <c r="A35" s="5"/>
       <c r="B35" s="52" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C35" s="51" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D35" s="51" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E35" s="7"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
     </row>
-    <row r="36" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="30" customHeight="1">
       <c r="A36" s="5"/>
       <c r="B36" s="52" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C36" s="51" t="s">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="D36" s="51" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E36" s="7"/>
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
     </row>
-    <row r="37" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="30" customHeight="1">
       <c r="A37" s="5"/>
-      <c r="B37" s="38" t="s">
+      <c r="B37" s="52" t="s">
+        <v>412</v>
+      </c>
+      <c r="C37" s="51" t="s">
         <v>381</v>
       </c>
-      <c r="C37" s="38" t="s">
-        <v>382</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>346</v>
+      <c r="D37" s="51" t="s">
+        <v>345</v>
       </c>
       <c r="E37" s="7"/>
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
     </row>
-    <row r="38" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="53"/>
+    <row r="38" spans="1:8" ht="30" customHeight="1">
+      <c r="A38" s="5"/>
       <c r="B38" s="38" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>318</v>
+        <v>381</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E38" s="7"/>
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
     </row>
-    <row r="39" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="5"/>
+    <row r="39" spans="1:8" ht="30" customHeight="1">
+      <c r="A39" s="53"/>
       <c r="B39" s="38" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C39" s="38" t="s">
         <v>318</v>
       </c>
       <c r="D39" s="38" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E39" s="7"/>
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
     </row>
-    <row r="40" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="30" customHeight="1">
       <c r="A40" s="5"/>
-      <c r="B40" s="51" t="s">
-        <v>414</v>
+      <c r="B40" s="38" t="s">
+        <v>379</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>385</v>
-      </c>
-      <c r="D40" s="51" t="s">
-        <v>346</v>
+        <v>318</v>
+      </c>
+      <c r="D40" s="38" t="s">
+        <v>345</v>
       </c>
       <c r="E40" s="7"/>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
     </row>
-    <row r="41" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="30" customHeight="1">
       <c r="A41" s="5"/>
       <c r="B41" s="51" t="s">
-        <v>378</v>
-      </c>
-      <c r="C41" s="51" t="s">
-        <v>377</v>
+        <v>413</v>
+      </c>
+      <c r="C41" s="38" t="s">
+        <v>384</v>
       </c>
       <c r="D41" s="51" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E41" s="7"/>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
     </row>
-    <row r="42" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="30" customHeight="1">
       <c r="A42" s="5"/>
       <c r="B42" s="51" t="s">
-        <v>415</v>
+        <v>377</v>
       </c>
       <c r="C42" s="51" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D42" s="51" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E42" s="7"/>
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
     </row>
-    <row r="43" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="30" customHeight="1">
       <c r="A43" s="5"/>
-      <c r="B43" s="51"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
+      <c r="B43" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>367</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>345</v>
+      </c>
       <c r="E43" s="7"/>
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
     </row>
-    <row r="44" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="30" customHeight="1">
       <c r="A44" s="5"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="38"/>
-      <c r="D44" s="38"/>
+      <c r="B44" s="51"/>
+      <c r="C44" s="51"/>
+      <c r="D44" s="51"/>
       <c r="E44" s="7"/>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
     </row>
-    <row r="45" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>33</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="C45" s="40" t="s">
-        <v>375</v>
-      </c>
-      <c r="D45" s="40" t="s">
-        <v>376</v>
-      </c>
+    <row r="45" spans="1:8" ht="30" customHeight="1">
+      <c r="A45" s="5"/>
+      <c r="B45" s="38"/>
+      <c r="C45" s="38"/>
+      <c r="D45" s="38"/>
       <c r="E45" s="7"/>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
     </row>
-    <row r="46" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="30" customHeight="1">
       <c r="A46" s="5">
+        <v>33</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C46" s="40" t="s">
+        <v>374</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>375</v>
+      </c>
+      <c r="E46" s="7"/>
+      <c r="F46" s="5"/>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8" ht="30" customHeight="1">
+      <c r="A47" s="5">
         <v>34</v>
       </c>
-      <c r="B46" s="38" t="s">
-        <v>378</v>
-      </c>
-      <c r="C46" s="38" t="s">
+      <c r="B47" s="38" t="s">
         <v>377</v>
       </c>
-      <c r="D46" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="E46" s="41"/>
-      <c r="F46" s="42"/>
-      <c r="G46" s="42"/>
-      <c r="H46" s="42"/>
-    </row>
-    <row r="47" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="5">
-        <v>38</v>
-      </c>
-      <c r="B47" s="38" t="s">
-        <v>383</v>
-      </c>
       <c r="C47" s="38" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>346</v>
-      </c>
-      <c r="E47" s="42"/>
+        <v>345</v>
+      </c>
+      <c r="E47" s="41"/>
       <c r="F47" s="42"/>
       <c r="G47" s="42"/>
       <c r="H47" s="42"/>
     </row>
-    <row r="48" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="30" customHeight="1">
       <c r="A48" s="5">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="38" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C48" s="38" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E48" s="42"/>
       <c r="F48" s="42"/>
       <c r="G48" s="42"/>
       <c r="H48" s="42"/>
     </row>
-    <row r="49" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="30" customHeight="1">
       <c r="A49" s="5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B49" s="38" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C49" s="38" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="D49" s="38" t="s">
-        <v>386</v>
+        <v>345</v>
       </c>
       <c r="E49" s="42"/>
       <c r="F49" s="42"/>
       <c r="G49" s="42"/>
       <c r="H49" s="42"/>
     </row>
-    <row r="50" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="30" customHeight="1">
       <c r="A50" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B50" s="38" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C50" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D50" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E50" s="42"/>
       <c r="F50" s="42"/>
       <c r="G50" s="42"/>
       <c r="H50" s="42"/>
     </row>
-    <row r="51" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="30" customHeight="1">
       <c r="A51" s="5">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="38" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C51" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D51" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E51" s="42"/>
       <c r="F51" s="42"/>
       <c r="G51" s="42"/>
       <c r="H51" s="42"/>
     </row>
-    <row r="52" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="30" customHeight="1">
       <c r="A52" s="5">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="38" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C52" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D52" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E52" s="42"/>
       <c r="F52" s="42"/>
       <c r="G52" s="42"/>
       <c r="H52" s="42"/>
     </row>
-    <row r="53" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="30" customHeight="1">
       <c r="A53" s="5">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B53" s="38" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C53" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D53" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E53" s="42"/>
       <c r="F53" s="42"/>
       <c r="G53" s="42"/>
       <c r="H53" s="42"/>
     </row>
-    <row r="54" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="30" customHeight="1">
       <c r="A54" s="5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B54" s="38" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="C54" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D54" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E54" s="42"/>
       <c r="F54" s="42"/>
       <c r="G54" s="42"/>
       <c r="H54" s="42"/>
     </row>
-    <row r="55" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="30" customHeight="1">
       <c r="A55" s="5">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B55" s="38" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C55" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D55" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E55" s="42"/>
       <c r="F55" s="42"/>
       <c r="G55" s="42"/>
       <c r="H55" s="42"/>
     </row>
-    <row r="56" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="30" customHeight="1">
       <c r="A56" s="5">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="38" t="s">
-        <v>257</v>
+        <v>396</v>
       </c>
       <c r="C56" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D56" s="38" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E56" s="42"/>
       <c r="F56" s="42"/>
       <c r="G56" s="42"/>
       <c r="H56" s="42"/>
     </row>
-    <row r="57" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="30" customHeight="1">
       <c r="A57" s="5">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="38" t="s">
-        <v>398</v>
+        <v>257</v>
       </c>
       <c r="C57" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D57" s="38" t="s">
-        <v>399</v>
+        <v>385</v>
       </c>
       <c r="E57" s="42"/>
       <c r="F57" s="42"/>
       <c r="G57" s="42"/>
       <c r="H57" s="42"/>
     </row>
-    <row r="58" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="30" customHeight="1">
       <c r="A58" s="5">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" s="38" t="s">
-        <v>48</v>
+        <v>397</v>
       </c>
       <c r="C58" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D58" s="38" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E58" s="42"/>
       <c r="F58" s="42"/>
       <c r="G58" s="42"/>
       <c r="H58" s="42"/>
     </row>
-    <row r="59" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="30" customHeight="1">
       <c r="A59" s="5">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B59" s="38" t="s">
-        <v>400</v>
+        <v>48</v>
       </c>
       <c r="C59" s="38" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D59" s="38" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E59" s="42"/>
       <c r="F59" s="42"/>
       <c r="G59" s="42"/>
       <c r="H59" s="42"/>
     </row>
-    <row r="60" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="30" customHeight="1">
       <c r="A60" s="5">
-        <v>51</v>
-      </c>
-      <c r="B60" s="42"/>
-      <c r="C60" s="42"/>
-      <c r="D60" s="42"/>
+        <v>50</v>
+      </c>
+      <c r="B60" s="38" t="s">
+        <v>399</v>
+      </c>
+      <c r="C60" s="38" t="s">
+        <v>357</v>
+      </c>
+      <c r="D60" s="38" t="s">
+        <v>398</v>
+      </c>
       <c r="E60" s="42"/>
       <c r="F60" s="42"/>
       <c r="G60" s="42"/>
       <c r="H60" s="42"/>
     </row>
-    <row r="61" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="30" customHeight="1">
       <c r="A61" s="5">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B61" s="42"/>
       <c r="C61" s="42"/>
@@ -8055,9 +8051,9 @@
       <c r="G61" s="42"/>
       <c r="H61" s="42"/>
     </row>
-    <row r="62" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="30" customHeight="1">
       <c r="A62" s="5">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B62" s="42"/>
       <c r="C62" s="42"/>
@@ -8067,9 +8063,9 @@
       <c r="G62" s="42"/>
       <c r="H62" s="42"/>
     </row>
-    <row r="63" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="30" customHeight="1">
       <c r="A63" s="5">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B63" s="42"/>
       <c r="C63" s="42"/>
@@ -8079,9 +8075,9 @@
       <c r="G63" s="42"/>
       <c r="H63" s="42"/>
     </row>
-    <row r="64" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="30" customHeight="1">
       <c r="A64" s="5">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B64" s="42"/>
       <c r="C64" s="42"/>
@@ -8091,9 +8087,9 @@
       <c r="G64" s="42"/>
       <c r="H64" s="42"/>
     </row>
-    <row r="65" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" ht="30" customHeight="1">
       <c r="A65" s="5">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B65" s="42"/>
       <c r="C65" s="42"/>
@@ -8103,9 +8099,9 @@
       <c r="G65" s="42"/>
       <c r="H65" s="42"/>
     </row>
-    <row r="66" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" ht="30" customHeight="1">
       <c r="A66" s="5">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66" s="42"/>
       <c r="C66" s="42"/>
@@ -8115,9 +8111,9 @@
       <c r="G66" s="42"/>
       <c r="H66" s="42"/>
     </row>
-    <row r="67" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" ht="30" customHeight="1">
       <c r="A67" s="5">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67" s="42"/>
       <c r="C67" s="42"/>
@@ -8127,9 +8123,9 @@
       <c r="G67" s="42"/>
       <c r="H67" s="42"/>
     </row>
-    <row r="68" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" ht="30" customHeight="1">
       <c r="A68" s="5">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B68" s="42"/>
       <c r="C68" s="42"/>
@@ -8139,9 +8135,9 @@
       <c r="G68" s="42"/>
       <c r="H68" s="42"/>
     </row>
-    <row r="69" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" ht="30" customHeight="1">
       <c r="A69" s="5">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B69" s="42"/>
       <c r="C69" s="42"/>
@@ -8151,9 +8147,9 @@
       <c r="G69" s="42"/>
       <c r="H69" s="42"/>
     </row>
-    <row r="70" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" ht="30" customHeight="1">
       <c r="A70" s="5">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B70" s="42"/>
       <c r="C70" s="42"/>
@@ -8163,9 +8159,9 @@
       <c r="G70" s="42"/>
       <c r="H70" s="42"/>
     </row>
-    <row r="71" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" ht="30" customHeight="1">
       <c r="A71" s="5">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B71" s="42"/>
       <c r="C71" s="42"/>
@@ -8175,9 +8171,9 @@
       <c r="G71" s="42"/>
       <c r="H71" s="42"/>
     </row>
-    <row r="72" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" ht="30" customHeight="1">
       <c r="A72" s="5">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B72" s="42"/>
       <c r="C72" s="42"/>
@@ -8187,9 +8183,9 @@
       <c r="G72" s="42"/>
       <c r="H72" s="42"/>
     </row>
-    <row r="73" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" ht="30" customHeight="1">
       <c r="A73" s="5">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B73" s="42"/>
       <c r="C73" s="42"/>
@@ -8199,9 +8195,9 @@
       <c r="G73" s="42"/>
       <c r="H73" s="42"/>
     </row>
-    <row r="74" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" ht="30" customHeight="1">
       <c r="A74" s="5">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B74" s="42"/>
       <c r="C74" s="42"/>
@@ -8211,9 +8207,9 @@
       <c r="G74" s="42"/>
       <c r="H74" s="42"/>
     </row>
-    <row r="75" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" ht="30" customHeight="1">
       <c r="A75" s="5">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B75" s="42"/>
       <c r="C75" s="42"/>
@@ -8223,9 +8219,9 @@
       <c r="G75" s="42"/>
       <c r="H75" s="42"/>
     </row>
-    <row r="76" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" ht="30" customHeight="1">
       <c r="A76" s="5">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B76" s="42"/>
       <c r="C76" s="42"/>
@@ -8235,9 +8231,9 @@
       <c r="G76" s="42"/>
       <c r="H76" s="42"/>
     </row>
-    <row r="77" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" ht="30" customHeight="1">
       <c r="A77" s="5">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B77" s="42"/>
       <c r="C77" s="42"/>
@@ -8247,9 +8243,9 @@
       <c r="G77" s="42"/>
       <c r="H77" s="42"/>
     </row>
-    <row r="78" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" ht="30" customHeight="1">
       <c r="A78" s="5">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B78" s="42"/>
       <c r="C78" s="42"/>
@@ -8259,9 +8255,9 @@
       <c r="G78" s="42"/>
       <c r="H78" s="42"/>
     </row>
-    <row r="79" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" ht="30" customHeight="1">
       <c r="A79" s="5">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B79" s="42"/>
       <c r="C79" s="42"/>
@@ -8271,9 +8267,9 @@
       <c r="G79" s="42"/>
       <c r="H79" s="42"/>
     </row>
-    <row r="80" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" ht="30" customHeight="1">
       <c r="A80" s="5">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B80" s="42"/>
       <c r="C80" s="42"/>
@@ -8283,9 +8279,9 @@
       <c r="G80" s="42"/>
       <c r="H80" s="42"/>
     </row>
-    <row r="81" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" ht="30" customHeight="1">
       <c r="A81" s="5">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B81" s="42"/>
       <c r="C81" s="42"/>
@@ -8295,9 +8291,9 @@
       <c r="G81" s="42"/>
       <c r="H81" s="42"/>
     </row>
-    <row r="82" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" ht="30" customHeight="1">
       <c r="A82" s="5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B82" s="42"/>
       <c r="C82" s="42"/>
@@ -8307,9 +8303,9 @@
       <c r="G82" s="42"/>
       <c r="H82" s="42"/>
     </row>
-    <row r="83" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" ht="30" customHeight="1">
       <c r="A83" s="5">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B83" s="42"/>
       <c r="C83" s="42"/>
@@ -8319,9 +8315,9 @@
       <c r="G83" s="42"/>
       <c r="H83" s="42"/>
     </row>
-    <row r="84" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" ht="30" customHeight="1">
       <c r="A84" s="5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B84" s="42"/>
       <c r="C84" s="42"/>
@@ -8331,9 +8327,9 @@
       <c r="G84" s="42"/>
       <c r="H84" s="42"/>
     </row>
-    <row r="85" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" ht="30" customHeight="1">
       <c r="A85" s="5">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B85" s="42"/>
       <c r="C85" s="42"/>
@@ -8343,9 +8339,9 @@
       <c r="G85" s="42"/>
       <c r="H85" s="42"/>
     </row>
-    <row r="86" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" ht="30" customHeight="1">
       <c r="A86" s="5">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B86" s="42"/>
       <c r="C86" s="42"/>
@@ -8355,9 +8351,9 @@
       <c r="G86" s="42"/>
       <c r="H86" s="42"/>
     </row>
-    <row r="87" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" ht="30" customHeight="1">
       <c r="A87" s="5">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B87" s="42"/>
       <c r="C87" s="42"/>
@@ -8367,9 +8363,9 @@
       <c r="G87" s="42"/>
       <c r="H87" s="42"/>
     </row>
-    <row r="88" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" ht="30" customHeight="1">
       <c r="A88" s="5">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B88" s="42"/>
       <c r="C88" s="42"/>
@@ -8379,9 +8375,9 @@
       <c r="G88" s="42"/>
       <c r="H88" s="42"/>
     </row>
-    <row r="89" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="30" customHeight="1">
       <c r="A89" s="5">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B89" s="42"/>
       <c r="C89" s="42"/>
@@ -8391,9 +8387,9 @@
       <c r="G89" s="42"/>
       <c r="H89" s="42"/>
     </row>
-    <row r="90" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" ht="30" customHeight="1">
       <c r="A90" s="5">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B90" s="42"/>
       <c r="C90" s="42"/>
@@ -8403,9 +8399,9 @@
       <c r="G90" s="42"/>
       <c r="H90" s="42"/>
     </row>
-    <row r="91" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="30" customHeight="1">
       <c r="A91" s="5">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B91" s="42"/>
       <c r="C91" s="42"/>
@@ -8415,9 +8411,9 @@
       <c r="G91" s="42"/>
       <c r="H91" s="42"/>
     </row>
-    <row r="92" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" ht="30" customHeight="1">
       <c r="A92" s="5">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B92" s="42"/>
       <c r="C92" s="42"/>
@@ -8427,9 +8423,9 @@
       <c r="G92" s="42"/>
       <c r="H92" s="42"/>
     </row>
-    <row r="93" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" ht="30" customHeight="1">
       <c r="A93" s="5">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B93" s="42"/>
       <c r="C93" s="42"/>
@@ -8439,9 +8435,9 @@
       <c r="G93" s="42"/>
       <c r="H93" s="42"/>
     </row>
-    <row r="94" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="30" customHeight="1">
       <c r="A94" s="5">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B94" s="42"/>
       <c r="C94" s="42"/>
@@ -8451,9 +8447,9 @@
       <c r="G94" s="42"/>
       <c r="H94" s="42"/>
     </row>
-    <row r="95" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" ht="30" customHeight="1">
       <c r="A95" s="5">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B95" s="42"/>
       <c r="C95" s="42"/>
@@ -8463,9 +8459,9 @@
       <c r="G95" s="42"/>
       <c r="H95" s="42"/>
     </row>
-    <row r="96" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" ht="30" customHeight="1">
       <c r="A96" s="5">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B96" s="42"/>
       <c r="C96" s="42"/>
@@ -8475,9 +8471,9 @@
       <c r="G96" s="42"/>
       <c r="H96" s="42"/>
     </row>
-    <row r="97" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" ht="30" customHeight="1">
       <c r="A97" s="5">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B97" s="42"/>
       <c r="C97" s="42"/>
@@ -8487,9 +8483,9 @@
       <c r="G97" s="42"/>
       <c r="H97" s="42"/>
     </row>
-    <row r="98" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" ht="30" customHeight="1">
       <c r="A98" s="5">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B98" s="42"/>
       <c r="C98" s="42"/>
@@ -8499,9 +8495,9 @@
       <c r="G98" s="42"/>
       <c r="H98" s="42"/>
     </row>
-    <row r="99" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" ht="30" customHeight="1">
       <c r="A99" s="5">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B99" s="42"/>
       <c r="C99" s="42"/>
@@ -8511,9 +8507,9 @@
       <c r="G99" s="42"/>
       <c r="H99" s="42"/>
     </row>
-    <row r="100" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" ht="30" customHeight="1">
       <c r="A100" s="5">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B100" s="42"/>
       <c r="C100" s="42"/>
@@ -8523,9 +8519,9 @@
       <c r="G100" s="42"/>
       <c r="H100" s="42"/>
     </row>
-    <row r="101" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" ht="30" customHeight="1">
       <c r="A101" s="5">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B101" s="42"/>
       <c r="C101" s="42"/>
@@ -8535,9 +8531,9 @@
       <c r="G101" s="42"/>
       <c r="H101" s="42"/>
     </row>
-    <row r="102" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" ht="30" customHeight="1">
       <c r="A102" s="5">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B102" s="42"/>
       <c r="C102" s="42"/>
@@ -8547,9 +8543,9 @@
       <c r="G102" s="42"/>
       <c r="H102" s="42"/>
     </row>
-    <row r="103" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" ht="30" customHeight="1">
       <c r="A103" s="5">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B103" s="42"/>
       <c r="C103" s="42"/>
@@ -8559,9 +8555,9 @@
       <c r="G103" s="42"/>
       <c r="H103" s="42"/>
     </row>
-    <row r="104" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" ht="30" customHeight="1">
       <c r="A104" s="5">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B104" s="42"/>
       <c r="C104" s="42"/>
@@ -8571,9 +8567,9 @@
       <c r="G104" s="42"/>
       <c r="H104" s="42"/>
     </row>
-    <row r="105" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" ht="30" customHeight="1">
       <c r="A105" s="5">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B105" s="42"/>
       <c r="C105" s="42"/>
@@ -8583,9 +8579,9 @@
       <c r="G105" s="42"/>
       <c r="H105" s="42"/>
     </row>
-    <row r="106" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" ht="30" customHeight="1">
       <c r="A106" s="5">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B106" s="42"/>
       <c r="C106" s="42"/>
@@ -8595,9 +8591,9 @@
       <c r="G106" s="42"/>
       <c r="H106" s="42"/>
     </row>
-    <row r="107" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" ht="30" customHeight="1">
       <c r="A107" s="5">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B107" s="42"/>
       <c r="C107" s="42"/>
@@ -8607,9 +8603,9 @@
       <c r="G107" s="42"/>
       <c r="H107" s="42"/>
     </row>
-    <row r="108" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" ht="30" customHeight="1">
       <c r="A108" s="5">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B108" s="42"/>
       <c r="C108" s="42"/>
@@ -8619,9 +8615,9 @@
       <c r="G108" s="42"/>
       <c r="H108" s="42"/>
     </row>
-    <row r="109" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" ht="30" customHeight="1">
       <c r="A109" s="5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B109" s="42"/>
       <c r="C109" s="42"/>
@@ -8631,8 +8627,20 @@
       <c r="G109" s="42"/>
       <c r="H109" s="42"/>
     </row>
+    <row r="110" spans="1:8" ht="30" customHeight="1">
+      <c r="A110" s="5">
+        <v>100</v>
+      </c>
+      <c r="B110" s="42"/>
+      <c r="C110" s="42"/>
+      <c r="D110" s="42"/>
+      <c r="E110" s="42"/>
+      <c r="F110" s="42"/>
+      <c r="G110" s="42"/>
+      <c r="H110" s="42"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H109"/>
+  <autoFilter ref="A1:H110"/>
   <hyperlinks>
     <hyperlink ref="C11" r:id="rId1" display="https://yandex.ru/search/?srm=1&amp;text=%D0%AD%D1%80%D0%B8%D1%85%20%D0%9C%D0%B0%D1%80%D0%B8%D1%8F%20%D0%A0%D0%B5%D0%BC%D0%B0%D1%80%D0%BA&amp;lr=14&amp;clid=2270455&amp;win=687&amp;primary_reqid=1786517055526639-14999433768309566645-balancer-l7leveler-kubr-yp-klg-171-BAL&amp;noreask=1&amp;ento=0oCghydXcyMzA3MhgCKglydXcyMzEzNDdqF9Ci0YDQuCDRgtC-0LLQsNGA0LjRidCwcgrQkNCy0YLQvtGAyYrrdg"/>
   </hyperlinks>
@@ -8642,27 +8650,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="8"/>
     <col min="3" max="3" width="19.85546875" style="8" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="47" t="s">
+        <v>407</v>
+      </c>
+      <c r="C1" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="C1" s="47" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8673,7 +8681,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8685,7 +8693,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -8697,7 +8705,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8709,7 +8717,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -8721,7 +8729,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8733,7 +8741,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8745,7 +8753,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8757,7 +8765,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -8769,7 +8777,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8781,7 +8789,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -8793,7 +8801,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -8805,7 +8813,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -8817,7 +8825,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -8829,7 +8837,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -8841,7 +8849,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -8853,7 +8861,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -8865,7 +8873,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -8877,7 +8885,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -8889,7 +8897,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8901,7 +8909,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3">
       <c r="A22" s="49">
         <v>21</v>
       </c>
@@ -8918,9 +8926,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
@@ -8928,9 +8936,9 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
     <col min="2" max="2" width="11.5703125" style="2" customWidth="1"/>
@@ -8939,7 +8947,7 @@
     <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" s="1" customFormat="1" ht="30" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -8974,13 +8982,13 @@
         <v>281</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
     </row>
-    <row r="2" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="45" customHeight="1">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -9004,7 +9012,7 @@
       </c>
       <c r="L2" s="7"/>
     </row>
-    <row r="3" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="45" customHeight="1">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -9028,7 +9036,7 @@
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
     </row>
-    <row r="4" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="45" customHeight="1">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -9056,7 +9064,7 @@
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15" ht="45" customHeight="1">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -9075,10 +9083,10 @@
       <c r="J5" s="7"/>
       <c r="K5" s="7"/>
       <c r="L5" s="7" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="45" customHeight="1">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -9086,7 +9094,7 @@
         <v>46263</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="7" t="s">
@@ -9094,7 +9102,7 @@
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
@@ -9102,7 +9110,7 @@
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15" ht="45" customHeight="1">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -9117,18 +9125,18 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="K7" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="K7" s="7" t="s">
-        <v>407</v>
-      </c>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15" ht="45" customHeight="1">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -9144,7 +9152,7 @@
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15" ht="45" customHeight="1">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -9160,7 +9168,7 @@
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
     </row>
-    <row r="10" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15" ht="45" customHeight="1">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -9176,7 +9184,7 @@
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" spans="1:15" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:15" ht="45" customHeight="1">
       <c r="A11" s="5">
         <v>10</v>
       </c>
